--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -62871,7 +62871,7 @@
         <v>1104653</v>
       </c>
       <c r="C2718" t="n">
-        <v>12.4099998474121</v>
+        <v>12.4499998092651</v>
       </c>
       <c r="D2718" t="n">
         <v>12.210000038147</v>
@@ -62883,6 +62883,29 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G2718" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>1637638</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>12.6899995803833</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>12.0600004196167</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>12.3100004196167</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>12.2950000762939</v>
+      </c>
+      <c r="G2719" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>1534353</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>12.5200004577637</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>12.1800003051758</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>12.3000001907349</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>12.3450002670288</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>1164810</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>12.4350004196167</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>12.1450004577637</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>12.3450002670288</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>12.2700004577637</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>1670362</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>12.6700000762939</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>12.335000038147</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>12.3400001525879</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>12.5649995803833</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>1377947</v>
+        <v>824125</v>
       </c>
       <c r="C2715" t="n">
-        <v>12.6549997329712</v>
+        <v>12.4300003051758</v>
       </c>
       <c r="D2715" t="n">
-        <v>12.2950000762939</v>
+        <v>12.1899995803833</v>
       </c>
       <c r="E2715" t="n">
-        <v>12.3149995803833</v>
+        <v>12.2399997711182</v>
       </c>
       <c r="F2715" t="n">
-        <v>12.5900001525879</v>
+        <v>12.3299999237061</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>1487560</v>
+        <v>1377947</v>
       </c>
       <c r="C2716" t="n">
-        <v>12.6949996948242</v>
+        <v>12.6549997329712</v>
       </c>
       <c r="D2716" t="n">
-        <v>12.0950002670288</v>
+        <v>12.2950000762939</v>
       </c>
       <c r="E2716" t="n">
-        <v>12.6949996948242</v>
+        <v>12.3149995803833</v>
       </c>
       <c r="F2716" t="n">
-        <v>12.1350002288818</v>
+        <v>12.5900001525879</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>1152687</v>
+        <v>1487560</v>
       </c>
       <c r="C2717" t="n">
-        <v>12.3900003433228</v>
+        <v>12.6949996948242</v>
       </c>
       <c r="D2717" t="n">
-        <v>12.0600004196167</v>
+        <v>12.0950002670288</v>
       </c>
       <c r="E2717" t="n">
-        <v>12.2049999237061</v>
+        <v>12.6949996948242</v>
       </c>
       <c r="F2717" t="n">
-        <v>12.3050003051758</v>
+        <v>12.1350002288818</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>1104653</v>
+        <v>1152687</v>
       </c>
       <c r="C2718" t="n">
-        <v>12.4499998092651</v>
+        <v>12.3900003433228</v>
       </c>
       <c r="D2718" t="n">
-        <v>12.210000038147</v>
+        <v>12.0600004196167</v>
       </c>
       <c r="E2718" t="n">
-        <v>12.210000038147</v>
+        <v>12.2049999237061</v>
       </c>
       <c r="F2718" t="n">
-        <v>12.4499998092651</v>
+        <v>12.3050003051758</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>1637638</v>
+        <v>1104653</v>
       </c>
       <c r="C2719" t="n">
-        <v>12.6899995803833</v>
+        <v>12.4499998092651</v>
       </c>
       <c r="D2719" t="n">
-        <v>12.0600004196167</v>
+        <v>12.210000038147</v>
       </c>
       <c r="E2719" t="n">
-        <v>12.3100004196167</v>
+        <v>12.210000038147</v>
       </c>
       <c r="F2719" t="n">
-        <v>12.2950000762939</v>
+        <v>12.4499998092651</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>1534353</v>
+        <v>1637638</v>
       </c>
       <c r="C2720" t="n">
-        <v>12.5200004577637</v>
+        <v>12.6899995803833</v>
       </c>
       <c r="D2720" t="n">
-        <v>12.1800003051758</v>
+        <v>12.0600004196167</v>
       </c>
       <c r="E2720" t="n">
-        <v>12.3000001907349</v>
+        <v>12.3100004196167</v>
       </c>
       <c r="F2720" t="n">
-        <v>12.3450002670288</v>
+        <v>12.2950000762939</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>1164810</v>
+        <v>1534353</v>
       </c>
       <c r="C2721" t="n">
-        <v>12.4350004196167</v>
+        <v>12.5200004577637</v>
       </c>
       <c r="D2721" t="n">
-        <v>12.1450004577637</v>
+        <v>12.1800003051758</v>
       </c>
       <c r="E2721" t="n">
+        <v>12.3000001907349</v>
+      </c>
+      <c r="F2721" t="n">
         <v>12.3450002670288</v>
-      </c>
-      <c r="F2721" t="n">
-        <v>12.2700004577637</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>1670362</v>
+        <v>1164810</v>
       </c>
       <c r="C2722" t="n">
-        <v>12.6700000762939</v>
+        <v>12.4350004196167</v>
       </c>
       <c r="D2722" t="n">
-        <v>12.335000038147</v>
+        <v>12.1450004577637</v>
       </c>
       <c r="E2722" t="n">
-        <v>12.3400001525879</v>
+        <v>12.3450002670288</v>
       </c>
       <c r="F2722" t="n">
-        <v>12.5649995803833</v>
+        <v>12.2700004577637</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>1443385</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>12.6750001907349</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>12.3800001144409</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>12.5450000762939</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>12.4300003051758</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.17872190475464</v>
       </c>
       <c r="G2" t="n">
-        <v>3.12481331825256</v>
+        <v>3.12481355667114</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.59337210655212</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5493905544281</v>
+        <v>2.54939079284668</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.60422611236572</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56006073951721</v>
+        <v>2.56006050109863</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.45769500732422</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4160144329071</v>
+        <v>2.41601467132568</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.76006102561951</v>
       </c>
       <c r="G18" t="n">
-        <v>2.71325278282166</v>
+        <v>2.71325254440308</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.71354293823242</v>
       </c>
       <c r="G23" t="n">
-        <v>2.66752338409424</v>
+        <v>2.66752362251282</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.56468605995178</v>
       </c>
       <c r="G24" t="n">
-        <v>2.52119135856628</v>
+        <v>2.52119112014771</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.41272711753845</v>
       </c>
       <c r="G26" t="n">
-        <v>2.37180948257446</v>
+        <v>2.37180924415588</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.25999402999878</v>
       </c>
       <c r="G27" t="n">
-        <v>2.22166657447815</v>
+        <v>2.22166633605957</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.10880994796753</v>
       </c>
       <c r="G28" t="n">
-        <v>2.07304620742798</v>
+        <v>2.07304644584656</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.0933051109314</v>
       </c>
       <c r="G30" t="n">
-        <v>2.05780434608459</v>
+        <v>2.05780458450317</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.41040110588074</v>
       </c>
       <c r="G33" t="n">
-        <v>2.3695228099823</v>
+        <v>2.36952257156372</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G35" t="n">
-        <v>2.56615734100342</v>
+        <v>2.566157579422</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.46389698982239</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42211151123047</v>
+        <v>2.42211127281189</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.64066505432129</v>
       </c>
       <c r="G37" t="n">
-        <v>2.59588170051575</v>
+        <v>2.59588146209717</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.45381808280945</v>
       </c>
       <c r="G50" t="n">
-        <v>2.41220331192017</v>
+        <v>2.41220355033875</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.64841794967651</v>
       </c>
       <c r="G54" t="n">
-        <v>2.60350298881531</v>
+        <v>2.60350322723389</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.73680210113525</v>
       </c>
       <c r="G56" t="n">
-        <v>2.69038844108582</v>
+        <v>2.69038820266724</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G60" t="n">
-        <v>2.56615734100342</v>
+        <v>2.566157579422</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.97326803207397</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92284393310547</v>
+        <v>2.92284369468689</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.87790608406067</v>
       </c>
       <c r="G71" t="n">
-        <v>2.82909917831421</v>
+        <v>2.82909941673279</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.87480497360229</v>
       </c>
       <c r="G72" t="n">
-        <v>2.82605075836182</v>
+        <v>2.82605051994324</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.81975889205933</v>
       </c>
       <c r="G75" t="n">
-        <v>2.77193808555603</v>
+        <v>2.77193832397461</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.77634191513062</v>
       </c>
       <c r="G76" t="n">
-        <v>2.72925758361816</v>
+        <v>2.72925734519958</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G77" t="n">
-        <v>2.73306894302368</v>
+        <v>2.7330687046051</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.79727506637573</v>
       </c>
       <c r="G81" t="n">
-        <v>2.749835729599</v>
+        <v>2.74983549118042</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.5476291179657</v>
       </c>
       <c r="G90" t="n">
-        <v>2.50442361831665</v>
+        <v>2.50442337989807</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G94" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G96" t="n">
-        <v>2.73306894302368</v>
+        <v>2.7330687046051</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.94070506095886</v>
       </c>
       <c r="G97" t="n">
-        <v>2.89083337783813</v>
+        <v>2.89083313941956</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G101" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.9693911075592</v>
       </c>
       <c r="G104" t="n">
-        <v>2.91903281211853</v>
+        <v>2.91903257369995</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G105" t="n">
-        <v>2.88244986534119</v>
+        <v>2.88244962692261</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.8934121131897</v>
       </c>
       <c r="G106" t="n">
-        <v>2.84434247016907</v>
+        <v>2.84434223175049</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.94458198547363</v>
       </c>
       <c r="G107" t="n">
-        <v>2.89464449882507</v>
+        <v>2.89464426040649</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.91201901435852</v>
       </c>
       <c r="G109" t="n">
-        <v>2.86263370513916</v>
+        <v>2.86263346672058</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G112" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.64919304847717</v>
       </c>
       <c r="G115" t="n">
-        <v>2.6042652130127</v>
+        <v>2.60426497459412</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.90581703186035</v>
       </c>
       <c r="G120" t="n">
-        <v>2.8565366268158</v>
+        <v>2.85653686523438</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.80502796173096</v>
       </c>
       <c r="G122" t="n">
-        <v>2.75745725631714</v>
+        <v>2.75745701789856</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.53057289123535</v>
       </c>
       <c r="G129" t="n">
-        <v>2.48765659332275</v>
+        <v>2.48765635490417</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.43831205368042</v>
       </c>
       <c r="G132" t="n">
-        <v>2.39696025848389</v>
+        <v>2.39696049690247</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56082248687744</v>
+        <v>2.56082224845886</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56082248687744</v>
+        <v>2.56082224845886</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.7057900428772</v>
       </c>
       <c r="G138" t="n">
-        <v>2.65990209579468</v>
+        <v>2.65990233421326</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.89186191558838</v>
       </c>
       <c r="G143" t="n">
-        <v>2.84281849861145</v>
+        <v>2.84281826019287</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G144" t="n">
-        <v>2.88244986534119</v>
+        <v>2.88244962692261</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.95310997962952</v>
       </c>
       <c r="G147" t="n">
-        <v>2.90302777290344</v>
+        <v>2.90302753448486</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.9918749332428</v>
       </c>
       <c r="G148" t="n">
-        <v>2.94113540649414</v>
+        <v>2.94113516807556</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.96551489830017</v>
       </c>
       <c r="G150" t="n">
-        <v>2.91522240638733</v>
+        <v>2.91522216796875</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.93527793884277</v>
       </c>
       <c r="G154" t="n">
-        <v>2.885498046875</v>
+        <v>2.88549828529358</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.95388507843018</v>
       </c>
       <c r="G157" t="n">
-        <v>2.90378952026367</v>
+        <v>2.90378975868225</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.05855107307434</v>
       </c>
       <c r="G159" t="n">
-        <v>3.00668048858643</v>
+        <v>3.006680727005</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.0221118927002</v>
       </c>
       <c r="G160" t="n">
-        <v>2.97085928916931</v>
+        <v>2.97085952758789</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.97404289245605</v>
       </c>
       <c r="G162" t="n">
-        <v>2.92360544204712</v>
+        <v>2.9236056804657</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.02676391601562</v>
       </c>
       <c r="G164" t="n">
-        <v>2.97543263435364</v>
+        <v>2.97543239593506</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.35936594009399</v>
       </c>
       <c r="G175" t="n">
-        <v>3.30239391326904</v>
+        <v>3.30239415168762</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.38262510299683</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32525849342346</v>
+        <v>3.32525873184204</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.31750011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>3.26123833656311</v>
+        <v>3.26123809814453</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.23764491081238</v>
       </c>
       <c r="G182" t="n">
-        <v>3.18273735046387</v>
+        <v>3.18273711204529</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.20430707931519</v>
       </c>
       <c r="G184" t="n">
-        <v>3.14996480941772</v>
+        <v>3.14996457099915</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.35083794593811</v>
       </c>
       <c r="G188" t="n">
-        <v>3.29401040077209</v>
+        <v>3.29401063919067</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.35548996925354</v>
       </c>
       <c r="G192" t="n">
-        <v>3.29858374595642</v>
+        <v>3.29858350753784</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.3570408821106</v>
       </c>
       <c r="G197" t="n">
-        <v>3.30010843276978</v>
+        <v>3.3001081943512</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.33067989349365</v>
       </c>
       <c r="G199" t="n">
-        <v>3.27419424057007</v>
+        <v>3.27419447898865</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.35238909721375</v>
       </c>
       <c r="G200" t="n">
-        <v>3.29553556442261</v>
+        <v>3.29553532600403</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.34308505058289</v>
       </c>
       <c r="G206" t="n">
-        <v>3.28638911247253</v>
+        <v>3.28638935089111</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.19965505599976</v>
       </c>
       <c r="G214" t="n">
-        <v>3.14539170265198</v>
+        <v>3.1453914642334</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.20353198051453</v>
       </c>
       <c r="G215" t="n">
-        <v>3.14920282363892</v>
+        <v>3.14920258522034</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.04226899147034</v>
       </c>
       <c r="G219" t="n">
-        <v>2.99067449569702</v>
+        <v>2.9906747341156</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.23299288749695</v>
       </c>
       <c r="G221" t="n">
-        <v>3.17816424369812</v>
+        <v>3.17816400527954</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.24384689331055</v>
       </c>
       <c r="G222" t="n">
-        <v>3.18883395195007</v>
+        <v>3.18883419036865</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.37254691123962</v>
       </c>
       <c r="G223" t="n">
-        <v>3.31535148620605</v>
+        <v>3.31535124778748</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G229" t="n">
-        <v>3.19340705871582</v>
+        <v>3.1934072971344</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.24617290496826</v>
       </c>
       <c r="G231" t="n">
-        <v>3.19112038612366</v>
+        <v>3.19112062454224</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G232" t="n">
-        <v>3.18197464942932</v>
+        <v>3.18197441101074</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.22601509094238</v>
       </c>
       <c r="G236" t="n">
-        <v>3.17130446434021</v>
+        <v>3.17130470275879</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G237" t="n">
-        <v>3.19340705871582</v>
+        <v>3.1934072971344</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G240" t="n">
-        <v>3.18197464942932</v>
+        <v>3.18197441101074</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.26167893409729</v>
       </c>
       <c r="G246" t="n">
-        <v>3.20636367797852</v>
+        <v>3.20636343955994</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.32602906227112</v>
       </c>
       <c r="G247" t="n">
-        <v>3.26962232589722</v>
+        <v>3.2696225643158</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.5446629524231</v>
       </c>
       <c r="G252" t="n">
-        <v>3.48454856872559</v>
+        <v>3.48454833030701</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.721431016922</v>
       </c>
       <c r="G258" t="n">
-        <v>3.65831875801086</v>
+        <v>3.65831851959229</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.00053787231445</v>
       </c>
       <c r="G260" t="n">
-        <v>3.93269205093384</v>
+        <v>3.93269228935242</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.05093193054199</v>
       </c>
       <c r="G266" t="n">
-        <v>3.9822313785553</v>
+        <v>3.98223161697388</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.18661022186279</v>
       </c>
       <c r="G272" t="n">
-        <v>4.11560869216919</v>
+        <v>4.11560916900635</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>4.27964496612549</v>
       </c>
       <c r="G273" t="n">
-        <v>4.20706605911255</v>
+        <v>4.20706558227539</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.43858098983765</v>
       </c>
       <c r="G274" t="n">
-        <v>4.36330652236938</v>
+        <v>4.36330604553223</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.442458152771</v>
       </c>
       <c r="G275" t="n">
-        <v>4.3671178817749</v>
+        <v>4.36711740493774</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.3610520362854</v>
       </c>
       <c r="G277" t="n">
-        <v>4.28709268569946</v>
+        <v>4.2870922088623</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.25251007080078</v>
       </c>
       <c r="G278" t="n">
-        <v>4.18039131164551</v>
+        <v>4.18039083480835</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.33779287338257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.26422739028931</v>
+        <v>4.26422786712646</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.27189207077026</v>
       </c>
       <c r="G284" t="n">
-        <v>4.19944477081299</v>
+        <v>4.19944429397583</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.12846183776855</v>
       </c>
       <c r="G288" t="n">
-        <v>4.05844688415527</v>
+        <v>4.05844640731812</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G291" t="n">
-        <v>4.5271692276001</v>
+        <v>4.52716970443726</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.52386379241943</v>
       </c>
       <c r="G293" t="n">
-        <v>4.44714260101318</v>
+        <v>4.44714307785034</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G297" t="n">
-        <v>4.5271692276001</v>
+        <v>4.52716970443726</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.64403486251831</v>
       </c>
       <c r="G299" t="n">
-        <v>4.5652756690979</v>
+        <v>4.56527614593506</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.88437795639038</v>
       </c>
       <c r="G301" t="n">
-        <v>4.80154275894165</v>
+        <v>4.80154323577881</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.09758520126343</v>
       </c>
       <c r="G302" t="n">
-        <v>5.0111346244812</v>
+        <v>5.01113414764404</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5.02780818939209</v>
       </c>
       <c r="G311" t="n">
-        <v>4.94254064559937</v>
+        <v>4.94254112243652</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5.06657314300537</v>
       </c>
       <c r="G313" t="n">
-        <v>4.98064804077148</v>
+        <v>4.98064851760864</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.11309099197388</v>
       </c>
       <c r="G316" t="n">
-        <v>5.02637767791748</v>
+        <v>5.02637720108032</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.19449710845947</v>
       </c>
       <c r="G317" t="n">
-        <v>5.10640239715576</v>
+        <v>5.10640287399292</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.21388006210327</v>
       </c>
       <c r="G320" t="n">
-        <v>5.12545728683472</v>
+        <v>5.12545680999756</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.48523378372192</v>
       </c>
       <c r="G322" t="n">
-        <v>5.39220857620239</v>
+        <v>5.39220905303955</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>6.08609008789062</v>
       </c>
       <c r="G326" t="n">
-        <v>5.98287487030029</v>
+        <v>5.98287534713745</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.11710214614868</v>
       </c>
       <c r="G328" t="n">
-        <v>6.01336097717285</v>
+        <v>6.01336145401001</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>6.20238494873047</v>
       </c>
       <c r="G333" t="n">
-        <v>6.09719800949097</v>
+        <v>6.09719753265381</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>7.13661909103394</v>
       </c>
       <c r="G338" t="n">
-        <v>7.01558828353882</v>
+        <v>7.01558780670166</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G339" t="n">
-        <v>6.72215986251831</v>
+        <v>6.72216033935547</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>7.07847213745117</v>
       </c>
       <c r="G343" t="n">
-        <v>6.95842695236206</v>
+        <v>6.95842742919922</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>7.02420091629028</v>
       </c>
       <c r="G344" t="n">
-        <v>6.90507650375366</v>
+        <v>6.9050760269165</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G346" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>7.40797281265259</v>
       </c>
       <c r="G347" t="n">
-        <v>7.28234004974365</v>
+        <v>7.28233957290649</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>6.38845586776733</v>
       </c>
       <c r="G352" t="n">
-        <v>6.28011274337769</v>
+        <v>6.28011322021484</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.03583002090454</v>
       </c>
       <c r="G358" t="n">
-        <v>6.91650867462158</v>
+        <v>6.91650819778442</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G360" t="n">
-        <v>6.72215986251831</v>
+        <v>6.72216033935547</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>6.86526489257812</v>
       </c>
       <c r="G369" t="n">
-        <v>6.74883604049683</v>
+        <v>6.74883556365967</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.77222919464111</v>
       </c>
       <c r="G370" t="n">
-        <v>6.65737771987915</v>
+        <v>6.65737819671631</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.76835203170776</v>
       </c>
       <c r="G372" t="n">
-        <v>6.65356636047363</v>
+        <v>6.65356683731079</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7.37308502197266</v>
       </c>
       <c r="G382" t="n">
-        <v>7.24804353713989</v>
+        <v>7.24804401397705</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G386" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.72972202301025</v>
       </c>
       <c r="G390" t="n">
-        <v>7.59863233566284</v>
+        <v>7.5986328125</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G392" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G394" t="n">
-        <v>8.1931095123291</v>
+        <v>8.19310855865479</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G395" t="n">
-        <v>8.36078262329102</v>
+        <v>8.3607816696167</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.0708532333374</v>
       </c>
       <c r="G398" t="n">
-        <v>7.93397808074951</v>
+        <v>7.93397903442383</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.03208827972412</v>
       </c>
       <c r="G399" t="n">
-        <v>7.89587068557739</v>
+        <v>7.89587116241455</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G402" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>7.67545080184937</v>
       </c>
       <c r="G409" t="n">
-        <v>7.54528188705444</v>
+        <v>7.54528141021729</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>7.30718517303467</v>
       </c>
       <c r="G412" t="n">
-        <v>7.18326187133789</v>
+        <v>7.18326139450073</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>7.07071876525879</v>
       </c>
       <c r="G417" t="n">
-        <v>6.95080518722534</v>
+        <v>6.9508056640625</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.985435962677</v>
       </c>
       <c r="G419" t="n">
-        <v>6.86696910858154</v>
+        <v>6.86696863174438</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G422" t="n">
-        <v>7.27853012084961</v>
+        <v>7.27852964401245</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.17925977706909</v>
       </c>
       <c r="G426" t="n">
-        <v>7.05750560760498</v>
+        <v>7.05750608444214</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G427" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.00107669830322</v>
       </c>
       <c r="G431" t="n">
-        <v>7.86538505554199</v>
+        <v>7.86538553237915</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.7142162322998</v>
       </c>
       <c r="G433" t="n">
-        <v>7.58338975906372</v>
+        <v>7.58338928222656</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G434" t="n">
-        <v>7.94922113418579</v>
+        <v>7.94922161102295</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G438" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G440" t="n">
-        <v>7.94922113418579</v>
+        <v>7.94922161102295</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G441" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G446" t="n">
-        <v>8.36078262329102</v>
+        <v>8.3607816696167</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>8.06309986114502</v>
       </c>
       <c r="G447" t="n">
-        <v>7.92635631561279</v>
+        <v>7.92635583877563</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G451" t="n">
-        <v>7.36617660522461</v>
+        <v>7.36617708206177</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>7.58629179000854</v>
       </c>
       <c r="G452" t="n">
-        <v>7.45763492584229</v>
+        <v>7.45763444900513</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.51651477813721</v>
       </c>
       <c r="G455" t="n">
-        <v>7.38904142379761</v>
+        <v>7.38904094696045</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G459" t="n">
-        <v>7.31663751602173</v>
+        <v>7.31663703918457</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G460" t="n">
-        <v>7.27853012084961</v>
+        <v>7.27852964401245</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.50100898742676</v>
       </c>
       <c r="G463" t="n">
-        <v>7.37379789352417</v>
+        <v>7.37379837036133</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G464" t="n">
-        <v>7.31663751602173</v>
+        <v>7.31663703918457</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.44673776626587</v>
       </c>
       <c r="G466" t="n">
-        <v>7.32044744491577</v>
+        <v>7.32044696807861</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G467" t="n">
-        <v>7.36617660522461</v>
+        <v>7.36617708206177</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>8.54378509521484</v>
       </c>
       <c r="G471" t="n">
-        <v>8.39889049530029</v>
+        <v>8.39888954162598</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G472" t="n">
-        <v>8.1931095123291</v>
+        <v>8.19310855865479</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>8.24141883850098</v>
       </c>
       <c r="G474" t="n">
-        <v>8.10165214538574</v>
+        <v>8.10165119171143</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>8.21040725708008</v>
       </c>
       <c r="G475" t="n">
-        <v>8.07116508483887</v>
+        <v>8.07116603851318</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>8.38872623443604</v>
       </c>
       <c r="G478" t="n">
-        <v>8.2464599609375</v>
+        <v>8.24646091461182</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.87716293334961</v>
       </c>
       <c r="G480" t="n">
-        <v>8.72661399841309</v>
+        <v>8.72661304473877</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G484" t="n">
-        <v>8.8866662979126</v>
+        <v>8.88666534423828</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.04772853851318</v>
       </c>
       <c r="G485" t="n">
-        <v>8.89428615570068</v>
+        <v>8.894287109375</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.17177677154541</v>
       </c>
       <c r="G488" t="n">
-        <v>9.01623058319092</v>
+        <v>9.01623153686523</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G497" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G501" t="n">
-        <v>9.96129608154297</v>
+        <v>9.96129703521729</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10.1796636581421</v>
       </c>
       <c r="G503" t="n">
-        <v>10.007025718689</v>
+        <v>10.0070247650146</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G506" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G507" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G510" t="n">
-        <v>9.79362392425537</v>
+        <v>9.79362297058105</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.70673179626465</v>
       </c>
       <c r="G511" t="n">
-        <v>9.5421142578125</v>
+        <v>9.54211330413818</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>10.1486520767212</v>
       </c>
       <c r="G513" t="n">
-        <v>9.97653865814209</v>
+        <v>9.97653961181641</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>10.5285491943359</v>
       </c>
       <c r="G515" t="n">
-        <v>10.3499946594238</v>
+        <v>10.3499937057495</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>11.2108106613159</v>
       </c>
       <c r="G519" t="n">
-        <v>11.0206842422485</v>
+        <v>11.0206851959229</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>11.265082359314</v>
       </c>
       <c r="G523" t="n">
-        <v>11.0740365982056</v>
+        <v>11.0740356445312</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>11.3658714294434</v>
       </c>
       <c r="G525" t="n">
-        <v>11.1731157302856</v>
+        <v>11.17311668396</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>11.3426122665405</v>
       </c>
       <c r="G526" t="n">
-        <v>11.1502513885498</v>
+        <v>11.1502504348755</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G528" t="n">
-        <v>10.8225269317627</v>
+        <v>10.8225259780884</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G534" t="n">
-        <v>10.8225269317627</v>
+        <v>10.8225259780884</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>10.4200067520142</v>
       </c>
       <c r="G540" t="n">
-        <v>10.2432928085327</v>
+        <v>10.2432918548584</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>10.5052900314331</v>
       </c>
       <c r="G541" t="n">
-        <v>10.3271293640137</v>
+        <v>10.3271284103394</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>10.4665250778198</v>
       </c>
       <c r="G545" t="n">
-        <v>10.2890224456787</v>
+        <v>10.2890214920044</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>10.3889951705933</v>
       </c>
       <c r="G549" t="n">
-        <v>10.2128057479858</v>
+        <v>10.2128067016602</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.9548282623291</v>
       </c>
       <c r="G551" t="n">
-        <v>9.78600311279297</v>
+        <v>9.78600215911865</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>9.59043788909912</v>
       </c>
       <c r="G555" t="n">
-        <v>9.42779159545898</v>
+        <v>9.4277925491333</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G561" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G563" t="n">
-        <v>9.79362392425537</v>
+        <v>9.79362297058105</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>10.1951704025269</v>
       </c>
       <c r="G568" t="n">
-        <v>10.0222692489624</v>
+        <v>10.0222682952881</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>11.0247392654419</v>
       </c>
       <c r="G572" t="n">
-        <v>10.8377695083618</v>
+        <v>10.8377685546875</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G577" t="n">
-        <v>8.8866662979126</v>
+        <v>8.88666534423828</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>9.11750602722168</v>
       </c>
       <c r="G580" t="n">
-        <v>8.96288108825684</v>
+        <v>8.96288013458252</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>9.45088386535645</v>
       </c>
       <c r="G581" t="n">
-        <v>9.29060459136963</v>
+        <v>9.29060554504395</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9.83078002929688</v>
       </c>
       <c r="G588" t="n">
-        <v>9.66405773162842</v>
+        <v>9.66405868530273</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G594" t="n">
-        <v>9.96129608154297</v>
+        <v>9.96129703521729</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>10.7068672180176</v>
       </c>
       <c r="G598" t="n">
-        <v>10.5252885818481</v>
+        <v>10.5252876281738</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>10.4277601242065</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2509145736694</v>
+        <v>10.2509136199951</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>10.0090990066528</v>
       </c>
       <c r="G607" t="n">
-        <v>9.83935260772705</v>
+        <v>9.83935356140137</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -71222,6 +71222,32 @@
         <v>12.6300001144409</v>
       </c>
       <c r="H2725" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>1302794</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>12.6949996948242</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>12.3599996566772</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>12.6599998474121</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>12.4099998474121</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>12.4099998474121</v>
+      </c>
+      <c r="H2726" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -71251,6 +71251,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2727" t="n">
+        <v>2578974</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>12.5200004577637</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>12</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>12.3500003814697</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>12.4350004196167</v>
+      </c>
+      <c r="G2727" t="n">
+        <v>12.4350004196167</v>
+      </c>
+      <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -71277,6 +71277,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>4196562</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>12.3149995803833</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>11.7200002670288</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>12.3100004196167</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>11.7550001144409</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>11.7550001144409</v>
+      </c>
+      <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -71303,6 +71303,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>2980067</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>11.9350004196167</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>11.5500001907349</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>11.8900003433228</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>11.7799997329712</v>
+      </c>
+      <c r="G2729" t="n">
+        <v>11.7799997329712</v>
+      </c>
+      <c r="H2729" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -71381,6 +71381,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2732">
+      <c r="A2732" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2732" t="n">
+        <v>2238255</v>
+      </c>
+      <c r="C2732" t="n">
+        <v>12.3649997711182</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>11.9899997711182</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>12.039999961853</v>
+      </c>
+      <c r="G2732" t="n">
+        <v>12.039999961853</v>
+      </c>
+      <c r="H2732" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>12.1750001907349</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>12.6850004196167</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>3488062</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>12.789999961853</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>12.1199998855591</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>12.6599998474121</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>12.6599998474121</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>12.2349996566772</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>1979452</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>12.3000001907349</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>11.9399995803833</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>12.1750001907349</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>12.1750001907349</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>11.9650001525879</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>1926741</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>11.6499996185303</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>11.8999996185303</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>11.8999996185303</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>11.6800003051758</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>3330043</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>12.5249996185303</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>11.6899995803833</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>11.7349996566772</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>2023579</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>12.7449998855591</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>12.3999996185303</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>12.3999996185303</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>12.5699996948242</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.17872190475464</v>
       </c>
       <c r="G2" t="n">
-        <v>3.12481355667114</v>
+        <v>3.12481331825256</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>2.59337210655212</v>
       </c>
       <c r="G9" t="n">
-        <v>2.54939079284668</v>
+        <v>2.5493905544281</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>2.60422611236572</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56006050109863</v>
+        <v>2.56006073951721</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>2.45769500732422</v>
       </c>
       <c r="G13" t="n">
-        <v>2.41601467132568</v>
+        <v>2.4160144329071</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>2.76006102561951</v>
       </c>
       <c r="G18" t="n">
-        <v>2.71325254440308</v>
+        <v>2.71325278282166</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>2.71354293823242</v>
       </c>
       <c r="G23" t="n">
-        <v>2.66752362251282</v>
+        <v>2.66752338409424</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>2.56468605995178</v>
       </c>
       <c r="G24" t="n">
-        <v>2.52119112014771</v>
+        <v>2.52119135856628</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>2.41272711753845</v>
       </c>
       <c r="G26" t="n">
-        <v>2.37180924415588</v>
+        <v>2.37180948257446</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.25999402999878</v>
       </c>
       <c r="G27" t="n">
-        <v>2.22166633605957</v>
+        <v>2.22166657447815</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>2.10880994796753</v>
       </c>
       <c r="G28" t="n">
-        <v>2.07304644584656</v>
+        <v>2.07304620742798</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>2.0933051109314</v>
       </c>
       <c r="G30" t="n">
-        <v>2.05780458450317</v>
+        <v>2.05780434608459</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>2.41040110588074</v>
       </c>
       <c r="G33" t="n">
-        <v>2.36952257156372</v>
+        <v>2.3695228099823</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G35" t="n">
-        <v>2.566157579422</v>
+        <v>2.56615734100342</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>2.46389698982239</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42211127281189</v>
+        <v>2.42211151123047</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.64066505432129</v>
       </c>
       <c r="G37" t="n">
-        <v>2.59588146209717</v>
+        <v>2.59588170051575</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>2.45381808280945</v>
       </c>
       <c r="G50" t="n">
-        <v>2.41220355033875</v>
+        <v>2.41220331192017</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>2.64841794967651</v>
       </c>
       <c r="G54" t="n">
-        <v>2.60350322723389</v>
+        <v>2.60350298881531</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>2.73680210113525</v>
       </c>
       <c r="G56" t="n">
-        <v>2.69038820266724</v>
+        <v>2.69038844108582</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G60" t="n">
-        <v>2.566157579422</v>
+        <v>2.56615734100342</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>2.97326803207397</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92284369468689</v>
+        <v>2.92284393310547</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>2.87790608406067</v>
       </c>
       <c r="G71" t="n">
-        <v>2.82909941673279</v>
+        <v>2.82909917831421</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>2.87480497360229</v>
       </c>
       <c r="G72" t="n">
-        <v>2.82605051994324</v>
+        <v>2.82605075836182</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>2.81975889205933</v>
       </c>
       <c r="G75" t="n">
-        <v>2.77193832397461</v>
+        <v>2.77193808555603</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>2.77634191513062</v>
       </c>
       <c r="G76" t="n">
-        <v>2.72925734519958</v>
+        <v>2.72925758361816</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G77" t="n">
-        <v>2.7330687046051</v>
+        <v>2.73306894302368</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>2.79727506637573</v>
       </c>
       <c r="G81" t="n">
-        <v>2.74983549118042</v>
+        <v>2.749835729599</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>2.5476291179657</v>
       </c>
       <c r="G90" t="n">
-        <v>2.50442337989807</v>
+        <v>2.50442361831665</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G94" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G96" t="n">
-        <v>2.7330687046051</v>
+        <v>2.73306894302368</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.94070506095886</v>
       </c>
       <c r="G97" t="n">
-        <v>2.89083313941956</v>
+        <v>2.89083337783813</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G101" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.9693911075592</v>
       </c>
       <c r="G104" t="n">
-        <v>2.91903257369995</v>
+        <v>2.91903281211853</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G105" t="n">
-        <v>2.88244962692261</v>
+        <v>2.88244986534119</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.8934121131897</v>
       </c>
       <c r="G106" t="n">
-        <v>2.84434223175049</v>
+        <v>2.84434247016907</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.94458198547363</v>
       </c>
       <c r="G107" t="n">
-        <v>2.89464426040649</v>
+        <v>2.89464449882507</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.91201901435852</v>
       </c>
       <c r="G109" t="n">
-        <v>2.86263346672058</v>
+        <v>2.86263370513916</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G112" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.64919304847717</v>
       </c>
       <c r="G115" t="n">
-        <v>2.60426497459412</v>
+        <v>2.6042652130127</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.90581703186035</v>
       </c>
       <c r="G120" t="n">
-        <v>2.85653686523438</v>
+        <v>2.8565366268158</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.80502796173096</v>
       </c>
       <c r="G122" t="n">
-        <v>2.75745701789856</v>
+        <v>2.75745725631714</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.53057289123535</v>
       </c>
       <c r="G129" t="n">
-        <v>2.48765635490417</v>
+        <v>2.48765659332275</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.43831205368042</v>
       </c>
       <c r="G132" t="n">
-        <v>2.39696049690247</v>
+        <v>2.39696025848389</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56082224845886</v>
+        <v>2.56082248687744</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56082224845886</v>
+        <v>2.56082248687744</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.7057900428772</v>
       </c>
       <c r="G138" t="n">
-        <v>2.65990233421326</v>
+        <v>2.65990209579468</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.89186191558838</v>
       </c>
       <c r="G143" t="n">
-        <v>2.84281826019287</v>
+        <v>2.84281849861145</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G144" t="n">
-        <v>2.88244962692261</v>
+        <v>2.88244986534119</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.95310997962952</v>
       </c>
       <c r="G147" t="n">
-        <v>2.90302753448486</v>
+        <v>2.90302777290344</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.9918749332428</v>
       </c>
       <c r="G148" t="n">
-        <v>2.94113516807556</v>
+        <v>2.94113540649414</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>2.96551489830017</v>
       </c>
       <c r="G150" t="n">
-        <v>2.91522216796875</v>
+        <v>2.91522240638733</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.93527793884277</v>
       </c>
       <c r="G154" t="n">
-        <v>2.88549828529358</v>
+        <v>2.885498046875</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.95388507843018</v>
       </c>
       <c r="G157" t="n">
-        <v>2.90378975868225</v>
+        <v>2.90378952026367</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.05855107307434</v>
       </c>
       <c r="G159" t="n">
-        <v>3.006680727005</v>
+        <v>3.00668048858643</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.0221118927002</v>
       </c>
       <c r="G160" t="n">
-        <v>2.97085952758789</v>
+        <v>2.97085928916931</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>2.97404289245605</v>
       </c>
       <c r="G162" t="n">
-        <v>2.9236056804657</v>
+        <v>2.92360544204712</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.02676391601562</v>
       </c>
       <c r="G164" t="n">
-        <v>2.97543239593506</v>
+        <v>2.97543263435364</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.35936594009399</v>
       </c>
       <c r="G175" t="n">
-        <v>3.30239415168762</v>
+        <v>3.30239391326904</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.38262510299683</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32525873184204</v>
+        <v>3.32525849342346</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.31750011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>3.26123809814453</v>
+        <v>3.26123833656311</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>3.23764491081238</v>
       </c>
       <c r="G182" t="n">
-        <v>3.18273711204529</v>
+        <v>3.18273735046387</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3.20430707931519</v>
       </c>
       <c r="G184" t="n">
-        <v>3.14996457099915</v>
+        <v>3.14996480941772</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>3.35083794593811</v>
       </c>
       <c r="G188" t="n">
-        <v>3.29401063919067</v>
+        <v>3.29401040077209</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>3.35548996925354</v>
       </c>
       <c r="G192" t="n">
-        <v>3.29858350753784</v>
+        <v>3.29858374595642</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.3570408821106</v>
       </c>
       <c r="G197" t="n">
-        <v>3.3001081943512</v>
+        <v>3.30010843276978</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.33067989349365</v>
       </c>
       <c r="G199" t="n">
-        <v>3.27419447898865</v>
+        <v>3.27419424057007</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.35238909721375</v>
       </c>
       <c r="G200" t="n">
-        <v>3.29553532600403</v>
+        <v>3.29553556442261</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.34308505058289</v>
       </c>
       <c r="G206" t="n">
-        <v>3.28638935089111</v>
+        <v>3.28638911247253</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.19965505599976</v>
       </c>
       <c r="G214" t="n">
-        <v>3.1453914642334</v>
+        <v>3.14539170265198</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.20353198051453</v>
       </c>
       <c r="G215" t="n">
-        <v>3.14920258522034</v>
+        <v>3.14920282363892</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3.04226899147034</v>
       </c>
       <c r="G219" t="n">
-        <v>2.9906747341156</v>
+        <v>2.99067449569702</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.23299288749695</v>
       </c>
       <c r="G221" t="n">
-        <v>3.17816400527954</v>
+        <v>3.17816424369812</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.24384689331055</v>
       </c>
       <c r="G222" t="n">
-        <v>3.18883419036865</v>
+        <v>3.18883395195007</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.37254691123962</v>
       </c>
       <c r="G223" t="n">
-        <v>3.31535124778748</v>
+        <v>3.31535148620605</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G229" t="n">
-        <v>3.1934072971344</v>
+        <v>3.19340705871582</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>3.24617290496826</v>
       </c>
       <c r="G231" t="n">
-        <v>3.19112062454224</v>
+        <v>3.19112038612366</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G232" t="n">
-        <v>3.18197441101074</v>
+        <v>3.18197464942932</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>3.22601509094238</v>
       </c>
       <c r="G236" t="n">
-        <v>3.17130470275879</v>
+        <v>3.17130446434021</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G237" t="n">
-        <v>3.1934072971344</v>
+        <v>3.19340705871582</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G240" t="n">
-        <v>3.18197441101074</v>
+        <v>3.18197464942932</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3.26167893409729</v>
       </c>
       <c r="G246" t="n">
-        <v>3.20636343955994</v>
+        <v>3.20636367797852</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>3.32602906227112</v>
       </c>
       <c r="G247" t="n">
-        <v>3.2696225643158</v>
+        <v>3.26962232589722</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>3.5446629524231</v>
       </c>
       <c r="G252" t="n">
-        <v>3.48454833030701</v>
+        <v>3.48454856872559</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>3.721431016922</v>
       </c>
       <c r="G258" t="n">
-        <v>3.65831851959229</v>
+        <v>3.65831875801086</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>4.00053787231445</v>
       </c>
       <c r="G260" t="n">
-        <v>3.93269228935242</v>
+        <v>3.93269205093384</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>4.05093193054199</v>
       </c>
       <c r="G266" t="n">
-        <v>3.98223161697388</v>
+        <v>3.9822313785553</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>4.18661022186279</v>
       </c>
       <c r="G272" t="n">
-        <v>4.11560916900635</v>
+        <v>4.11560869216919</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>4.27964496612549</v>
       </c>
       <c r="G273" t="n">
-        <v>4.20706558227539</v>
+        <v>4.20706605911255</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>4.43858098983765</v>
       </c>
       <c r="G274" t="n">
-        <v>4.36330604553223</v>
+        <v>4.36330652236938</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.442458152771</v>
       </c>
       <c r="G275" t="n">
-        <v>4.36711740493774</v>
+        <v>4.3671178817749</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>4.3610520362854</v>
       </c>
       <c r="G277" t="n">
-        <v>4.2870922088623</v>
+        <v>4.28709268569946</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.25251007080078</v>
       </c>
       <c r="G278" t="n">
-        <v>4.18039083480835</v>
+        <v>4.18039131164551</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>4.33779287338257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.26422786712646</v>
+        <v>4.26422739028931</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>4.27189207077026</v>
       </c>
       <c r="G284" t="n">
-        <v>4.19944429397583</v>
+        <v>4.19944477081299</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.12846183776855</v>
       </c>
       <c r="G288" t="n">
-        <v>4.05844640731812</v>
+        <v>4.05844688415527</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G291" t="n">
-        <v>4.52716970443726</v>
+        <v>4.5271692276001</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>4.52386379241943</v>
       </c>
       <c r="G293" t="n">
-        <v>4.44714307785034</v>
+        <v>4.44714260101318</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G297" t="n">
-        <v>4.52716970443726</v>
+        <v>4.5271692276001</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>4.64403486251831</v>
       </c>
       <c r="G299" t="n">
-        <v>4.56527614593506</v>
+        <v>4.5652756690979</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.88437795639038</v>
       </c>
       <c r="G301" t="n">
-        <v>4.80154323577881</v>
+        <v>4.80154275894165</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.09758520126343</v>
       </c>
       <c r="G302" t="n">
-        <v>5.01113414764404</v>
+        <v>5.0111346244812</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>5.02780818939209</v>
       </c>
       <c r="G311" t="n">
-        <v>4.94254112243652</v>
+        <v>4.94254064559937</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>5.06657314300537</v>
       </c>
       <c r="G313" t="n">
-        <v>4.98064851760864</v>
+        <v>4.98064804077148</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>5.11309099197388</v>
       </c>
       <c r="G316" t="n">
-        <v>5.02637720108032</v>
+        <v>5.02637767791748</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>5.19449710845947</v>
       </c>
       <c r="G317" t="n">
-        <v>5.10640287399292</v>
+        <v>5.10640239715576</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>5.21388006210327</v>
       </c>
       <c r="G320" t="n">
-        <v>5.12545680999756</v>
+        <v>5.12545728683472</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>5.48523378372192</v>
       </c>
       <c r="G322" t="n">
-        <v>5.39220905303955</v>
+        <v>5.39220857620239</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>6.08609008789062</v>
       </c>
       <c r="G326" t="n">
-        <v>5.98287534713745</v>
+        <v>5.98287487030029</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.11710214614868</v>
       </c>
       <c r="G328" t="n">
-        <v>6.01336145401001</v>
+        <v>6.01336097717285</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>6.20238494873047</v>
       </c>
       <c r="G333" t="n">
-        <v>6.09719753265381</v>
+        <v>6.09719800949097</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>7.13661909103394</v>
       </c>
       <c r="G338" t="n">
-        <v>7.01558780670166</v>
+        <v>7.01558828353882</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G339" t="n">
-        <v>6.72216033935547</v>
+        <v>6.72215986251831</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>7.07847213745117</v>
       </c>
       <c r="G343" t="n">
-        <v>6.95842742919922</v>
+        <v>6.95842695236206</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>7.02420091629028</v>
       </c>
       <c r="G344" t="n">
-        <v>6.9050760269165</v>
+        <v>6.90507650375366</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G346" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>7.40797281265259</v>
       </c>
       <c r="G347" t="n">
-        <v>7.28233957290649</v>
+        <v>7.28234004974365</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>6.38845586776733</v>
       </c>
       <c r="G352" t="n">
-        <v>6.28011322021484</v>
+        <v>6.28011274337769</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>7.03583002090454</v>
       </c>
       <c r="G358" t="n">
-        <v>6.91650819778442</v>
+        <v>6.91650867462158</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G360" t="n">
-        <v>6.72216033935547</v>
+        <v>6.72215986251831</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>6.86526489257812</v>
       </c>
       <c r="G369" t="n">
-        <v>6.74883556365967</v>
+        <v>6.74883604049683</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.77222919464111</v>
       </c>
       <c r="G370" t="n">
-        <v>6.65737819671631</v>
+        <v>6.65737771987915</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>6.76835203170776</v>
       </c>
       <c r="G372" t="n">
-        <v>6.65356683731079</v>
+        <v>6.65356636047363</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>7.37308502197266</v>
       </c>
       <c r="G382" t="n">
-        <v>7.24804401397705</v>
+        <v>7.24804353713989</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G386" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>7.72972202301025</v>
       </c>
       <c r="G390" t="n">
-        <v>7.5986328125</v>
+        <v>7.59863233566284</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G392" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G394" t="n">
-        <v>8.19310855865479</v>
+        <v>8.1931095123291</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G395" t="n">
-        <v>8.3607816696167</v>
+        <v>8.36078262329102</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.0708532333374</v>
       </c>
       <c r="G398" t="n">
-        <v>7.93397903442383</v>
+        <v>7.93397808074951</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.03208827972412</v>
       </c>
       <c r="G399" t="n">
-        <v>7.89587116241455</v>
+        <v>7.89587068557739</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G402" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>7.67545080184937</v>
       </c>
       <c r="G409" t="n">
-        <v>7.54528141021729</v>
+        <v>7.54528188705444</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>7.30718517303467</v>
       </c>
       <c r="G412" t="n">
-        <v>7.18326139450073</v>
+        <v>7.18326187133789</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>7.07071876525879</v>
       </c>
       <c r="G417" t="n">
-        <v>6.9508056640625</v>
+        <v>6.95080518722534</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.985435962677</v>
       </c>
       <c r="G419" t="n">
-        <v>6.86696863174438</v>
+        <v>6.86696910858154</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G422" t="n">
-        <v>7.27852964401245</v>
+        <v>7.27853012084961</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>7.17925977706909</v>
       </c>
       <c r="G426" t="n">
-        <v>7.05750608444214</v>
+        <v>7.05750560760498</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G427" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.00107669830322</v>
       </c>
       <c r="G431" t="n">
-        <v>7.86538553237915</v>
+        <v>7.86538505554199</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>7.7142162322998</v>
       </c>
       <c r="G433" t="n">
-        <v>7.58338928222656</v>
+        <v>7.58338975906372</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G434" t="n">
-        <v>7.94922161102295</v>
+        <v>7.94922113418579</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G438" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G440" t="n">
-        <v>7.94922161102295</v>
+        <v>7.94922113418579</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G441" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G446" t="n">
-        <v>8.3607816696167</v>
+        <v>8.36078262329102</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>8.06309986114502</v>
       </c>
       <c r="G447" t="n">
-        <v>7.92635583877563</v>
+        <v>7.92635631561279</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G451" t="n">
-        <v>7.36617708206177</v>
+        <v>7.36617660522461</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>7.58629179000854</v>
       </c>
       <c r="G452" t="n">
-        <v>7.45763444900513</v>
+        <v>7.45763492584229</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>7.51651477813721</v>
       </c>
       <c r="G455" t="n">
-        <v>7.38904094696045</v>
+        <v>7.38904142379761</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G459" t="n">
-        <v>7.31663703918457</v>
+        <v>7.31663751602173</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G460" t="n">
-        <v>7.27852964401245</v>
+        <v>7.27853012084961</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>7.50100898742676</v>
       </c>
       <c r="G463" t="n">
-        <v>7.37379837036133</v>
+        <v>7.37379789352417</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G464" t="n">
-        <v>7.31663703918457</v>
+        <v>7.31663751602173</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>7.44673776626587</v>
       </c>
       <c r="G466" t="n">
-        <v>7.32044696807861</v>
+        <v>7.32044744491577</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G467" t="n">
-        <v>7.36617708206177</v>
+        <v>7.36617660522461</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>8.54378509521484</v>
       </c>
       <c r="G471" t="n">
-        <v>8.39888954162598</v>
+        <v>8.39889049530029</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G472" t="n">
-        <v>8.19310855865479</v>
+        <v>8.1931095123291</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>8.24141883850098</v>
       </c>
       <c r="G474" t="n">
-        <v>8.10165119171143</v>
+        <v>8.10165214538574</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>8.21040725708008</v>
       </c>
       <c r="G475" t="n">
-        <v>8.07116603851318</v>
+        <v>8.07116508483887</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>8.38872623443604</v>
       </c>
       <c r="G478" t="n">
-        <v>8.24646091461182</v>
+        <v>8.2464599609375</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.87716293334961</v>
       </c>
       <c r="G480" t="n">
-        <v>8.72661304473877</v>
+        <v>8.72661399841309</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G484" t="n">
-        <v>8.88666534423828</v>
+        <v>8.8866662979126</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>9.04772853851318</v>
       </c>
       <c r="G485" t="n">
-        <v>8.894287109375</v>
+        <v>8.89428615570068</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>9.17177677154541</v>
       </c>
       <c r="G488" t="n">
-        <v>9.01623153686523</v>
+        <v>9.01623058319092</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G497" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G501" t="n">
-        <v>9.96129703521729</v>
+        <v>9.96129608154297</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>10.1796636581421</v>
       </c>
       <c r="G503" t="n">
-        <v>10.0070247650146</v>
+        <v>10.007025718689</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G506" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G507" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G510" t="n">
-        <v>9.79362297058105</v>
+        <v>9.79362392425537</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>9.70673179626465</v>
       </c>
       <c r="G511" t="n">
-        <v>9.54211330413818</v>
+        <v>9.5421142578125</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>10.1486520767212</v>
       </c>
       <c r="G513" t="n">
-        <v>9.97653961181641</v>
+        <v>9.97653865814209</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>10.5285491943359</v>
       </c>
       <c r="G515" t="n">
-        <v>10.3499937057495</v>
+        <v>10.3499946594238</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>11.2108106613159</v>
       </c>
       <c r="G519" t="n">
-        <v>11.0206851959229</v>
+        <v>11.0206842422485</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>11.265082359314</v>
       </c>
       <c r="G523" t="n">
-        <v>11.0740356445312</v>
+        <v>11.0740365982056</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>11.3658714294434</v>
       </c>
       <c r="G525" t="n">
-        <v>11.17311668396</v>
+        <v>11.1731157302856</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>11.3426122665405</v>
       </c>
       <c r="G526" t="n">
-        <v>11.1502504348755</v>
+        <v>11.1502513885498</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G528" t="n">
-        <v>10.8225259780884</v>
+        <v>10.8225269317627</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G534" t="n">
-        <v>10.8225259780884</v>
+        <v>10.8225269317627</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>10.4200067520142</v>
       </c>
       <c r="G540" t="n">
-        <v>10.2432918548584</v>
+        <v>10.2432928085327</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>10.5052900314331</v>
       </c>
       <c r="G541" t="n">
-        <v>10.3271284103394</v>
+        <v>10.3271293640137</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>10.4665250778198</v>
       </c>
       <c r="G545" t="n">
-        <v>10.2890214920044</v>
+        <v>10.2890224456787</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>10.3889951705933</v>
       </c>
       <c r="G549" t="n">
-        <v>10.2128067016602</v>
+        <v>10.2128057479858</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>9.9548282623291</v>
       </c>
       <c r="G551" t="n">
-        <v>9.78600215911865</v>
+        <v>9.78600311279297</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>9.59043788909912</v>
       </c>
       <c r="G555" t="n">
-        <v>9.4277925491333</v>
+        <v>9.42779159545898</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G561" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G563" t="n">
-        <v>9.79362297058105</v>
+        <v>9.79362392425537</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>10.1951704025269</v>
       </c>
       <c r="G568" t="n">
-        <v>10.0222682952881</v>
+        <v>10.0222692489624</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>11.0247392654419</v>
       </c>
       <c r="G572" t="n">
-        <v>10.8377685546875</v>
+        <v>10.8377695083618</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G577" t="n">
-        <v>8.88666534423828</v>
+        <v>8.8866662979126</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>9.11750602722168</v>
       </c>
       <c r="G580" t="n">
-        <v>8.96288013458252</v>
+        <v>8.96288108825684</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>9.45088386535645</v>
       </c>
       <c r="G581" t="n">
-        <v>9.29060554504395</v>
+        <v>9.29060459136963</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>9.83078002929688</v>
       </c>
       <c r="G588" t="n">
-        <v>9.66405868530273</v>
+        <v>9.66405773162842</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G594" t="n">
-        <v>9.96129703521729</v>
+        <v>9.96129608154297</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>10.7068672180176</v>
       </c>
       <c r="G598" t="n">
-        <v>10.5252876281738</v>
+        <v>10.5252885818481</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>10.4277601242065</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2509136199951</v>
+        <v>10.2509145736694</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>10.0090990066528</v>
       </c>
       <c r="G607" t="n">
-        <v>9.83935356140137</v>
+        <v>9.83935260772705</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -71664,6 +71664,32 @@
         <v>12.2700004577637</v>
       </c>
       <c r="H2742" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>1841068</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>12.2250003814697</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>11.8649997711182</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>12.0600004196167</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>12.1099996566772</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>12.1099996566772</v>
+      </c>
+      <c r="H2743" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -71693,6 +71693,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>1836528</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>12.5950002670288</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>12.1750001907349</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>12.1750001907349</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>12.5200004577637</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>12.5200004577637</v>
+      </c>
+      <c r="H2744" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.17872190475464</v>
       </c>
       <c r="G2" t="n">
-        <v>3.12481355667114</v>
+        <v>3.12481331825256</v>
       </c>
       <c r="H2" t="n">
         <v>493230</v>
@@ -630,7 +630,7 @@
         <v>2.59337210655212</v>
       </c>
       <c r="G9" t="n">
-        <v>2.54939079284668</v>
+        <v>2.5493905544281</v>
       </c>
       <c r="H9" t="n">
         <v>256430</v>
@@ -688,7 +688,7 @@
         <v>2.60422611236572</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56006050109863</v>
+        <v>2.56006073951721</v>
       </c>
       <c r="H11" t="n">
         <v>214063</v>
@@ -746,7 +746,7 @@
         <v>2.45769500732422</v>
       </c>
       <c r="G13" t="n">
-        <v>2.41601467132568</v>
+        <v>2.4160144329071</v>
       </c>
       <c r="H13" t="n">
         <v>205959</v>
@@ -891,7 +891,7 @@
         <v>2.76006102561951</v>
       </c>
       <c r="G18" t="n">
-        <v>2.71325254440308</v>
+        <v>2.71325278282166</v>
       </c>
       <c r="H18" t="n">
         <v>596593</v>
@@ -1036,7 +1036,7 @@
         <v>2.71354293823242</v>
       </c>
       <c r="G23" t="n">
-        <v>2.66752362251282</v>
+        <v>2.66752338409424</v>
       </c>
       <c r="H23" t="n">
         <v>131540</v>
@@ -1065,7 +1065,7 @@
         <v>2.56468605995178</v>
       </c>
       <c r="G24" t="n">
-        <v>2.52119112014771</v>
+        <v>2.52119135856628</v>
       </c>
       <c r="H24" t="n">
         <v>163658</v>
@@ -1123,7 +1123,7 @@
         <v>2.41272711753845</v>
       </c>
       <c r="G26" t="n">
-        <v>2.37180924415588</v>
+        <v>2.37180948257446</v>
       </c>
       <c r="H26" t="n">
         <v>144800</v>
@@ -1152,7 +1152,7 @@
         <v>2.25999402999878</v>
       </c>
       <c r="G27" t="n">
-        <v>2.22166633605957</v>
+        <v>2.22166657447815</v>
       </c>
       <c r="H27" t="n">
         <v>346665</v>
@@ -1181,7 +1181,7 @@
         <v>2.10880994796753</v>
       </c>
       <c r="G28" t="n">
-        <v>2.07304644584656</v>
+        <v>2.07304620742798</v>
       </c>
       <c r="H28" t="n">
         <v>423821</v>
@@ -1239,7 +1239,7 @@
         <v>2.0933051109314</v>
       </c>
       <c r="G30" t="n">
-        <v>2.05780458450317</v>
+        <v>2.05780434608459</v>
       </c>
       <c r="H30" t="n">
         <v>144475</v>
@@ -1326,7 +1326,7 @@
         <v>2.41040110588074</v>
       </c>
       <c r="G33" t="n">
-        <v>2.36952257156372</v>
+        <v>2.3695228099823</v>
       </c>
       <c r="H33" t="n">
         <v>205506</v>
@@ -1384,7 +1384,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G35" t="n">
-        <v>2.566157579422</v>
+        <v>2.56615734100342</v>
       </c>
       <c r="H35" t="n">
         <v>251553</v>
@@ -1413,7 +1413,7 @@
         <v>2.46389698982239</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42211127281189</v>
+        <v>2.42211151123047</v>
       </c>
       <c r="H36" t="n">
         <v>190917</v>
@@ -1442,7 +1442,7 @@
         <v>2.64066505432129</v>
       </c>
       <c r="G37" t="n">
-        <v>2.59588146209717</v>
+        <v>2.59588170051575</v>
       </c>
       <c r="H37" t="n">
         <v>246557</v>
@@ -1819,7 +1819,7 @@
         <v>2.45381808280945</v>
       </c>
       <c r="G50" t="n">
-        <v>2.41220355033875</v>
+        <v>2.41220331192017</v>
       </c>
       <c r="H50" t="n">
         <v>159744</v>
@@ -1935,7 +1935,7 @@
         <v>2.64841794967651</v>
       </c>
       <c r="G54" t="n">
-        <v>2.60350322723389</v>
+        <v>2.60350298881531</v>
       </c>
       <c r="H54" t="n">
         <v>485506</v>
@@ -1993,7 +1993,7 @@
         <v>2.73680210113525</v>
       </c>
       <c r="G56" t="n">
-        <v>2.69038820266724</v>
+        <v>2.69038844108582</v>
       </c>
       <c r="H56" t="n">
         <v>159844</v>
@@ -2109,7 +2109,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G60" t="n">
-        <v>2.566157579422</v>
+        <v>2.56615734100342</v>
       </c>
       <c r="H60" t="n">
         <v>103412</v>
@@ -2341,7 +2341,7 @@
         <v>2.97326803207397</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92284369468689</v>
+        <v>2.92284393310547</v>
       </c>
       <c r="H68" t="n">
         <v>318172</v>
@@ -2428,7 +2428,7 @@
         <v>2.87790608406067</v>
       </c>
       <c r="G71" t="n">
-        <v>2.82909941673279</v>
+        <v>2.82909917831421</v>
       </c>
       <c r="H71" t="n">
         <v>190823</v>
@@ -2457,7 +2457,7 @@
         <v>2.87480497360229</v>
       </c>
       <c r="G72" t="n">
-        <v>2.82605051994324</v>
+        <v>2.82605075836182</v>
       </c>
       <c r="H72" t="n">
         <v>241086</v>
@@ -2544,7 +2544,7 @@
         <v>2.81975889205933</v>
       </c>
       <c r="G75" t="n">
-        <v>2.77193832397461</v>
+        <v>2.77193808555603</v>
       </c>
       <c r="H75" t="n">
         <v>310240</v>
@@ -2573,7 +2573,7 @@
         <v>2.77634191513062</v>
       </c>
       <c r="G76" t="n">
-        <v>2.72925734519958</v>
+        <v>2.72925758361816</v>
       </c>
       <c r="H76" t="n">
         <v>301835</v>
@@ -2602,7 +2602,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G77" t="n">
-        <v>2.7330687046051</v>
+        <v>2.73306894302368</v>
       </c>
       <c r="H77" t="n">
         <v>155939</v>
@@ -2718,7 +2718,7 @@
         <v>2.79727506637573</v>
       </c>
       <c r="G81" t="n">
-        <v>2.74983549118042</v>
+        <v>2.749835729599</v>
       </c>
       <c r="H81" t="n">
         <v>168823</v>
@@ -2979,7 +2979,7 @@
         <v>2.5476291179657</v>
       </c>
       <c r="G90" t="n">
-        <v>2.50442337989807</v>
+        <v>2.50442361831665</v>
       </c>
       <c r="H90" t="n">
         <v>137592</v>
@@ -3095,7 +3095,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G94" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H94" t="n">
         <v>593089</v>
@@ -3153,7 +3153,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G96" t="n">
-        <v>2.7330687046051</v>
+        <v>2.73306894302368</v>
       </c>
       <c r="H96" t="n">
         <v>193495</v>
@@ -3182,7 +3182,7 @@
         <v>2.94070506095886</v>
       </c>
       <c r="G97" t="n">
-        <v>2.89083313941956</v>
+        <v>2.89083337783813</v>
       </c>
       <c r="H97" t="n">
         <v>678677</v>
@@ -3298,7 +3298,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G101" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H101" t="n">
         <v>97675</v>
@@ -3385,7 +3385,7 @@
         <v>2.9693911075592</v>
       </c>
       <c r="G104" t="n">
-        <v>2.91903257369995</v>
+        <v>2.91903281211853</v>
       </c>
       <c r="H104" t="n">
         <v>94349</v>
@@ -3414,7 +3414,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G105" t="n">
-        <v>2.88244962692261</v>
+        <v>2.88244986534119</v>
       </c>
       <c r="H105" t="n">
         <v>76056</v>
@@ -3443,7 +3443,7 @@
         <v>2.8934121131897</v>
       </c>
       <c r="G106" t="n">
-        <v>2.84434223175049</v>
+        <v>2.84434247016907</v>
       </c>
       <c r="H106" t="n">
         <v>160927</v>
@@ -3472,7 +3472,7 @@
         <v>2.94458198547363</v>
       </c>
       <c r="G107" t="n">
-        <v>2.89464426040649</v>
+        <v>2.89464449882507</v>
       </c>
       <c r="H107" t="n">
         <v>122794</v>
@@ -3530,7 +3530,7 @@
         <v>2.91201901435852</v>
       </c>
       <c r="G109" t="n">
-        <v>2.86263346672058</v>
+        <v>2.86263370513916</v>
       </c>
       <c r="H109" t="n">
         <v>97079</v>
@@ -3617,7 +3617,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G112" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H112" t="n">
         <v>87752</v>
@@ -3704,7 +3704,7 @@
         <v>2.64919304847717</v>
       </c>
       <c r="G115" t="n">
-        <v>2.60426497459412</v>
+        <v>2.6042652130127</v>
       </c>
       <c r="H115" t="n">
         <v>158384</v>
@@ -3849,7 +3849,7 @@
         <v>2.90581703186035</v>
       </c>
       <c r="G120" t="n">
-        <v>2.85653686523438</v>
+        <v>2.8565366268158</v>
       </c>
       <c r="H120" t="n">
         <v>140706</v>
@@ -3907,7 +3907,7 @@
         <v>2.80502796173096</v>
       </c>
       <c r="G122" t="n">
-        <v>2.75745701789856</v>
+        <v>2.75745725631714</v>
       </c>
       <c r="H122" t="n">
         <v>103410</v>
@@ -4110,7 +4110,7 @@
         <v>2.53057289123535</v>
       </c>
       <c r="G129" t="n">
-        <v>2.48765635490417</v>
+        <v>2.48765659332275</v>
       </c>
       <c r="H129" t="n">
         <v>122546</v>
@@ -4197,7 +4197,7 @@
         <v>2.43831205368042</v>
       </c>
       <c r="G132" t="n">
-        <v>2.39696049690247</v>
+        <v>2.39696025848389</v>
       </c>
       <c r="H132" t="n">
         <v>324481</v>
@@ -4255,7 +4255,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56082224845886</v>
+        <v>2.56082248687744</v>
       </c>
       <c r="H134" t="n">
         <v>116496</v>
@@ -4284,7 +4284,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56082224845886</v>
+        <v>2.56082248687744</v>
       </c>
       <c r="H135" t="n">
         <v>77002</v>
@@ -4371,7 +4371,7 @@
         <v>2.7057900428772</v>
       </c>
       <c r="G138" t="n">
-        <v>2.65990233421326</v>
+        <v>2.65990209579468</v>
       </c>
       <c r="H138" t="n">
         <v>227795</v>
@@ -4516,7 +4516,7 @@
         <v>2.89186191558838</v>
       </c>
       <c r="G143" t="n">
-        <v>2.84281826019287</v>
+        <v>2.84281849861145</v>
       </c>
       <c r="H143" t="n">
         <v>433122</v>
@@ -4545,7 +4545,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G144" t="n">
-        <v>2.88244962692261</v>
+        <v>2.88244986534119</v>
       </c>
       <c r="H144" t="n">
         <v>504151</v>
@@ -4632,7 +4632,7 @@
         <v>2.95310997962952</v>
       </c>
       <c r="G147" t="n">
-        <v>2.90302753448486</v>
+        <v>2.90302777290344</v>
       </c>
       <c r="H147" t="n">
         <v>124606</v>
@@ -4661,7 +4661,7 @@
         <v>2.9918749332428</v>
       </c>
       <c r="G148" t="n">
-        <v>2.94113516807556</v>
+        <v>2.94113540649414</v>
       </c>
       <c r="H148" t="n">
         <v>115180</v>
@@ -4719,7 +4719,7 @@
         <v>2.96551489830017</v>
       </c>
       <c r="G150" t="n">
-        <v>2.91522216796875</v>
+        <v>2.91522240638733</v>
       </c>
       <c r="H150" t="n">
         <v>107908</v>
@@ -4748,7 +4748,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H151" t="n">
         <v>112608</v>
@@ -4835,7 +4835,7 @@
         <v>2.93527793884277</v>
       </c>
       <c r="G154" t="n">
-        <v>2.88549828529358</v>
+        <v>2.885498046875</v>
       </c>
       <c r="H154" t="n">
         <v>98584</v>
@@ -4922,7 +4922,7 @@
         <v>2.95388507843018</v>
       </c>
       <c r="G157" t="n">
-        <v>2.90378975868225</v>
+        <v>2.90378952026367</v>
       </c>
       <c r="H157" t="n">
         <v>130813</v>
@@ -4980,7 +4980,7 @@
         <v>3.05855107307434</v>
       </c>
       <c r="G159" t="n">
-        <v>3.006680727005</v>
+        <v>3.00668048858643</v>
       </c>
       <c r="H159" t="n">
         <v>293073</v>
@@ -5009,7 +5009,7 @@
         <v>3.0221118927002</v>
       </c>
       <c r="G160" t="n">
-        <v>2.97085952758789</v>
+        <v>2.97085928916931</v>
       </c>
       <c r="H160" t="n">
         <v>76130</v>
@@ -5067,7 +5067,7 @@
         <v>2.97404289245605</v>
       </c>
       <c r="G162" t="n">
-        <v>2.9236056804657</v>
+        <v>2.92360544204712</v>
       </c>
       <c r="H162" t="n">
         <v>29083</v>
@@ -5125,7 +5125,7 @@
         <v>3.02676391601562</v>
       </c>
       <c r="G164" t="n">
-        <v>2.97543239593506</v>
+        <v>2.97543263435364</v>
       </c>
       <c r="H164" t="n">
         <v>68786</v>
@@ -5444,7 +5444,7 @@
         <v>3.35936594009399</v>
       </c>
       <c r="G175" t="n">
-        <v>3.30239415168762</v>
+        <v>3.30239391326904</v>
       </c>
       <c r="H175" t="n">
         <v>136675</v>
@@ -5531,7 +5531,7 @@
         <v>3.38262510299683</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32525873184204</v>
+        <v>3.32525849342346</v>
       </c>
       <c r="H178" t="n">
         <v>282670</v>
@@ -5560,7 +5560,7 @@
         <v>3.31750011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>3.26123809814453</v>
+        <v>3.26123833656311</v>
       </c>
       <c r="H179" t="n">
         <v>124150</v>
@@ -5647,7 +5647,7 @@
         <v>3.23764491081238</v>
       </c>
       <c r="G182" t="n">
-        <v>3.18273711204529</v>
+        <v>3.18273735046387</v>
       </c>
       <c r="H182" t="n">
         <v>146776</v>
@@ -5705,7 +5705,7 @@
         <v>3.20430707931519</v>
       </c>
       <c r="G184" t="n">
-        <v>3.14996457099915</v>
+        <v>3.14996480941772</v>
       </c>
       <c r="H184" t="n">
         <v>75785</v>
@@ -5821,7 +5821,7 @@
         <v>3.35083794593811</v>
       </c>
       <c r="G188" t="n">
-        <v>3.29401063919067</v>
+        <v>3.29401040077209</v>
       </c>
       <c r="H188" t="n">
         <v>126105</v>
@@ -5937,7 +5937,7 @@
         <v>3.35548996925354</v>
       </c>
       <c r="G192" t="n">
-        <v>3.29858350753784</v>
+        <v>3.29858374595642</v>
       </c>
       <c r="H192" t="n">
         <v>204931</v>
@@ -6082,7 +6082,7 @@
         <v>3.3570408821106</v>
       </c>
       <c r="G197" t="n">
-        <v>3.3001081943512</v>
+        <v>3.30010843276978</v>
       </c>
       <c r="H197" t="n">
         <v>92448</v>
@@ -6140,7 +6140,7 @@
         <v>3.33067989349365</v>
       </c>
       <c r="G199" t="n">
-        <v>3.27419447898865</v>
+        <v>3.27419424057007</v>
       </c>
       <c r="H199" t="n">
         <v>109612</v>
@@ -6169,7 +6169,7 @@
         <v>3.35238909721375</v>
       </c>
       <c r="G200" t="n">
-        <v>3.29553532600403</v>
+        <v>3.29553556442261</v>
       </c>
       <c r="H200" t="n">
         <v>72532</v>
@@ -6343,7 +6343,7 @@
         <v>3.34308505058289</v>
       </c>
       <c r="G206" t="n">
-        <v>3.28638935089111</v>
+        <v>3.28638911247253</v>
       </c>
       <c r="H206" t="n">
         <v>211723</v>
@@ -6575,7 +6575,7 @@
         <v>3.19965505599976</v>
       </c>
       <c r="G214" t="n">
-        <v>3.1453914642334</v>
+        <v>3.14539170265198</v>
       </c>
       <c r="H214" t="n">
         <v>46695</v>
@@ -6604,7 +6604,7 @@
         <v>3.20353198051453</v>
       </c>
       <c r="G215" t="n">
-        <v>3.14920258522034</v>
+        <v>3.14920282363892</v>
       </c>
       <c r="H215" t="n">
         <v>20449</v>
@@ -6720,7 +6720,7 @@
         <v>3.04226899147034</v>
       </c>
       <c r="G219" t="n">
-        <v>2.9906747341156</v>
+        <v>2.99067449569702</v>
       </c>
       <c r="H219" t="n">
         <v>119131</v>
@@ -6778,7 +6778,7 @@
         <v>3.23299288749695</v>
       </c>
       <c r="G221" t="n">
-        <v>3.17816400527954</v>
+        <v>3.17816424369812</v>
       </c>
       <c r="H221" t="n">
         <v>190310</v>
@@ -6807,7 +6807,7 @@
         <v>3.24384689331055</v>
       </c>
       <c r="G222" t="n">
-        <v>3.18883419036865</v>
+        <v>3.18883395195007</v>
       </c>
       <c r="H222" t="n">
         <v>201688</v>
@@ -6836,7 +6836,7 @@
         <v>3.37254691123962</v>
       </c>
       <c r="G223" t="n">
-        <v>3.31535124778748</v>
+        <v>3.31535148620605</v>
       </c>
       <c r="H223" t="n">
         <v>480056</v>
@@ -7010,7 +7010,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G229" t="n">
-        <v>3.1934072971344</v>
+        <v>3.19340705871582</v>
       </c>
       <c r="H229" t="n">
         <v>91423</v>
@@ -7068,7 +7068,7 @@
         <v>3.24617290496826</v>
       </c>
       <c r="G231" t="n">
-        <v>3.19112062454224</v>
+        <v>3.19112038612366</v>
       </c>
       <c r="H231" t="n">
         <v>60078</v>
@@ -7097,7 +7097,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G232" t="n">
-        <v>3.18197441101074</v>
+        <v>3.18197464942932</v>
       </c>
       <c r="H232" t="n">
         <v>46953</v>
@@ -7213,7 +7213,7 @@
         <v>3.22601509094238</v>
       </c>
       <c r="G236" t="n">
-        <v>3.17130470275879</v>
+        <v>3.17130446434021</v>
       </c>
       <c r="H236" t="n">
         <v>92031</v>
@@ -7242,7 +7242,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G237" t="n">
-        <v>3.1934072971344</v>
+        <v>3.19340705871582</v>
       </c>
       <c r="H237" t="n">
         <v>65003</v>
@@ -7329,7 +7329,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G240" t="n">
-        <v>3.18197441101074</v>
+        <v>3.18197464942932</v>
       </c>
       <c r="H240" t="n">
         <v>117377</v>
@@ -7503,7 +7503,7 @@
         <v>3.26167893409729</v>
       </c>
       <c r="G246" t="n">
-        <v>3.20636343955994</v>
+        <v>3.20636367797852</v>
       </c>
       <c r="H246" t="n">
         <v>207240</v>
@@ -7532,7 +7532,7 @@
         <v>3.32602906227112</v>
       </c>
       <c r="G247" t="n">
-        <v>3.2696225643158</v>
+        <v>3.26962232589722</v>
       </c>
       <c r="H247" t="n">
         <v>91899</v>
@@ -7677,7 +7677,7 @@
         <v>3.5446629524231</v>
       </c>
       <c r="G252" t="n">
-        <v>3.48454833030701</v>
+        <v>3.48454856872559</v>
       </c>
       <c r="H252" t="n">
         <v>194782</v>
@@ -7851,7 +7851,7 @@
         <v>3.721431016922</v>
       </c>
       <c r="G258" t="n">
-        <v>3.65831851959229</v>
+        <v>3.65831875801086</v>
       </c>
       <c r="H258" t="n">
         <v>319621</v>
@@ -7909,7 +7909,7 @@
         <v>4.00053787231445</v>
       </c>
       <c r="G260" t="n">
-        <v>3.93269228935242</v>
+        <v>3.93269205093384</v>
       </c>
       <c r="H260" t="n">
         <v>648070</v>
@@ -8083,7 +8083,7 @@
         <v>4.05093193054199</v>
       </c>
       <c r="G266" t="n">
-        <v>3.98223161697388</v>
+        <v>3.9822313785553</v>
       </c>
       <c r="H266" t="n">
         <v>236555</v>
@@ -8257,7 +8257,7 @@
         <v>4.18661022186279</v>
       </c>
       <c r="G272" t="n">
-        <v>4.11560916900635</v>
+        <v>4.11560869216919</v>
       </c>
       <c r="H272" t="n">
         <v>1412380</v>
@@ -8286,7 +8286,7 @@
         <v>4.27964496612549</v>
       </c>
       <c r="G273" t="n">
-        <v>4.20706558227539</v>
+        <v>4.20706605911255</v>
       </c>
       <c r="H273" t="n">
         <v>1069890</v>
@@ -8315,7 +8315,7 @@
         <v>4.43858098983765</v>
       </c>
       <c r="G274" t="n">
-        <v>4.36330604553223</v>
+        <v>4.36330652236938</v>
       </c>
       <c r="H274" t="n">
         <v>723596</v>
@@ -8344,7 +8344,7 @@
         <v>4.442458152771</v>
       </c>
       <c r="G275" t="n">
-        <v>4.36711740493774</v>
+        <v>4.3671178817749</v>
       </c>
       <c r="H275" t="n">
         <v>567984</v>
@@ -8402,7 +8402,7 @@
         <v>4.3610520362854</v>
       </c>
       <c r="G277" t="n">
-        <v>4.2870922088623</v>
+        <v>4.28709268569946</v>
       </c>
       <c r="H277" t="n">
         <v>208145</v>
@@ -8431,7 +8431,7 @@
         <v>4.25251007080078</v>
       </c>
       <c r="G278" t="n">
-        <v>4.18039083480835</v>
+        <v>4.18039131164551</v>
       </c>
       <c r="H278" t="n">
         <v>280129</v>
@@ -8547,7 +8547,7 @@
         <v>4.33779287338257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.26422786712646</v>
+        <v>4.26422739028931</v>
       </c>
       <c r="H282" t="n">
         <v>221629</v>
@@ -8605,7 +8605,7 @@
         <v>4.27189207077026</v>
       </c>
       <c r="G284" t="n">
-        <v>4.19944429397583</v>
+        <v>4.19944477081299</v>
       </c>
       <c r="H284" t="n">
         <v>219679</v>
@@ -8721,7 +8721,7 @@
         <v>4.12846183776855</v>
       </c>
       <c r="G288" t="n">
-        <v>4.05844640731812</v>
+        <v>4.05844688415527</v>
       </c>
       <c r="H288" t="n">
         <v>181443</v>
@@ -8808,7 +8808,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G291" t="n">
-        <v>4.52716970443726</v>
+        <v>4.5271692276001</v>
       </c>
       <c r="H291" t="n">
         <v>1365540</v>
@@ -8866,7 +8866,7 @@
         <v>4.52386379241943</v>
       </c>
       <c r="G293" t="n">
-        <v>4.44714307785034</v>
+        <v>4.44714260101318</v>
       </c>
       <c r="H293" t="n">
         <v>403894</v>
@@ -8982,7 +8982,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G297" t="n">
-        <v>4.52716970443726</v>
+        <v>4.5271692276001</v>
       </c>
       <c r="H297" t="n">
         <v>367010</v>
@@ -9040,7 +9040,7 @@
         <v>4.64403486251831</v>
       </c>
       <c r="G299" t="n">
-        <v>4.56527614593506</v>
+        <v>4.5652756690979</v>
       </c>
       <c r="H299" t="n">
         <v>165971</v>
@@ -9098,7 +9098,7 @@
         <v>4.88437795639038</v>
       </c>
       <c r="G301" t="n">
-        <v>4.80154323577881</v>
+        <v>4.80154275894165</v>
       </c>
       <c r="H301" t="n">
         <v>885013</v>
@@ -9127,7 +9127,7 @@
         <v>5.09758520126343</v>
       </c>
       <c r="G302" t="n">
-        <v>5.01113414764404</v>
+        <v>5.0111346244812</v>
       </c>
       <c r="H302" t="n">
         <v>1328330</v>
@@ -9388,7 +9388,7 @@
         <v>5.02780818939209</v>
       </c>
       <c r="G311" t="n">
-        <v>4.94254112243652</v>
+        <v>4.94254064559937</v>
       </c>
       <c r="H311" t="n">
         <v>342293</v>
@@ -9446,7 +9446,7 @@
         <v>5.06657314300537</v>
       </c>
       <c r="G313" t="n">
-        <v>4.98064851760864</v>
+        <v>4.98064804077148</v>
       </c>
       <c r="H313" t="n">
         <v>238791</v>
@@ -9533,7 +9533,7 @@
         <v>5.11309099197388</v>
       </c>
       <c r="G316" t="n">
-        <v>5.02637720108032</v>
+        <v>5.02637767791748</v>
       </c>
       <c r="H316" t="n">
         <v>297516</v>
@@ -9562,7 +9562,7 @@
         <v>5.19449710845947</v>
       </c>
       <c r="G317" t="n">
-        <v>5.10640287399292</v>
+        <v>5.10640239715576</v>
       </c>
       <c r="H317" t="n">
         <v>464423</v>
@@ -9649,7 +9649,7 @@
         <v>5.21388006210327</v>
       </c>
       <c r="G320" t="n">
-        <v>5.12545680999756</v>
+        <v>5.12545728683472</v>
       </c>
       <c r="H320" t="n">
         <v>546852</v>
@@ -9707,7 +9707,7 @@
         <v>5.48523378372192</v>
       </c>
       <c r="G322" t="n">
-        <v>5.39220905303955</v>
+        <v>5.39220857620239</v>
       </c>
       <c r="H322" t="n">
         <v>940314</v>
@@ -9823,7 +9823,7 @@
         <v>6.08609008789062</v>
       </c>
       <c r="G326" t="n">
-        <v>5.98287534713745</v>
+        <v>5.98287487030029</v>
       </c>
       <c r="H326" t="n">
         <v>1806086</v>
@@ -9881,7 +9881,7 @@
         <v>6.11710214614868</v>
       </c>
       <c r="G328" t="n">
-        <v>6.01336145401001</v>
+        <v>6.01336097717285</v>
       </c>
       <c r="H328" t="n">
         <v>1777020</v>
@@ -10026,7 +10026,7 @@
         <v>6.20238494873047</v>
       </c>
       <c r="G333" t="n">
-        <v>6.09719753265381</v>
+        <v>6.09719800949097</v>
       </c>
       <c r="H333" t="n">
         <v>1738052</v>
@@ -10171,7 +10171,7 @@
         <v>7.13661909103394</v>
       </c>
       <c r="G338" t="n">
-        <v>7.01558780670166</v>
+        <v>7.01558828353882</v>
       </c>
       <c r="H338" t="n">
         <v>2024444</v>
@@ -10200,7 +10200,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G339" t="n">
-        <v>6.72216033935547</v>
+        <v>6.72215986251831</v>
       </c>
       <c r="H339" t="n">
         <v>1597497</v>
@@ -10316,7 +10316,7 @@
         <v>7.07847213745117</v>
       </c>
       <c r="G343" t="n">
-        <v>6.95842742919922</v>
+        <v>6.95842695236206</v>
       </c>
       <c r="H343" t="n">
         <v>1152592</v>
@@ -10345,7 +10345,7 @@
         <v>7.02420091629028</v>
       </c>
       <c r="G344" t="n">
-        <v>6.9050760269165</v>
+        <v>6.90507650375366</v>
       </c>
       <c r="H344" t="n">
         <v>757764</v>
@@ -10403,7 +10403,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G346" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H346" t="n">
         <v>1253565</v>
@@ -10432,7 +10432,7 @@
         <v>7.40797281265259</v>
       </c>
       <c r="G347" t="n">
-        <v>7.28233957290649</v>
+        <v>7.28234004974365</v>
       </c>
       <c r="H347" t="n">
         <v>953069</v>
@@ -10577,7 +10577,7 @@
         <v>6.38845586776733</v>
       </c>
       <c r="G352" t="n">
-        <v>6.28011322021484</v>
+        <v>6.28011274337769</v>
       </c>
       <c r="H352" t="n">
         <v>1189739</v>
@@ -10751,7 +10751,7 @@
         <v>7.03583002090454</v>
       </c>
       <c r="G358" t="n">
-        <v>6.91650819778442</v>
+        <v>6.91650867462158</v>
       </c>
       <c r="H358" t="n">
         <v>557993</v>
@@ -10809,7 +10809,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G360" t="n">
-        <v>6.72216033935547</v>
+        <v>6.72215986251831</v>
       </c>
       <c r="H360" t="n">
         <v>383136</v>
@@ -11070,7 +11070,7 @@
         <v>6.86526489257812</v>
       </c>
       <c r="G369" t="n">
-        <v>6.74883556365967</v>
+        <v>6.74883604049683</v>
       </c>
       <c r="H369" t="n">
         <v>381623</v>
@@ -11099,7 +11099,7 @@
         <v>6.77222919464111</v>
       </c>
       <c r="G370" t="n">
-        <v>6.65737819671631</v>
+        <v>6.65737771987915</v>
       </c>
       <c r="H370" t="n">
         <v>410334</v>
@@ -11157,7 +11157,7 @@
         <v>6.76835203170776</v>
       </c>
       <c r="G372" t="n">
-        <v>6.65356683731079</v>
+        <v>6.65356636047363</v>
       </c>
       <c r="H372" t="n">
         <v>220177</v>
@@ -11447,7 +11447,7 @@
         <v>7.37308502197266</v>
       </c>
       <c r="G382" t="n">
-        <v>7.24804401397705</v>
+        <v>7.24804353713989</v>
       </c>
       <c r="H382" t="n">
         <v>2466801</v>
@@ -11563,7 +11563,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G386" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H386" t="n">
         <v>674582</v>
@@ -11679,7 +11679,7 @@
         <v>7.72972202301025</v>
       </c>
       <c r="G390" t="n">
-        <v>7.5986328125</v>
+        <v>7.59863233566284</v>
       </c>
       <c r="H390" t="n">
         <v>446172</v>
@@ -11737,7 +11737,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G392" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H392" t="n">
         <v>528987</v>
@@ -11795,7 +11795,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G394" t="n">
-        <v>8.19310855865479</v>
+        <v>8.1931095123291</v>
       </c>
       <c r="H394" t="n">
         <v>618520</v>
@@ -11824,7 +11824,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G395" t="n">
-        <v>8.3607816696167</v>
+        <v>8.36078262329102</v>
       </c>
       <c r="H395" t="n">
         <v>589330</v>
@@ -11911,7 +11911,7 @@
         <v>8.0708532333374</v>
       </c>
       <c r="G398" t="n">
-        <v>7.93397903442383</v>
+        <v>7.93397808074951</v>
       </c>
       <c r="H398" t="n">
         <v>1105464</v>
@@ -11940,7 +11940,7 @@
         <v>8.03208827972412</v>
       </c>
       <c r="G399" t="n">
-        <v>7.89587116241455</v>
+        <v>7.89587068557739</v>
       </c>
       <c r="H399" t="n">
         <v>704166</v>
@@ -12027,7 +12027,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G402" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H402" t="n">
         <v>4317226</v>
@@ -12230,7 +12230,7 @@
         <v>7.67545080184937</v>
       </c>
       <c r="G409" t="n">
-        <v>7.54528141021729</v>
+        <v>7.54528188705444</v>
       </c>
       <c r="H409" t="n">
         <v>485472</v>
@@ -12317,7 +12317,7 @@
         <v>7.30718517303467</v>
       </c>
       <c r="G412" t="n">
-        <v>7.18326139450073</v>
+        <v>7.18326187133789</v>
       </c>
       <c r="H412" t="n">
         <v>778353</v>
@@ -12462,7 +12462,7 @@
         <v>7.07071876525879</v>
       </c>
       <c r="G417" t="n">
-        <v>6.9508056640625</v>
+        <v>6.95080518722534</v>
       </c>
       <c r="H417" t="n">
         <v>221650</v>
@@ -12520,7 +12520,7 @@
         <v>6.985435962677</v>
       </c>
       <c r="G419" t="n">
-        <v>6.86696863174438</v>
+        <v>6.86696910858154</v>
       </c>
       <c r="H419" t="n">
         <v>607996</v>
@@ -12607,7 +12607,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G422" t="n">
-        <v>7.27852964401245</v>
+        <v>7.27853012084961</v>
       </c>
       <c r="H422" t="n">
         <v>880611</v>
@@ -12723,7 +12723,7 @@
         <v>7.17925977706909</v>
       </c>
       <c r="G426" t="n">
-        <v>7.05750608444214</v>
+        <v>7.05750560760498</v>
       </c>
       <c r="H426" t="n">
         <v>1555624</v>
@@ -12752,7 +12752,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G427" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H427" t="n">
         <v>1335622</v>
@@ -12868,7 +12868,7 @@
         <v>8.00107669830322</v>
       </c>
       <c r="G431" t="n">
-        <v>7.86538553237915</v>
+        <v>7.86538505554199</v>
       </c>
       <c r="H431" t="n">
         <v>781944</v>
@@ -12926,7 +12926,7 @@
         <v>7.7142162322998</v>
       </c>
       <c r="G433" t="n">
-        <v>7.58338928222656</v>
+        <v>7.58338975906372</v>
       </c>
       <c r="H433" t="n">
         <v>526446</v>
@@ -12955,7 +12955,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G434" t="n">
-        <v>7.94922161102295</v>
+        <v>7.94922113418579</v>
       </c>
       <c r="H434" t="n">
         <v>1316387</v>
@@ -13071,7 +13071,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G438" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H438" t="n">
         <v>447832</v>
@@ -13129,7 +13129,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G440" t="n">
-        <v>7.94922161102295</v>
+        <v>7.94922113418579</v>
       </c>
       <c r="H440" t="n">
         <v>478643</v>
@@ -13158,7 +13158,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G441" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H441" t="n">
         <v>375921</v>
@@ -13303,7 +13303,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G446" t="n">
-        <v>8.3607816696167</v>
+        <v>8.36078262329102</v>
       </c>
       <c r="H446" t="n">
         <v>2904190</v>
@@ -13332,7 +13332,7 @@
         <v>8.06309986114502</v>
       </c>
       <c r="G447" t="n">
-        <v>7.92635583877563</v>
+        <v>7.92635631561279</v>
       </c>
       <c r="H447" t="n">
         <v>4805532</v>
@@ -13448,7 +13448,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G451" t="n">
-        <v>7.36617708206177</v>
+        <v>7.36617660522461</v>
       </c>
       <c r="H451" t="n">
         <v>1207097</v>
@@ -13477,7 +13477,7 @@
         <v>7.58629179000854</v>
       </c>
       <c r="G452" t="n">
-        <v>7.45763444900513</v>
+        <v>7.45763492584229</v>
       </c>
       <c r="H452" t="n">
         <v>1486373</v>
@@ -13564,7 +13564,7 @@
         <v>7.51651477813721</v>
       </c>
       <c r="G455" t="n">
-        <v>7.38904094696045</v>
+        <v>7.38904142379761</v>
       </c>
       <c r="H455" t="n">
         <v>957250</v>
@@ -13680,7 +13680,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G459" t="n">
-        <v>7.31663703918457</v>
+        <v>7.31663751602173</v>
       </c>
       <c r="H459" t="n">
         <v>430589</v>
@@ -13709,7 +13709,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G460" t="n">
-        <v>7.27852964401245</v>
+        <v>7.27853012084961</v>
       </c>
       <c r="H460" t="n">
         <v>425428</v>
@@ -13796,7 +13796,7 @@
         <v>7.50100898742676</v>
       </c>
       <c r="G463" t="n">
-        <v>7.37379837036133</v>
+        <v>7.37379789352417</v>
       </c>
       <c r="H463" t="n">
         <v>490050</v>
@@ -13825,7 +13825,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G464" t="n">
-        <v>7.31663703918457</v>
+        <v>7.31663751602173</v>
       </c>
       <c r="H464" t="n">
         <v>447048</v>
@@ -13883,7 +13883,7 @@
         <v>7.44673776626587</v>
       </c>
       <c r="G466" t="n">
-        <v>7.32044696807861</v>
+        <v>7.32044744491577</v>
       </c>
       <c r="H466" t="n">
         <v>650810</v>
@@ -13912,7 +13912,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G467" t="n">
-        <v>7.36617708206177</v>
+        <v>7.36617660522461</v>
       </c>
       <c r="H467" t="n">
         <v>504330</v>
@@ -14028,7 +14028,7 @@
         <v>8.54378509521484</v>
       </c>
       <c r="G471" t="n">
-        <v>8.39888954162598</v>
+        <v>8.39889049530029</v>
       </c>
       <c r="H471" t="n">
         <v>1645276</v>
@@ -14057,7 +14057,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G472" t="n">
-        <v>8.19310855865479</v>
+        <v>8.1931095123291</v>
       </c>
       <c r="H472" t="n">
         <v>1740272</v>
@@ -14115,7 +14115,7 @@
         <v>8.24141883850098</v>
       </c>
       <c r="G474" t="n">
-        <v>8.10165119171143</v>
+        <v>8.10165214538574</v>
       </c>
       <c r="H474" t="n">
         <v>648959</v>
@@ -14144,7 +14144,7 @@
         <v>8.21040725708008</v>
       </c>
       <c r="G475" t="n">
-        <v>8.07116603851318</v>
+        <v>8.07116508483887</v>
       </c>
       <c r="H475" t="n">
         <v>437746</v>
@@ -14231,7 +14231,7 @@
         <v>8.38872623443604</v>
       </c>
       <c r="G478" t="n">
-        <v>8.24646091461182</v>
+        <v>8.2464599609375</v>
       </c>
       <c r="H478" t="n">
         <v>2636241</v>
@@ -14289,7 +14289,7 @@
         <v>8.87716293334961</v>
       </c>
       <c r="G480" t="n">
-        <v>8.72661304473877</v>
+        <v>8.72661399841309</v>
       </c>
       <c r="H480" t="n">
         <v>2854751</v>
@@ -14405,7 +14405,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G484" t="n">
-        <v>8.88666534423828</v>
+        <v>8.8866662979126</v>
       </c>
       <c r="H484" t="n">
         <v>943241</v>
@@ -14434,7 +14434,7 @@
         <v>9.04772853851318</v>
       </c>
       <c r="G485" t="n">
-        <v>8.894287109375</v>
+        <v>8.89428615570068</v>
       </c>
       <c r="H485" t="n">
         <v>875881</v>
@@ -14521,7 +14521,7 @@
         <v>9.17177677154541</v>
       </c>
       <c r="G488" t="n">
-        <v>9.01623153686523</v>
+        <v>9.01623058319092</v>
       </c>
       <c r="H488" t="n">
         <v>886825</v>
@@ -14782,7 +14782,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G497" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H497" t="n">
         <v>1414410</v>
@@ -14898,7 +14898,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G501" t="n">
-        <v>9.96129703521729</v>
+        <v>9.96129608154297</v>
       </c>
       <c r="H501" t="n">
         <v>845538</v>
@@ -14956,7 +14956,7 @@
         <v>10.1796636581421</v>
       </c>
       <c r="G503" t="n">
-        <v>10.0070247650146</v>
+        <v>10.007025718689</v>
       </c>
       <c r="H503" t="n">
         <v>832310</v>
@@ -15043,7 +15043,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G506" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H506" t="n">
         <v>913020</v>
@@ -15072,7 +15072,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G507" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H507" t="n">
         <v>366112</v>
@@ -15159,7 +15159,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G510" t="n">
-        <v>9.79362297058105</v>
+        <v>9.79362392425537</v>
       </c>
       <c r="H510" t="n">
         <v>238182</v>
@@ -15188,7 +15188,7 @@
         <v>9.70673179626465</v>
       </c>
       <c r="G511" t="n">
-        <v>9.54211330413818</v>
+        <v>9.5421142578125</v>
       </c>
       <c r="H511" t="n">
         <v>455430</v>
@@ -15246,7 +15246,7 @@
         <v>10.1486520767212</v>
       </c>
       <c r="G513" t="n">
-        <v>9.97653961181641</v>
+        <v>9.97653865814209</v>
       </c>
       <c r="H513" t="n">
         <v>442390</v>
@@ -15304,7 +15304,7 @@
         <v>10.5285491943359</v>
       </c>
       <c r="G515" t="n">
-        <v>10.3499937057495</v>
+        <v>10.3499946594238</v>
       </c>
       <c r="H515" t="n">
         <v>969702</v>
@@ -15420,7 +15420,7 @@
         <v>11.2108106613159</v>
       </c>
       <c r="G519" t="n">
-        <v>11.0206851959229</v>
+        <v>11.0206842422485</v>
       </c>
       <c r="H519" t="n">
         <v>1860164</v>
@@ -15536,7 +15536,7 @@
         <v>11.265082359314</v>
       </c>
       <c r="G523" t="n">
-        <v>11.0740356445312</v>
+        <v>11.0740365982056</v>
       </c>
       <c r="H523" t="n">
         <v>1216725</v>
@@ -15594,7 +15594,7 @@
         <v>11.3658714294434</v>
       </c>
       <c r="G525" t="n">
-        <v>11.17311668396</v>
+        <v>11.1731157302856</v>
       </c>
       <c r="H525" t="n">
         <v>686072</v>
@@ -15623,7 +15623,7 @@
         <v>11.3426122665405</v>
       </c>
       <c r="G526" t="n">
-        <v>11.1502504348755</v>
+        <v>11.1502513885498</v>
       </c>
       <c r="H526" t="n">
         <v>701379</v>
@@ -15681,7 +15681,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G528" t="n">
-        <v>10.8225259780884</v>
+        <v>10.8225269317627</v>
       </c>
       <c r="H528" t="n">
         <v>764225</v>
@@ -15855,7 +15855,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G534" t="n">
-        <v>10.8225259780884</v>
+        <v>10.8225269317627</v>
       </c>
       <c r="H534" t="n">
         <v>1206401</v>
@@ -16029,7 +16029,7 @@
         <v>10.4200067520142</v>
       </c>
       <c r="G540" t="n">
-        <v>10.2432918548584</v>
+        <v>10.2432928085327</v>
       </c>
       <c r="H540" t="n">
         <v>1215961</v>
@@ -16058,7 +16058,7 @@
         <v>10.5052900314331</v>
       </c>
       <c r="G541" t="n">
-        <v>10.3271284103394</v>
+        <v>10.3271293640137</v>
       </c>
       <c r="H541" t="n">
         <v>891258</v>
@@ -16174,7 +16174,7 @@
         <v>10.4665250778198</v>
       </c>
       <c r="G545" t="n">
-        <v>10.2890214920044</v>
+        <v>10.2890224456787</v>
       </c>
       <c r="H545" t="n">
         <v>418757</v>
@@ -16290,7 +16290,7 @@
         <v>10.3889951705933</v>
       </c>
       <c r="G549" t="n">
-        <v>10.2128067016602</v>
+        <v>10.2128057479858</v>
       </c>
       <c r="H549" t="n">
         <v>499673</v>
@@ -16348,7 +16348,7 @@
         <v>9.9548282623291</v>
       </c>
       <c r="G551" t="n">
-        <v>9.78600215911865</v>
+        <v>9.78600311279297</v>
       </c>
       <c r="H551" t="n">
         <v>665775</v>
@@ -16464,7 +16464,7 @@
         <v>9.59043788909912</v>
       </c>
       <c r="G555" t="n">
-        <v>9.4277925491333</v>
+        <v>9.42779159545898</v>
       </c>
       <c r="H555" t="n">
         <v>595699</v>
@@ -16638,7 +16638,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G561" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H561" t="n">
         <v>502777</v>
@@ -16696,7 +16696,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G563" t="n">
-        <v>9.79362297058105</v>
+        <v>9.79362392425537</v>
       </c>
       <c r="H563" t="n">
         <v>395215</v>
@@ -16841,7 +16841,7 @@
         <v>10.1951704025269</v>
       </c>
       <c r="G568" t="n">
-        <v>10.0222682952881</v>
+        <v>10.0222692489624</v>
       </c>
       <c r="H568" t="n">
         <v>554786</v>
@@ -16957,7 +16957,7 @@
         <v>11.0247392654419</v>
       </c>
       <c r="G572" t="n">
-        <v>10.8377685546875</v>
+        <v>10.8377695083618</v>
       </c>
       <c r="H572" t="n">
         <v>977445</v>
@@ -17102,7 +17102,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G577" t="n">
-        <v>8.88666534423828</v>
+        <v>8.8866662979126</v>
       </c>
       <c r="H577" t="n">
         <v>1985248</v>
@@ -17189,7 +17189,7 @@
         <v>9.11750602722168</v>
       </c>
       <c r="G580" t="n">
-        <v>8.96288013458252</v>
+        <v>8.96288108825684</v>
       </c>
       <c r="H580" t="n">
         <v>887045</v>
@@ -17218,7 +17218,7 @@
         <v>9.45088386535645</v>
       </c>
       <c r="G581" t="n">
-        <v>9.29060554504395</v>
+        <v>9.29060459136963</v>
       </c>
       <c r="H581" t="n">
         <v>2141921</v>
@@ -17421,7 +17421,7 @@
         <v>9.83078002929688</v>
       </c>
       <c r="G588" t="n">
-        <v>9.66405868530273</v>
+        <v>9.66405773162842</v>
       </c>
       <c r="H588" t="n">
         <v>640698</v>
@@ -17595,7 +17595,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G594" t="n">
-        <v>9.96129703521729</v>
+        <v>9.96129608154297</v>
       </c>
       <c r="H594" t="n">
         <v>397609</v>
@@ -17711,7 +17711,7 @@
         <v>10.7068672180176</v>
       </c>
       <c r="G598" t="n">
-        <v>10.5252876281738</v>
+        <v>10.5252885818481</v>
       </c>
       <c r="H598" t="n">
         <v>677899</v>
@@ -17914,7 +17914,7 @@
         <v>10.4277601242065</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2509136199951</v>
+        <v>10.2509145736694</v>
       </c>
       <c r="H605" t="n">
         <v>654563</v>
@@ -17972,7 +17972,7 @@
         <v>10.0090990066528</v>
       </c>
       <c r="G607" t="n">
-        <v>9.83935356140137</v>
+        <v>9.83935260772705</v>
       </c>
       <c r="H607" t="n">
         <v>1087774</v>
@@ -79951,6 +79951,64 @@
         <v>1836528</v>
       </c>
       <c r="I2744" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2745">
+      <c r="A2745" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2745" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2745" t="n">
+        <v>12.4200000762939</v>
+      </c>
+      <c r="D2745" t="n">
+        <v>12.4650001525879</v>
+      </c>
+      <c r="E2745" t="n">
+        <v>12.1149997711182</v>
+      </c>
+      <c r="F2745" t="n">
+        <v>12.3649997711182</v>
+      </c>
+      <c r="G2745" t="n">
+        <v>12.3649997711182</v>
+      </c>
+      <c r="H2745" t="n">
+        <v>1242264</v>
+      </c>
+      <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>12.375</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>11.9700002670288</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>12.289999961853</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>12.289999961853</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>2063439</v>
+      </c>
+      <c r="I2746" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -80012,6 +80012,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>12.4099998474121</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>12.1199998855591</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>12.2550001144409</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>12.2550001144409</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>1523759</v>
+      </c>
+      <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.17872190475464</v>
       </c>
       <c r="G2" t="n">
-        <v>3.12481331825256</v>
+        <v>3.12481355667114</v>
       </c>
       <c r="H2" t="n">
         <v>493230</v>
@@ -630,7 +630,7 @@
         <v>2.59337210655212</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5493905544281</v>
+        <v>2.54939079284668</v>
       </c>
       <c r="H9" t="n">
         <v>256430</v>
@@ -688,7 +688,7 @@
         <v>2.60422611236572</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56006073951721</v>
+        <v>2.56006050109863</v>
       </c>
       <c r="H11" t="n">
         <v>214063</v>
@@ -746,7 +746,7 @@
         <v>2.45769500732422</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4160144329071</v>
+        <v>2.41601467132568</v>
       </c>
       <c r="H13" t="n">
         <v>205959</v>
@@ -891,7 +891,7 @@
         <v>2.76006102561951</v>
       </c>
       <c r="G18" t="n">
-        <v>2.71325278282166</v>
+        <v>2.71325254440308</v>
       </c>
       <c r="H18" t="n">
         <v>596593</v>
@@ -1036,7 +1036,7 @@
         <v>2.71354293823242</v>
       </c>
       <c r="G23" t="n">
-        <v>2.66752338409424</v>
+        <v>2.66752362251282</v>
       </c>
       <c r="H23" t="n">
         <v>131540</v>
@@ -1065,7 +1065,7 @@
         <v>2.56468605995178</v>
       </c>
       <c r="G24" t="n">
-        <v>2.52119135856628</v>
+        <v>2.52119112014771</v>
       </c>
       <c r="H24" t="n">
         <v>163658</v>
@@ -1123,7 +1123,7 @@
         <v>2.41272711753845</v>
       </c>
       <c r="G26" t="n">
-        <v>2.37180948257446</v>
+        <v>2.37180924415588</v>
       </c>
       <c r="H26" t="n">
         <v>144800</v>
@@ -1152,7 +1152,7 @@
         <v>2.25999402999878</v>
       </c>
       <c r="G27" t="n">
-        <v>2.22166657447815</v>
+        <v>2.22166633605957</v>
       </c>
       <c r="H27" t="n">
         <v>346665</v>
@@ -1181,7 +1181,7 @@
         <v>2.10880994796753</v>
       </c>
       <c r="G28" t="n">
-        <v>2.07304620742798</v>
+        <v>2.07304644584656</v>
       </c>
       <c r="H28" t="n">
         <v>423821</v>
@@ -1239,7 +1239,7 @@
         <v>2.0933051109314</v>
       </c>
       <c r="G30" t="n">
-        <v>2.05780434608459</v>
+        <v>2.05780458450317</v>
       </c>
       <c r="H30" t="n">
         <v>144475</v>
@@ -1326,7 +1326,7 @@
         <v>2.41040110588074</v>
       </c>
       <c r="G33" t="n">
-        <v>2.3695228099823</v>
+        <v>2.36952257156372</v>
       </c>
       <c r="H33" t="n">
         <v>205506</v>
@@ -1384,7 +1384,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G35" t="n">
-        <v>2.56615734100342</v>
+        <v>2.566157579422</v>
       </c>
       <c r="H35" t="n">
         <v>251553</v>
@@ -1413,7 +1413,7 @@
         <v>2.46389698982239</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42211151123047</v>
+        <v>2.42211127281189</v>
       </c>
       <c r="H36" t="n">
         <v>190917</v>
@@ -1442,7 +1442,7 @@
         <v>2.64066505432129</v>
       </c>
       <c r="G37" t="n">
-        <v>2.59588170051575</v>
+        <v>2.59588146209717</v>
       </c>
       <c r="H37" t="n">
         <v>246557</v>
@@ -1819,7 +1819,7 @@
         <v>2.45381808280945</v>
       </c>
       <c r="G50" t="n">
-        <v>2.41220331192017</v>
+        <v>2.41220355033875</v>
       </c>
       <c r="H50" t="n">
         <v>159744</v>
@@ -1935,7 +1935,7 @@
         <v>2.64841794967651</v>
       </c>
       <c r="G54" t="n">
-        <v>2.60350298881531</v>
+        <v>2.60350322723389</v>
       </c>
       <c r="H54" t="n">
         <v>485506</v>
@@ -1993,7 +1993,7 @@
         <v>2.73680210113525</v>
       </c>
       <c r="G56" t="n">
-        <v>2.69038844108582</v>
+        <v>2.69038820266724</v>
       </c>
       <c r="H56" t="n">
         <v>159844</v>
@@ -2109,7 +2109,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G60" t="n">
-        <v>2.56615734100342</v>
+        <v>2.566157579422</v>
       </c>
       <c r="H60" t="n">
         <v>103412</v>
@@ -2341,7 +2341,7 @@
         <v>2.97326803207397</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92284393310547</v>
+        <v>2.92284369468689</v>
       </c>
       <c r="H68" t="n">
         <v>318172</v>
@@ -2428,7 +2428,7 @@
         <v>2.87790608406067</v>
       </c>
       <c r="G71" t="n">
-        <v>2.82909917831421</v>
+        <v>2.82909941673279</v>
       </c>
       <c r="H71" t="n">
         <v>190823</v>
@@ -2457,7 +2457,7 @@
         <v>2.87480497360229</v>
       </c>
       <c r="G72" t="n">
-        <v>2.82605075836182</v>
+        <v>2.82605051994324</v>
       </c>
       <c r="H72" t="n">
         <v>241086</v>
@@ -2544,7 +2544,7 @@
         <v>2.81975889205933</v>
       </c>
       <c r="G75" t="n">
-        <v>2.77193808555603</v>
+        <v>2.77193832397461</v>
       </c>
       <c r="H75" t="n">
         <v>310240</v>
@@ -2573,7 +2573,7 @@
         <v>2.77634191513062</v>
       </c>
       <c r="G76" t="n">
-        <v>2.72925758361816</v>
+        <v>2.72925734519958</v>
       </c>
       <c r="H76" t="n">
         <v>301835</v>
@@ -2602,7 +2602,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G77" t="n">
-        <v>2.73306894302368</v>
+        <v>2.7330687046051</v>
       </c>
       <c r="H77" t="n">
         <v>155939</v>
@@ -2718,7 +2718,7 @@
         <v>2.79727506637573</v>
       </c>
       <c r="G81" t="n">
-        <v>2.749835729599</v>
+        <v>2.74983549118042</v>
       </c>
       <c r="H81" t="n">
         <v>168823</v>
@@ -2979,7 +2979,7 @@
         <v>2.5476291179657</v>
       </c>
       <c r="G90" t="n">
-        <v>2.50442361831665</v>
+        <v>2.50442337989807</v>
       </c>
       <c r="H90" t="n">
         <v>137592</v>
@@ -3095,7 +3095,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G94" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H94" t="n">
         <v>593089</v>
@@ -3153,7 +3153,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G96" t="n">
-        <v>2.73306894302368</v>
+        <v>2.7330687046051</v>
       </c>
       <c r="H96" t="n">
         <v>193495</v>
@@ -3182,7 +3182,7 @@
         <v>2.94070506095886</v>
       </c>
       <c r="G97" t="n">
-        <v>2.89083337783813</v>
+        <v>2.89083313941956</v>
       </c>
       <c r="H97" t="n">
         <v>678677</v>
@@ -3298,7 +3298,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G101" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H101" t="n">
         <v>97675</v>
@@ -3385,7 +3385,7 @@
         <v>2.9693911075592</v>
       </c>
       <c r="G104" t="n">
-        <v>2.91903281211853</v>
+        <v>2.91903257369995</v>
       </c>
       <c r="H104" t="n">
         <v>94349</v>
@@ -3414,7 +3414,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G105" t="n">
-        <v>2.88244986534119</v>
+        <v>2.88244962692261</v>
       </c>
       <c r="H105" t="n">
         <v>76056</v>
@@ -3443,7 +3443,7 @@
         <v>2.8934121131897</v>
       </c>
       <c r="G106" t="n">
-        <v>2.84434247016907</v>
+        <v>2.84434223175049</v>
       </c>
       <c r="H106" t="n">
         <v>160927</v>
@@ -3472,7 +3472,7 @@
         <v>2.94458198547363</v>
       </c>
       <c r="G107" t="n">
-        <v>2.89464449882507</v>
+        <v>2.89464426040649</v>
       </c>
       <c r="H107" t="n">
         <v>122794</v>
@@ -3530,7 +3530,7 @@
         <v>2.91201901435852</v>
       </c>
       <c r="G109" t="n">
-        <v>2.86263370513916</v>
+        <v>2.86263346672058</v>
       </c>
       <c r="H109" t="n">
         <v>97079</v>
@@ -3617,7 +3617,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G112" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H112" t="n">
         <v>87752</v>
@@ -3704,7 +3704,7 @@
         <v>2.64919304847717</v>
       </c>
       <c r="G115" t="n">
-        <v>2.6042652130127</v>
+        <v>2.60426497459412</v>
       </c>
       <c r="H115" t="n">
         <v>158384</v>
@@ -3849,7 +3849,7 @@
         <v>2.90581703186035</v>
       </c>
       <c r="G120" t="n">
-        <v>2.8565366268158</v>
+        <v>2.85653686523438</v>
       </c>
       <c r="H120" t="n">
         <v>140706</v>
@@ -3907,7 +3907,7 @@
         <v>2.80502796173096</v>
       </c>
       <c r="G122" t="n">
-        <v>2.75745725631714</v>
+        <v>2.75745701789856</v>
       </c>
       <c r="H122" t="n">
         <v>103410</v>
@@ -4110,7 +4110,7 @@
         <v>2.53057289123535</v>
       </c>
       <c r="G129" t="n">
-        <v>2.48765659332275</v>
+        <v>2.48765635490417</v>
       </c>
       <c r="H129" t="n">
         <v>122546</v>
@@ -4197,7 +4197,7 @@
         <v>2.43831205368042</v>
       </c>
       <c r="G132" t="n">
-        <v>2.39696025848389</v>
+        <v>2.39696049690247</v>
       </c>
       <c r="H132" t="n">
         <v>324481</v>
@@ -4255,7 +4255,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56082248687744</v>
+        <v>2.56082224845886</v>
       </c>
       <c r="H134" t="n">
         <v>116496</v>
@@ -4284,7 +4284,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56082248687744</v>
+        <v>2.56082224845886</v>
       </c>
       <c r="H135" t="n">
         <v>77002</v>
@@ -4371,7 +4371,7 @@
         <v>2.7057900428772</v>
       </c>
       <c r="G138" t="n">
-        <v>2.65990209579468</v>
+        <v>2.65990233421326</v>
       </c>
       <c r="H138" t="n">
         <v>227795</v>
@@ -4516,7 +4516,7 @@
         <v>2.89186191558838</v>
       </c>
       <c r="G143" t="n">
-        <v>2.84281849861145</v>
+        <v>2.84281826019287</v>
       </c>
       <c r="H143" t="n">
         <v>433122</v>
@@ -4545,7 +4545,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G144" t="n">
-        <v>2.88244986534119</v>
+        <v>2.88244962692261</v>
       </c>
       <c r="H144" t="n">
         <v>504151</v>
@@ -4632,7 +4632,7 @@
         <v>2.95310997962952</v>
       </c>
       <c r="G147" t="n">
-        <v>2.90302777290344</v>
+        <v>2.90302753448486</v>
       </c>
       <c r="H147" t="n">
         <v>124606</v>
@@ -4661,7 +4661,7 @@
         <v>2.9918749332428</v>
       </c>
       <c r="G148" t="n">
-        <v>2.94113540649414</v>
+        <v>2.94113516807556</v>
       </c>
       <c r="H148" t="n">
         <v>115180</v>
@@ -4719,7 +4719,7 @@
         <v>2.96551489830017</v>
       </c>
       <c r="G150" t="n">
-        <v>2.91522240638733</v>
+        <v>2.91522216796875</v>
       </c>
       <c r="H150" t="n">
         <v>107908</v>
@@ -4748,7 +4748,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H151" t="n">
         <v>112608</v>
@@ -4835,7 +4835,7 @@
         <v>2.93527793884277</v>
       </c>
       <c r="G154" t="n">
-        <v>2.885498046875</v>
+        <v>2.88549828529358</v>
       </c>
       <c r="H154" t="n">
         <v>98584</v>
@@ -4922,7 +4922,7 @@
         <v>2.95388507843018</v>
       </c>
       <c r="G157" t="n">
-        <v>2.90378952026367</v>
+        <v>2.90378975868225</v>
       </c>
       <c r="H157" t="n">
         <v>130813</v>
@@ -4980,7 +4980,7 @@
         <v>3.05855107307434</v>
       </c>
       <c r="G159" t="n">
-        <v>3.00668048858643</v>
+        <v>3.006680727005</v>
       </c>
       <c r="H159" t="n">
         <v>293073</v>
@@ -5009,7 +5009,7 @@
         <v>3.0221118927002</v>
       </c>
       <c r="G160" t="n">
-        <v>2.97085928916931</v>
+        <v>2.97085952758789</v>
       </c>
       <c r="H160" t="n">
         <v>76130</v>
@@ -5067,7 +5067,7 @@
         <v>2.97404289245605</v>
       </c>
       <c r="G162" t="n">
-        <v>2.92360544204712</v>
+        <v>2.9236056804657</v>
       </c>
       <c r="H162" t="n">
         <v>29083</v>
@@ -5125,7 +5125,7 @@
         <v>3.02676391601562</v>
       </c>
       <c r="G164" t="n">
-        <v>2.97543263435364</v>
+        <v>2.97543239593506</v>
       </c>
       <c r="H164" t="n">
         <v>68786</v>
@@ -5444,7 +5444,7 @@
         <v>3.35936594009399</v>
       </c>
       <c r="G175" t="n">
-        <v>3.30239391326904</v>
+        <v>3.30239415168762</v>
       </c>
       <c r="H175" t="n">
         <v>136675</v>
@@ -5531,7 +5531,7 @@
         <v>3.38262510299683</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32525849342346</v>
+        <v>3.32525873184204</v>
       </c>
       <c r="H178" t="n">
         <v>282670</v>
@@ -5560,7 +5560,7 @@
         <v>3.31750011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>3.26123833656311</v>
+        <v>3.26123809814453</v>
       </c>
       <c r="H179" t="n">
         <v>124150</v>
@@ -5647,7 +5647,7 @@
         <v>3.23764491081238</v>
       </c>
       <c r="G182" t="n">
-        <v>3.18273735046387</v>
+        <v>3.18273711204529</v>
       </c>
       <c r="H182" t="n">
         <v>146776</v>
@@ -5705,7 +5705,7 @@
         <v>3.20430707931519</v>
       </c>
       <c r="G184" t="n">
-        <v>3.14996480941772</v>
+        <v>3.14996457099915</v>
       </c>
       <c r="H184" t="n">
         <v>75785</v>
@@ -5821,7 +5821,7 @@
         <v>3.35083794593811</v>
       </c>
       <c r="G188" t="n">
-        <v>3.29401040077209</v>
+        <v>3.29401063919067</v>
       </c>
       <c r="H188" t="n">
         <v>126105</v>
@@ -5937,7 +5937,7 @@
         <v>3.35548996925354</v>
       </c>
       <c r="G192" t="n">
-        <v>3.29858374595642</v>
+        <v>3.29858350753784</v>
       </c>
       <c r="H192" t="n">
         <v>204931</v>
@@ -6082,7 +6082,7 @@
         <v>3.3570408821106</v>
       </c>
       <c r="G197" t="n">
-        <v>3.30010843276978</v>
+        <v>3.3001081943512</v>
       </c>
       <c r="H197" t="n">
         <v>92448</v>
@@ -6140,7 +6140,7 @@
         <v>3.33067989349365</v>
       </c>
       <c r="G199" t="n">
-        <v>3.27419424057007</v>
+        <v>3.27419447898865</v>
       </c>
       <c r="H199" t="n">
         <v>109612</v>
@@ -6169,7 +6169,7 @@
         <v>3.35238909721375</v>
       </c>
       <c r="G200" t="n">
-        <v>3.29553556442261</v>
+        <v>3.29553532600403</v>
       </c>
       <c r="H200" t="n">
         <v>72532</v>
@@ -6343,7 +6343,7 @@
         <v>3.34308505058289</v>
       </c>
       <c r="G206" t="n">
-        <v>3.28638911247253</v>
+        <v>3.28638935089111</v>
       </c>
       <c r="H206" t="n">
         <v>211723</v>
@@ -6575,7 +6575,7 @@
         <v>3.19965505599976</v>
       </c>
       <c r="G214" t="n">
-        <v>3.14539170265198</v>
+        <v>3.1453914642334</v>
       </c>
       <c r="H214" t="n">
         <v>46695</v>
@@ -6604,7 +6604,7 @@
         <v>3.20353198051453</v>
       </c>
       <c r="G215" t="n">
-        <v>3.14920282363892</v>
+        <v>3.14920258522034</v>
       </c>
       <c r="H215" t="n">
         <v>20449</v>
@@ -6720,7 +6720,7 @@
         <v>3.04226899147034</v>
       </c>
       <c r="G219" t="n">
-        <v>2.99067449569702</v>
+        <v>2.9906747341156</v>
       </c>
       <c r="H219" t="n">
         <v>119131</v>
@@ -6778,7 +6778,7 @@
         <v>3.23299288749695</v>
       </c>
       <c r="G221" t="n">
-        <v>3.17816424369812</v>
+        <v>3.17816400527954</v>
       </c>
       <c r="H221" t="n">
         <v>190310</v>
@@ -6807,7 +6807,7 @@
         <v>3.24384689331055</v>
       </c>
       <c r="G222" t="n">
-        <v>3.18883395195007</v>
+        <v>3.18883419036865</v>
       </c>
       <c r="H222" t="n">
         <v>201688</v>
@@ -6836,7 +6836,7 @@
         <v>3.37254691123962</v>
       </c>
       <c r="G223" t="n">
-        <v>3.31535148620605</v>
+        <v>3.31535124778748</v>
       </c>
       <c r="H223" t="n">
         <v>480056</v>
@@ -7010,7 +7010,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G229" t="n">
-        <v>3.19340705871582</v>
+        <v>3.1934072971344</v>
       </c>
       <c r="H229" t="n">
         <v>91423</v>
@@ -7068,7 +7068,7 @@
         <v>3.24617290496826</v>
       </c>
       <c r="G231" t="n">
-        <v>3.19112038612366</v>
+        <v>3.19112062454224</v>
       </c>
       <c r="H231" t="n">
         <v>60078</v>
@@ -7097,7 +7097,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G232" t="n">
-        <v>3.18197464942932</v>
+        <v>3.18197441101074</v>
       </c>
       <c r="H232" t="n">
         <v>46953</v>
@@ -7213,7 +7213,7 @@
         <v>3.22601509094238</v>
       </c>
       <c r="G236" t="n">
-        <v>3.17130446434021</v>
+        <v>3.17130470275879</v>
       </c>
       <c r="H236" t="n">
         <v>92031</v>
@@ -7242,7 +7242,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G237" t="n">
-        <v>3.19340705871582</v>
+        <v>3.1934072971344</v>
       </c>
       <c r="H237" t="n">
         <v>65003</v>
@@ -7329,7 +7329,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G240" t="n">
-        <v>3.18197464942932</v>
+        <v>3.18197441101074</v>
       </c>
       <c r="H240" t="n">
         <v>117377</v>
@@ -7503,7 +7503,7 @@
         <v>3.26167893409729</v>
       </c>
       <c r="G246" t="n">
-        <v>3.20636367797852</v>
+        <v>3.20636343955994</v>
       </c>
       <c r="H246" t="n">
         <v>207240</v>
@@ -7532,7 +7532,7 @@
         <v>3.32602906227112</v>
       </c>
       <c r="G247" t="n">
-        <v>3.26962232589722</v>
+        <v>3.2696225643158</v>
       </c>
       <c r="H247" t="n">
         <v>91899</v>
@@ -7677,7 +7677,7 @@
         <v>3.5446629524231</v>
       </c>
       <c r="G252" t="n">
-        <v>3.48454856872559</v>
+        <v>3.48454833030701</v>
       </c>
       <c r="H252" t="n">
         <v>194782</v>
@@ -7851,7 +7851,7 @@
         <v>3.721431016922</v>
       </c>
       <c r="G258" t="n">
-        <v>3.65831875801086</v>
+        <v>3.65831851959229</v>
       </c>
       <c r="H258" t="n">
         <v>319621</v>
@@ -7909,7 +7909,7 @@
         <v>4.00053787231445</v>
       </c>
       <c r="G260" t="n">
-        <v>3.93269205093384</v>
+        <v>3.93269228935242</v>
       </c>
       <c r="H260" t="n">
         <v>648070</v>
@@ -8083,7 +8083,7 @@
         <v>4.05093193054199</v>
       </c>
       <c r="G266" t="n">
-        <v>3.9822313785553</v>
+        <v>3.98223161697388</v>
       </c>
       <c r="H266" t="n">
         <v>236555</v>
@@ -8257,7 +8257,7 @@
         <v>4.18661022186279</v>
       </c>
       <c r="G272" t="n">
-        <v>4.11560869216919</v>
+        <v>4.11560916900635</v>
       </c>
       <c r="H272" t="n">
         <v>1412380</v>
@@ -8286,7 +8286,7 @@
         <v>4.27964496612549</v>
       </c>
       <c r="G273" t="n">
-        <v>4.20706605911255</v>
+        <v>4.20706558227539</v>
       </c>
       <c r="H273" t="n">
         <v>1069890</v>
@@ -8315,7 +8315,7 @@
         <v>4.43858098983765</v>
       </c>
       <c r="G274" t="n">
-        <v>4.36330652236938</v>
+        <v>4.36330604553223</v>
       </c>
       <c r="H274" t="n">
         <v>723596</v>
@@ -8344,7 +8344,7 @@
         <v>4.442458152771</v>
       </c>
       <c r="G275" t="n">
-        <v>4.3671178817749</v>
+        <v>4.36711740493774</v>
       </c>
       <c r="H275" t="n">
         <v>567984</v>
@@ -8402,7 +8402,7 @@
         <v>4.3610520362854</v>
       </c>
       <c r="G277" t="n">
-        <v>4.28709268569946</v>
+        <v>4.2870922088623</v>
       </c>
       <c r="H277" t="n">
         <v>208145</v>
@@ -8431,7 +8431,7 @@
         <v>4.25251007080078</v>
       </c>
       <c r="G278" t="n">
-        <v>4.18039131164551</v>
+        <v>4.18039083480835</v>
       </c>
       <c r="H278" t="n">
         <v>280129</v>
@@ -8547,7 +8547,7 @@
         <v>4.33779287338257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.26422739028931</v>
+        <v>4.26422786712646</v>
       </c>
       <c r="H282" t="n">
         <v>221629</v>
@@ -8605,7 +8605,7 @@
         <v>4.27189207077026</v>
       </c>
       <c r="G284" t="n">
-        <v>4.19944477081299</v>
+        <v>4.19944429397583</v>
       </c>
       <c r="H284" t="n">
         <v>219679</v>
@@ -8721,7 +8721,7 @@
         <v>4.12846183776855</v>
       </c>
       <c r="G288" t="n">
-        <v>4.05844688415527</v>
+        <v>4.05844640731812</v>
       </c>
       <c r="H288" t="n">
         <v>181443</v>
@@ -8808,7 +8808,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G291" t="n">
-        <v>4.5271692276001</v>
+        <v>4.52716970443726</v>
       </c>
       <c r="H291" t="n">
         <v>1365540</v>
@@ -8866,7 +8866,7 @@
         <v>4.52386379241943</v>
       </c>
       <c r="G293" t="n">
-        <v>4.44714260101318</v>
+        <v>4.44714307785034</v>
       </c>
       <c r="H293" t="n">
         <v>403894</v>
@@ -8982,7 +8982,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G297" t="n">
-        <v>4.5271692276001</v>
+        <v>4.52716970443726</v>
       </c>
       <c r="H297" t="n">
         <v>367010</v>
@@ -9040,7 +9040,7 @@
         <v>4.64403486251831</v>
       </c>
       <c r="G299" t="n">
-        <v>4.5652756690979</v>
+        <v>4.56527614593506</v>
       </c>
       <c r="H299" t="n">
         <v>165971</v>
@@ -9098,7 +9098,7 @@
         <v>4.88437795639038</v>
       </c>
       <c r="G301" t="n">
-        <v>4.80154275894165</v>
+        <v>4.80154323577881</v>
       </c>
       <c r="H301" t="n">
         <v>885013</v>
@@ -9127,7 +9127,7 @@
         <v>5.09758520126343</v>
       </c>
       <c r="G302" t="n">
-        <v>5.0111346244812</v>
+        <v>5.01113414764404</v>
       </c>
       <c r="H302" t="n">
         <v>1328330</v>
@@ -9388,7 +9388,7 @@
         <v>5.02780818939209</v>
       </c>
       <c r="G311" t="n">
-        <v>4.94254064559937</v>
+        <v>4.94254112243652</v>
       </c>
       <c r="H311" t="n">
         <v>342293</v>
@@ -9446,7 +9446,7 @@
         <v>5.06657314300537</v>
       </c>
       <c r="G313" t="n">
-        <v>4.98064804077148</v>
+        <v>4.98064851760864</v>
       </c>
       <c r="H313" t="n">
         <v>238791</v>
@@ -9533,7 +9533,7 @@
         <v>5.11309099197388</v>
       </c>
       <c r="G316" t="n">
-        <v>5.02637767791748</v>
+        <v>5.02637720108032</v>
       </c>
       <c r="H316" t="n">
         <v>297516</v>
@@ -9562,7 +9562,7 @@
         <v>5.19449710845947</v>
       </c>
       <c r="G317" t="n">
-        <v>5.10640239715576</v>
+        <v>5.10640287399292</v>
       </c>
       <c r="H317" t="n">
         <v>464423</v>
@@ -9649,7 +9649,7 @@
         <v>5.21388006210327</v>
       </c>
       <c r="G320" t="n">
-        <v>5.12545728683472</v>
+        <v>5.12545680999756</v>
       </c>
       <c r="H320" t="n">
         <v>546852</v>
@@ -9707,7 +9707,7 @@
         <v>5.48523378372192</v>
       </c>
       <c r="G322" t="n">
-        <v>5.39220857620239</v>
+        <v>5.39220905303955</v>
       </c>
       <c r="H322" t="n">
         <v>940314</v>
@@ -9823,7 +9823,7 @@
         <v>6.08609008789062</v>
       </c>
       <c r="G326" t="n">
-        <v>5.98287487030029</v>
+        <v>5.98287534713745</v>
       </c>
       <c r="H326" t="n">
         <v>1806086</v>
@@ -9881,7 +9881,7 @@
         <v>6.11710214614868</v>
       </c>
       <c r="G328" t="n">
-        <v>6.01336097717285</v>
+        <v>6.01336145401001</v>
       </c>
       <c r="H328" t="n">
         <v>1777020</v>
@@ -10026,7 +10026,7 @@
         <v>6.20238494873047</v>
       </c>
       <c r="G333" t="n">
-        <v>6.09719800949097</v>
+        <v>6.09719753265381</v>
       </c>
       <c r="H333" t="n">
         <v>1738052</v>
@@ -10171,7 +10171,7 @@
         <v>7.13661909103394</v>
       </c>
       <c r="G338" t="n">
-        <v>7.01558828353882</v>
+        <v>7.01558780670166</v>
       </c>
       <c r="H338" t="n">
         <v>2024444</v>
@@ -10200,7 +10200,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G339" t="n">
-        <v>6.72215986251831</v>
+        <v>6.72216033935547</v>
       </c>
       <c r="H339" t="n">
         <v>1597497</v>
@@ -10316,7 +10316,7 @@
         <v>7.07847213745117</v>
       </c>
       <c r="G343" t="n">
-        <v>6.95842695236206</v>
+        <v>6.95842742919922</v>
       </c>
       <c r="H343" t="n">
         <v>1152592</v>
@@ -10345,7 +10345,7 @@
         <v>7.02420091629028</v>
       </c>
       <c r="G344" t="n">
-        <v>6.90507650375366</v>
+        <v>6.9050760269165</v>
       </c>
       <c r="H344" t="n">
         <v>757764</v>
@@ -10403,7 +10403,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G346" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H346" t="n">
         <v>1253565</v>
@@ -10432,7 +10432,7 @@
         <v>7.40797281265259</v>
       </c>
       <c r="G347" t="n">
-        <v>7.28234004974365</v>
+        <v>7.28233957290649</v>
       </c>
       <c r="H347" t="n">
         <v>953069</v>
@@ -10577,7 +10577,7 @@
         <v>6.38845586776733</v>
       </c>
       <c r="G352" t="n">
-        <v>6.28011274337769</v>
+        <v>6.28011322021484</v>
       </c>
       <c r="H352" t="n">
         <v>1189739</v>
@@ -10751,7 +10751,7 @@
         <v>7.03583002090454</v>
       </c>
       <c r="G358" t="n">
-        <v>6.91650867462158</v>
+        <v>6.91650819778442</v>
       </c>
       <c r="H358" t="n">
         <v>557993</v>
@@ -10809,7 +10809,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G360" t="n">
-        <v>6.72215986251831</v>
+        <v>6.72216033935547</v>
       </c>
       <c r="H360" t="n">
         <v>383136</v>
@@ -11070,7 +11070,7 @@
         <v>6.86526489257812</v>
       </c>
       <c r="G369" t="n">
-        <v>6.74883604049683</v>
+        <v>6.74883556365967</v>
       </c>
       <c r="H369" t="n">
         <v>381623</v>
@@ -11099,7 +11099,7 @@
         <v>6.77222919464111</v>
       </c>
       <c r="G370" t="n">
-        <v>6.65737771987915</v>
+        <v>6.65737819671631</v>
       </c>
       <c r="H370" t="n">
         <v>410334</v>
@@ -11157,7 +11157,7 @@
         <v>6.76835203170776</v>
       </c>
       <c r="G372" t="n">
-        <v>6.65356636047363</v>
+        <v>6.65356683731079</v>
       </c>
       <c r="H372" t="n">
         <v>220177</v>
@@ -11447,7 +11447,7 @@
         <v>7.37308502197266</v>
       </c>
       <c r="G382" t="n">
-        <v>7.24804353713989</v>
+        <v>7.24804401397705</v>
       </c>
       <c r="H382" t="n">
         <v>2466801</v>
@@ -11563,7 +11563,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G386" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H386" t="n">
         <v>674582</v>
@@ -11679,7 +11679,7 @@
         <v>7.72972202301025</v>
       </c>
       <c r="G390" t="n">
-        <v>7.59863233566284</v>
+        <v>7.5986328125</v>
       </c>
       <c r="H390" t="n">
         <v>446172</v>
@@ -11737,7 +11737,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G392" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H392" t="n">
         <v>528987</v>
@@ -11795,7 +11795,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G394" t="n">
-        <v>8.1931095123291</v>
+        <v>8.19310855865479</v>
       </c>
       <c r="H394" t="n">
         <v>618520</v>
@@ -11824,7 +11824,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G395" t="n">
-        <v>8.36078262329102</v>
+        <v>8.3607816696167</v>
       </c>
       <c r="H395" t="n">
         <v>589330</v>
@@ -11911,7 +11911,7 @@
         <v>8.0708532333374</v>
       </c>
       <c r="G398" t="n">
-        <v>7.93397808074951</v>
+        <v>7.93397903442383</v>
       </c>
       <c r="H398" t="n">
         <v>1105464</v>
@@ -11940,7 +11940,7 @@
         <v>8.03208827972412</v>
       </c>
       <c r="G399" t="n">
-        <v>7.89587068557739</v>
+        <v>7.89587116241455</v>
       </c>
       <c r="H399" t="n">
         <v>704166</v>
@@ -12027,7 +12027,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G402" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H402" t="n">
         <v>4317226</v>
@@ -12230,7 +12230,7 @@
         <v>7.67545080184937</v>
       </c>
       <c r="G409" t="n">
-        <v>7.54528188705444</v>
+        <v>7.54528141021729</v>
       </c>
       <c r="H409" t="n">
         <v>485472</v>
@@ -12317,7 +12317,7 @@
         <v>7.30718517303467</v>
       </c>
       <c r="G412" t="n">
-        <v>7.18326187133789</v>
+        <v>7.18326139450073</v>
       </c>
       <c r="H412" t="n">
         <v>778353</v>
@@ -12462,7 +12462,7 @@
         <v>7.07071876525879</v>
       </c>
       <c r="G417" t="n">
-        <v>6.95080518722534</v>
+        <v>6.9508056640625</v>
       </c>
       <c r="H417" t="n">
         <v>221650</v>
@@ -12520,7 +12520,7 @@
         <v>6.985435962677</v>
       </c>
       <c r="G419" t="n">
-        <v>6.86696910858154</v>
+        <v>6.86696863174438</v>
       </c>
       <c r="H419" t="n">
         <v>607996</v>
@@ -12607,7 +12607,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G422" t="n">
-        <v>7.27853012084961</v>
+        <v>7.27852964401245</v>
       </c>
       <c r="H422" t="n">
         <v>880611</v>
@@ -12723,7 +12723,7 @@
         <v>7.17925977706909</v>
       </c>
       <c r="G426" t="n">
-        <v>7.05750560760498</v>
+        <v>7.05750608444214</v>
       </c>
       <c r="H426" t="n">
         <v>1555624</v>
@@ -12752,7 +12752,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G427" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H427" t="n">
         <v>1335622</v>
@@ -12868,7 +12868,7 @@
         <v>8.00107669830322</v>
       </c>
       <c r="G431" t="n">
-        <v>7.86538505554199</v>
+        <v>7.86538553237915</v>
       </c>
       <c r="H431" t="n">
         <v>781944</v>
@@ -12926,7 +12926,7 @@
         <v>7.7142162322998</v>
       </c>
       <c r="G433" t="n">
-        <v>7.58338975906372</v>
+        <v>7.58338928222656</v>
       </c>
       <c r="H433" t="n">
         <v>526446</v>
@@ -12955,7 +12955,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G434" t="n">
-        <v>7.94922113418579</v>
+        <v>7.94922161102295</v>
       </c>
       <c r="H434" t="n">
         <v>1316387</v>
@@ -13071,7 +13071,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G438" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H438" t="n">
         <v>447832</v>
@@ -13129,7 +13129,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G440" t="n">
-        <v>7.94922113418579</v>
+        <v>7.94922161102295</v>
       </c>
       <c r="H440" t="n">
         <v>478643</v>
@@ -13158,7 +13158,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G441" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H441" t="n">
         <v>375921</v>
@@ -13303,7 +13303,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G446" t="n">
-        <v>8.36078262329102</v>
+        <v>8.3607816696167</v>
       </c>
       <c r="H446" t="n">
         <v>2904190</v>
@@ -13332,7 +13332,7 @@
         <v>8.06309986114502</v>
       </c>
       <c r="G447" t="n">
-        <v>7.92635631561279</v>
+        <v>7.92635583877563</v>
       </c>
       <c r="H447" t="n">
         <v>4805532</v>
@@ -13448,7 +13448,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G451" t="n">
-        <v>7.36617660522461</v>
+        <v>7.36617708206177</v>
       </c>
       <c r="H451" t="n">
         <v>1207097</v>
@@ -13477,7 +13477,7 @@
         <v>7.58629179000854</v>
       </c>
       <c r="G452" t="n">
-        <v>7.45763492584229</v>
+        <v>7.45763444900513</v>
       </c>
       <c r="H452" t="n">
         <v>1486373</v>
@@ -13564,7 +13564,7 @@
         <v>7.51651477813721</v>
       </c>
       <c r="G455" t="n">
-        <v>7.38904142379761</v>
+        <v>7.38904094696045</v>
       </c>
       <c r="H455" t="n">
         <v>957250</v>
@@ -13680,7 +13680,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G459" t="n">
-        <v>7.31663751602173</v>
+        <v>7.31663703918457</v>
       </c>
       <c r="H459" t="n">
         <v>430589</v>
@@ -13709,7 +13709,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G460" t="n">
-        <v>7.27853012084961</v>
+        <v>7.27852964401245</v>
       </c>
       <c r="H460" t="n">
         <v>425428</v>
@@ -13796,7 +13796,7 @@
         <v>7.50100898742676</v>
       </c>
       <c r="G463" t="n">
-        <v>7.37379789352417</v>
+        <v>7.37379837036133</v>
       </c>
       <c r="H463" t="n">
         <v>490050</v>
@@ -13825,7 +13825,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G464" t="n">
-        <v>7.31663751602173</v>
+        <v>7.31663703918457</v>
       </c>
       <c r="H464" t="n">
         <v>447048</v>
@@ -13883,7 +13883,7 @@
         <v>7.44673776626587</v>
       </c>
       <c r="G466" t="n">
-        <v>7.32044744491577</v>
+        <v>7.32044696807861</v>
       </c>
       <c r="H466" t="n">
         <v>650810</v>
@@ -13912,7 +13912,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G467" t="n">
-        <v>7.36617660522461</v>
+        <v>7.36617708206177</v>
       </c>
       <c r="H467" t="n">
         <v>504330</v>
@@ -14028,7 +14028,7 @@
         <v>8.54378509521484</v>
       </c>
       <c r="G471" t="n">
-        <v>8.39889049530029</v>
+        <v>8.39888954162598</v>
       </c>
       <c r="H471" t="n">
         <v>1645276</v>
@@ -14057,7 +14057,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G472" t="n">
-        <v>8.1931095123291</v>
+        <v>8.19310855865479</v>
       </c>
       <c r="H472" t="n">
         <v>1740272</v>
@@ -14115,7 +14115,7 @@
         <v>8.24141883850098</v>
       </c>
       <c r="G474" t="n">
-        <v>8.10165214538574</v>
+        <v>8.10165119171143</v>
       </c>
       <c r="H474" t="n">
         <v>648959</v>
@@ -14144,7 +14144,7 @@
         <v>8.21040725708008</v>
       </c>
       <c r="G475" t="n">
-        <v>8.07116508483887</v>
+        <v>8.07116603851318</v>
       </c>
       <c r="H475" t="n">
         <v>437746</v>
@@ -14231,7 +14231,7 @@
         <v>8.38872623443604</v>
       </c>
       <c r="G478" t="n">
-        <v>8.2464599609375</v>
+        <v>8.24646091461182</v>
       </c>
       <c r="H478" t="n">
         <v>2636241</v>
@@ -14289,7 +14289,7 @@
         <v>8.87716293334961</v>
       </c>
       <c r="G480" t="n">
-        <v>8.72661399841309</v>
+        <v>8.72661304473877</v>
       </c>
       <c r="H480" t="n">
         <v>2854751</v>
@@ -14405,7 +14405,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G484" t="n">
-        <v>8.8866662979126</v>
+        <v>8.88666534423828</v>
       </c>
       <c r="H484" t="n">
         <v>943241</v>
@@ -14434,7 +14434,7 @@
         <v>9.04772853851318</v>
       </c>
       <c r="G485" t="n">
-        <v>8.89428615570068</v>
+        <v>8.894287109375</v>
       </c>
       <c r="H485" t="n">
         <v>875881</v>
@@ -14521,7 +14521,7 @@
         <v>9.17177677154541</v>
       </c>
       <c r="G488" t="n">
-        <v>9.01623058319092</v>
+        <v>9.01623153686523</v>
       </c>
       <c r="H488" t="n">
         <v>886825</v>
@@ -14782,7 +14782,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G497" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H497" t="n">
         <v>1414410</v>
@@ -14898,7 +14898,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G501" t="n">
-        <v>9.96129608154297</v>
+        <v>9.96129703521729</v>
       </c>
       <c r="H501" t="n">
         <v>845538</v>
@@ -14956,7 +14956,7 @@
         <v>10.1796636581421</v>
       </c>
       <c r="G503" t="n">
-        <v>10.007025718689</v>
+        <v>10.0070247650146</v>
       </c>
       <c r="H503" t="n">
         <v>832310</v>
@@ -15043,7 +15043,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G506" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H506" t="n">
         <v>913020</v>
@@ -15072,7 +15072,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G507" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H507" t="n">
         <v>366112</v>
@@ -15159,7 +15159,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G510" t="n">
-        <v>9.79362392425537</v>
+        <v>9.79362297058105</v>
       </c>
       <c r="H510" t="n">
         <v>238182</v>
@@ -15188,7 +15188,7 @@
         <v>9.70673179626465</v>
       </c>
       <c r="G511" t="n">
-        <v>9.5421142578125</v>
+        <v>9.54211330413818</v>
       </c>
       <c r="H511" t="n">
         <v>455430</v>
@@ -15246,7 +15246,7 @@
         <v>10.1486520767212</v>
       </c>
       <c r="G513" t="n">
-        <v>9.97653865814209</v>
+        <v>9.97653961181641</v>
       </c>
       <c r="H513" t="n">
         <v>442390</v>
@@ -15304,7 +15304,7 @@
         <v>10.5285491943359</v>
       </c>
       <c r="G515" t="n">
-        <v>10.3499946594238</v>
+        <v>10.3499937057495</v>
       </c>
       <c r="H515" t="n">
         <v>969702</v>
@@ -15420,7 +15420,7 @@
         <v>11.2108106613159</v>
       </c>
       <c r="G519" t="n">
-        <v>11.0206842422485</v>
+        <v>11.0206851959229</v>
       </c>
       <c r="H519" t="n">
         <v>1860164</v>
@@ -15536,7 +15536,7 @@
         <v>11.265082359314</v>
       </c>
       <c r="G523" t="n">
-        <v>11.0740365982056</v>
+        <v>11.0740356445312</v>
       </c>
       <c r="H523" t="n">
         <v>1216725</v>
@@ -15594,7 +15594,7 @@
         <v>11.3658714294434</v>
       </c>
       <c r="G525" t="n">
-        <v>11.1731157302856</v>
+        <v>11.17311668396</v>
       </c>
       <c r="H525" t="n">
         <v>686072</v>
@@ -15623,7 +15623,7 @@
         <v>11.3426122665405</v>
       </c>
       <c r="G526" t="n">
-        <v>11.1502513885498</v>
+        <v>11.1502504348755</v>
       </c>
       <c r="H526" t="n">
         <v>701379</v>
@@ -15681,7 +15681,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G528" t="n">
-        <v>10.8225269317627</v>
+        <v>10.8225259780884</v>
       </c>
       <c r="H528" t="n">
         <v>764225</v>
@@ -15855,7 +15855,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G534" t="n">
-        <v>10.8225269317627</v>
+        <v>10.8225259780884</v>
       </c>
       <c r="H534" t="n">
         <v>1206401</v>
@@ -16029,7 +16029,7 @@
         <v>10.4200067520142</v>
       </c>
       <c r="G540" t="n">
-        <v>10.2432928085327</v>
+        <v>10.2432918548584</v>
       </c>
       <c r="H540" t="n">
         <v>1215961</v>
@@ -16058,7 +16058,7 @@
         <v>10.5052900314331</v>
       </c>
       <c r="G541" t="n">
-        <v>10.3271293640137</v>
+        <v>10.3271284103394</v>
       </c>
       <c r="H541" t="n">
         <v>891258</v>
@@ -16174,7 +16174,7 @@
         <v>10.4665250778198</v>
       </c>
       <c r="G545" t="n">
-        <v>10.2890224456787</v>
+        <v>10.2890214920044</v>
       </c>
       <c r="H545" t="n">
         <v>418757</v>
@@ -16290,7 +16290,7 @@
         <v>10.3889951705933</v>
       </c>
       <c r="G549" t="n">
-        <v>10.2128057479858</v>
+        <v>10.2128067016602</v>
       </c>
       <c r="H549" t="n">
         <v>499673</v>
@@ -16348,7 +16348,7 @@
         <v>9.9548282623291</v>
       </c>
       <c r="G551" t="n">
-        <v>9.78600311279297</v>
+        <v>9.78600215911865</v>
       </c>
       <c r="H551" t="n">
         <v>665775</v>
@@ -16464,7 +16464,7 @@
         <v>9.59043788909912</v>
       </c>
       <c r="G555" t="n">
-        <v>9.42779159545898</v>
+        <v>9.4277925491333</v>
       </c>
       <c r="H555" t="n">
         <v>595699</v>
@@ -16638,7 +16638,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G561" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H561" t="n">
         <v>502777</v>
@@ -16696,7 +16696,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G563" t="n">
-        <v>9.79362392425537</v>
+        <v>9.79362297058105</v>
       </c>
       <c r="H563" t="n">
         <v>395215</v>
@@ -16841,7 +16841,7 @@
         <v>10.1951704025269</v>
       </c>
       <c r="G568" t="n">
-        <v>10.0222692489624</v>
+        <v>10.0222682952881</v>
       </c>
       <c r="H568" t="n">
         <v>554786</v>
@@ -16957,7 +16957,7 @@
         <v>11.0247392654419</v>
       </c>
       <c r="G572" t="n">
-        <v>10.8377695083618</v>
+        <v>10.8377685546875</v>
       </c>
       <c r="H572" t="n">
         <v>977445</v>
@@ -17102,7 +17102,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G577" t="n">
-        <v>8.8866662979126</v>
+        <v>8.88666534423828</v>
       </c>
       <c r="H577" t="n">
         <v>1985248</v>
@@ -17189,7 +17189,7 @@
         <v>9.11750602722168</v>
       </c>
       <c r="G580" t="n">
-        <v>8.96288108825684</v>
+        <v>8.96288013458252</v>
       </c>
       <c r="H580" t="n">
         <v>887045</v>
@@ -17218,7 +17218,7 @@
         <v>9.45088386535645</v>
       </c>
       <c r="G581" t="n">
-        <v>9.29060459136963</v>
+        <v>9.29060554504395</v>
       </c>
       <c r="H581" t="n">
         <v>2141921</v>
@@ -17421,7 +17421,7 @@
         <v>9.83078002929688</v>
       </c>
       <c r="G588" t="n">
-        <v>9.66405773162842</v>
+        <v>9.66405868530273</v>
       </c>
       <c r="H588" t="n">
         <v>640698</v>
@@ -17595,7 +17595,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G594" t="n">
-        <v>9.96129608154297</v>
+        <v>9.96129703521729</v>
       </c>
       <c r="H594" t="n">
         <v>397609</v>
@@ -17711,7 +17711,7 @@
         <v>10.7068672180176</v>
       </c>
       <c r="G598" t="n">
-        <v>10.5252885818481</v>
+        <v>10.5252876281738</v>
       </c>
       <c r="H598" t="n">
         <v>677899</v>
@@ -17914,7 +17914,7 @@
         <v>10.4277601242065</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2509145736694</v>
+        <v>10.2509136199951</v>
       </c>
       <c r="H605" t="n">
         <v>654563</v>
@@ -17972,7 +17972,7 @@
         <v>10.0090990066528</v>
       </c>
       <c r="G607" t="n">
-        <v>9.83935260772705</v>
+        <v>9.83935356140137</v>
       </c>
       <c r="H607" t="n">
         <v>1087774</v>
@@ -80038,6 +80038,35 @@
         <v>1523759</v>
       </c>
       <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2748">
+      <c r="A2748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2748" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2748" t="n">
+        <v>12.2550001144409</v>
+      </c>
+      <c r="D2748" t="n">
+        <v>12.3450002670288</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>12.0649995803833</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>12.0649995803833</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>12.0649995803833</v>
+      </c>
+      <c r="H2748" t="n">
+        <v>1117959</v>
+      </c>
+      <c r="I2748" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.17872190475464</v>
       </c>
       <c r="G2" t="n">
-        <v>3.12481355667114</v>
+        <v>3.12481331825256</v>
       </c>
       <c r="H2" t="n">
         <v>493230</v>
@@ -630,7 +630,7 @@
         <v>2.59337210655212</v>
       </c>
       <c r="G9" t="n">
-        <v>2.54939079284668</v>
+        <v>2.5493905544281</v>
       </c>
       <c r="H9" t="n">
         <v>256430</v>
@@ -688,7 +688,7 @@
         <v>2.60422611236572</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56006050109863</v>
+        <v>2.56006073951721</v>
       </c>
       <c r="H11" t="n">
         <v>214063</v>
@@ -746,7 +746,7 @@
         <v>2.45769500732422</v>
       </c>
       <c r="G13" t="n">
-        <v>2.41601467132568</v>
+        <v>2.4160144329071</v>
       </c>
       <c r="H13" t="n">
         <v>205959</v>
@@ -891,7 +891,7 @@
         <v>2.76006102561951</v>
       </c>
       <c r="G18" t="n">
-        <v>2.71325254440308</v>
+        <v>2.71325278282166</v>
       </c>
       <c r="H18" t="n">
         <v>596593</v>
@@ -1036,7 +1036,7 @@
         <v>2.71354293823242</v>
       </c>
       <c r="G23" t="n">
-        <v>2.66752362251282</v>
+        <v>2.66752338409424</v>
       </c>
       <c r="H23" t="n">
         <v>131540</v>
@@ -1065,7 +1065,7 @@
         <v>2.56468605995178</v>
       </c>
       <c r="G24" t="n">
-        <v>2.52119112014771</v>
+        <v>2.52119135856628</v>
       </c>
       <c r="H24" t="n">
         <v>163658</v>
@@ -1123,7 +1123,7 @@
         <v>2.41272711753845</v>
       </c>
       <c r="G26" t="n">
-        <v>2.37180924415588</v>
+        <v>2.37180948257446</v>
       </c>
       <c r="H26" t="n">
         <v>144800</v>
@@ -1152,7 +1152,7 @@
         <v>2.25999402999878</v>
       </c>
       <c r="G27" t="n">
-        <v>2.22166633605957</v>
+        <v>2.22166657447815</v>
       </c>
       <c r="H27" t="n">
         <v>346665</v>
@@ -1181,7 +1181,7 @@
         <v>2.10880994796753</v>
       </c>
       <c r="G28" t="n">
-        <v>2.07304644584656</v>
+        <v>2.07304620742798</v>
       </c>
       <c r="H28" t="n">
         <v>423821</v>
@@ -1239,7 +1239,7 @@
         <v>2.0933051109314</v>
       </c>
       <c r="G30" t="n">
-        <v>2.05780458450317</v>
+        <v>2.05780434608459</v>
       </c>
       <c r="H30" t="n">
         <v>144475</v>
@@ -1326,7 +1326,7 @@
         <v>2.41040110588074</v>
       </c>
       <c r="G33" t="n">
-        <v>2.36952257156372</v>
+        <v>2.3695228099823</v>
       </c>
       <c r="H33" t="n">
         <v>205506</v>
@@ -1384,7 +1384,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G35" t="n">
-        <v>2.566157579422</v>
+        <v>2.56615734100342</v>
       </c>
       <c r="H35" t="n">
         <v>251553</v>
@@ -1413,7 +1413,7 @@
         <v>2.46389698982239</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42211127281189</v>
+        <v>2.42211151123047</v>
       </c>
       <c r="H36" t="n">
         <v>190917</v>
@@ -1442,7 +1442,7 @@
         <v>2.64066505432129</v>
       </c>
       <c r="G37" t="n">
-        <v>2.59588146209717</v>
+        <v>2.59588170051575</v>
       </c>
       <c r="H37" t="n">
         <v>246557</v>
@@ -1819,7 +1819,7 @@
         <v>2.45381808280945</v>
       </c>
       <c r="G50" t="n">
-        <v>2.41220355033875</v>
+        <v>2.41220331192017</v>
       </c>
       <c r="H50" t="n">
         <v>159744</v>
@@ -1935,7 +1935,7 @@
         <v>2.64841794967651</v>
       </c>
       <c r="G54" t="n">
-        <v>2.60350322723389</v>
+        <v>2.60350298881531</v>
       </c>
       <c r="H54" t="n">
         <v>485506</v>
@@ -1993,7 +1993,7 @@
         <v>2.73680210113525</v>
       </c>
       <c r="G56" t="n">
-        <v>2.69038820266724</v>
+        <v>2.69038844108582</v>
       </c>
       <c r="H56" t="n">
         <v>159844</v>
@@ -2109,7 +2109,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G60" t="n">
-        <v>2.566157579422</v>
+        <v>2.56615734100342</v>
       </c>
       <c r="H60" t="n">
         <v>103412</v>
@@ -2341,7 +2341,7 @@
         <v>2.97326803207397</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92284369468689</v>
+        <v>2.92284393310547</v>
       </c>
       <c r="H68" t="n">
         <v>318172</v>
@@ -2428,7 +2428,7 @@
         <v>2.87790608406067</v>
       </c>
       <c r="G71" t="n">
-        <v>2.82909941673279</v>
+        <v>2.82909917831421</v>
       </c>
       <c r="H71" t="n">
         <v>190823</v>
@@ -2457,7 +2457,7 @@
         <v>2.87480497360229</v>
       </c>
       <c r="G72" t="n">
-        <v>2.82605051994324</v>
+        <v>2.82605075836182</v>
       </c>
       <c r="H72" t="n">
         <v>241086</v>
@@ -2544,7 +2544,7 @@
         <v>2.81975889205933</v>
       </c>
       <c r="G75" t="n">
-        <v>2.77193832397461</v>
+        <v>2.77193808555603</v>
       </c>
       <c r="H75" t="n">
         <v>310240</v>
@@ -2573,7 +2573,7 @@
         <v>2.77634191513062</v>
       </c>
       <c r="G76" t="n">
-        <v>2.72925734519958</v>
+        <v>2.72925758361816</v>
       </c>
       <c r="H76" t="n">
         <v>301835</v>
@@ -2602,7 +2602,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G77" t="n">
-        <v>2.7330687046051</v>
+        <v>2.73306894302368</v>
       </c>
       <c r="H77" t="n">
         <v>155939</v>
@@ -2718,7 +2718,7 @@
         <v>2.79727506637573</v>
       </c>
       <c r="G81" t="n">
-        <v>2.74983549118042</v>
+        <v>2.749835729599</v>
       </c>
       <c r="H81" t="n">
         <v>168823</v>
@@ -2979,7 +2979,7 @@
         <v>2.5476291179657</v>
       </c>
       <c r="G90" t="n">
-        <v>2.50442337989807</v>
+        <v>2.50442361831665</v>
       </c>
       <c r="H90" t="n">
         <v>137592</v>
@@ -3095,7 +3095,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G94" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H94" t="n">
         <v>593089</v>
@@ -3153,7 +3153,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G96" t="n">
-        <v>2.7330687046051</v>
+        <v>2.73306894302368</v>
       </c>
       <c r="H96" t="n">
         <v>193495</v>
@@ -3182,7 +3182,7 @@
         <v>2.94070506095886</v>
       </c>
       <c r="G97" t="n">
-        <v>2.89083313941956</v>
+        <v>2.89083337783813</v>
       </c>
       <c r="H97" t="n">
         <v>678677</v>
@@ -3298,7 +3298,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G101" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H101" t="n">
         <v>97675</v>
@@ -3385,7 +3385,7 @@
         <v>2.9693911075592</v>
       </c>
       <c r="G104" t="n">
-        <v>2.91903257369995</v>
+        <v>2.91903281211853</v>
       </c>
       <c r="H104" t="n">
         <v>94349</v>
@@ -3414,7 +3414,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G105" t="n">
-        <v>2.88244962692261</v>
+        <v>2.88244986534119</v>
       </c>
       <c r="H105" t="n">
         <v>76056</v>
@@ -3443,7 +3443,7 @@
         <v>2.8934121131897</v>
       </c>
       <c r="G106" t="n">
-        <v>2.84434223175049</v>
+        <v>2.84434247016907</v>
       </c>
       <c r="H106" t="n">
         <v>160927</v>
@@ -3472,7 +3472,7 @@
         <v>2.94458198547363</v>
       </c>
       <c r="G107" t="n">
-        <v>2.89464426040649</v>
+        <v>2.89464449882507</v>
       </c>
       <c r="H107" t="n">
         <v>122794</v>
@@ -3530,7 +3530,7 @@
         <v>2.91201901435852</v>
       </c>
       <c r="G109" t="n">
-        <v>2.86263346672058</v>
+        <v>2.86263370513916</v>
       </c>
       <c r="H109" t="n">
         <v>97079</v>
@@ -3617,7 +3617,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G112" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H112" t="n">
         <v>87752</v>
@@ -3704,7 +3704,7 @@
         <v>2.64919304847717</v>
       </c>
       <c r="G115" t="n">
-        <v>2.60426497459412</v>
+        <v>2.6042652130127</v>
       </c>
       <c r="H115" t="n">
         <v>158384</v>
@@ -3849,7 +3849,7 @@
         <v>2.90581703186035</v>
       </c>
       <c r="G120" t="n">
-        <v>2.85653686523438</v>
+        <v>2.8565366268158</v>
       </c>
       <c r="H120" t="n">
         <v>140706</v>
@@ -3907,7 +3907,7 @@
         <v>2.80502796173096</v>
       </c>
       <c r="G122" t="n">
-        <v>2.75745701789856</v>
+        <v>2.75745725631714</v>
       </c>
       <c r="H122" t="n">
         <v>103410</v>
@@ -4110,7 +4110,7 @@
         <v>2.53057289123535</v>
       </c>
       <c r="G129" t="n">
-        <v>2.48765635490417</v>
+        <v>2.48765659332275</v>
       </c>
       <c r="H129" t="n">
         <v>122546</v>
@@ -4197,7 +4197,7 @@
         <v>2.43831205368042</v>
       </c>
       <c r="G132" t="n">
-        <v>2.39696049690247</v>
+        <v>2.39696025848389</v>
       </c>
       <c r="H132" t="n">
         <v>324481</v>
@@ -4255,7 +4255,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56082224845886</v>
+        <v>2.56082248687744</v>
       </c>
       <c r="H134" t="n">
         <v>116496</v>
@@ -4284,7 +4284,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56082224845886</v>
+        <v>2.56082248687744</v>
       </c>
       <c r="H135" t="n">
         <v>77002</v>
@@ -4371,7 +4371,7 @@
         <v>2.7057900428772</v>
       </c>
       <c r="G138" t="n">
-        <v>2.65990233421326</v>
+        <v>2.65990209579468</v>
       </c>
       <c r="H138" t="n">
         <v>227795</v>
@@ -4516,7 +4516,7 @@
         <v>2.89186191558838</v>
       </c>
       <c r="G143" t="n">
-        <v>2.84281826019287</v>
+        <v>2.84281849861145</v>
       </c>
       <c r="H143" t="n">
         <v>433122</v>
@@ -4545,7 +4545,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G144" t="n">
-        <v>2.88244962692261</v>
+        <v>2.88244986534119</v>
       </c>
       <c r="H144" t="n">
         <v>504151</v>
@@ -4632,7 +4632,7 @@
         <v>2.95310997962952</v>
       </c>
       <c r="G147" t="n">
-        <v>2.90302753448486</v>
+        <v>2.90302777290344</v>
       </c>
       <c r="H147" t="n">
         <v>124606</v>
@@ -4661,7 +4661,7 @@
         <v>2.9918749332428</v>
       </c>
       <c r="G148" t="n">
-        <v>2.94113516807556</v>
+        <v>2.94113540649414</v>
       </c>
       <c r="H148" t="n">
         <v>115180</v>
@@ -4719,7 +4719,7 @@
         <v>2.96551489830017</v>
       </c>
       <c r="G150" t="n">
-        <v>2.91522216796875</v>
+        <v>2.91522240638733</v>
       </c>
       <c r="H150" t="n">
         <v>107908</v>
@@ -4748,7 +4748,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87330460548401</v>
+        <v>2.87330436706543</v>
       </c>
       <c r="H151" t="n">
         <v>112608</v>
@@ -4835,7 +4835,7 @@
         <v>2.93527793884277</v>
       </c>
       <c r="G154" t="n">
-        <v>2.88549828529358</v>
+        <v>2.885498046875</v>
       </c>
       <c r="H154" t="n">
         <v>98584</v>
@@ -4922,7 +4922,7 @@
         <v>2.95388507843018</v>
       </c>
       <c r="G157" t="n">
-        <v>2.90378975868225</v>
+        <v>2.90378952026367</v>
       </c>
       <c r="H157" t="n">
         <v>130813</v>
@@ -4980,7 +4980,7 @@
         <v>3.05855107307434</v>
       </c>
       <c r="G159" t="n">
-        <v>3.006680727005</v>
+        <v>3.00668048858643</v>
       </c>
       <c r="H159" t="n">
         <v>293073</v>
@@ -5009,7 +5009,7 @@
         <v>3.0221118927002</v>
       </c>
       <c r="G160" t="n">
-        <v>2.97085952758789</v>
+        <v>2.97085928916931</v>
       </c>
       <c r="H160" t="n">
         <v>76130</v>
@@ -5067,7 +5067,7 @@
         <v>2.97404289245605</v>
       </c>
       <c r="G162" t="n">
-        <v>2.9236056804657</v>
+        <v>2.92360544204712</v>
       </c>
       <c r="H162" t="n">
         <v>29083</v>
@@ -5125,7 +5125,7 @@
         <v>3.02676391601562</v>
       </c>
       <c r="G164" t="n">
-        <v>2.97543239593506</v>
+        <v>2.97543263435364</v>
       </c>
       <c r="H164" t="n">
         <v>68786</v>
@@ -5444,7 +5444,7 @@
         <v>3.35936594009399</v>
       </c>
       <c r="G175" t="n">
-        <v>3.30239415168762</v>
+        <v>3.30239391326904</v>
       </c>
       <c r="H175" t="n">
         <v>136675</v>
@@ -5531,7 +5531,7 @@
         <v>3.38262510299683</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32525873184204</v>
+        <v>3.32525849342346</v>
       </c>
       <c r="H178" t="n">
         <v>282670</v>
@@ -5560,7 +5560,7 @@
         <v>3.31750011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>3.26123809814453</v>
+        <v>3.26123833656311</v>
       </c>
       <c r="H179" t="n">
         <v>124150</v>
@@ -5647,7 +5647,7 @@
         <v>3.23764491081238</v>
       </c>
       <c r="G182" t="n">
-        <v>3.18273711204529</v>
+        <v>3.18273735046387</v>
       </c>
       <c r="H182" t="n">
         <v>146776</v>
@@ -5705,7 +5705,7 @@
         <v>3.20430707931519</v>
       </c>
       <c r="G184" t="n">
-        <v>3.14996457099915</v>
+        <v>3.14996480941772</v>
       </c>
       <c r="H184" t="n">
         <v>75785</v>
@@ -5821,7 +5821,7 @@
         <v>3.35083794593811</v>
       </c>
       <c r="G188" t="n">
-        <v>3.29401063919067</v>
+        <v>3.29401040077209</v>
       </c>
       <c r="H188" t="n">
         <v>126105</v>
@@ -5937,7 +5937,7 @@
         <v>3.35548996925354</v>
       </c>
       <c r="G192" t="n">
-        <v>3.29858350753784</v>
+        <v>3.29858374595642</v>
       </c>
       <c r="H192" t="n">
         <v>204931</v>
@@ -6082,7 +6082,7 @@
         <v>3.3570408821106</v>
       </c>
       <c r="G197" t="n">
-        <v>3.3001081943512</v>
+        <v>3.30010843276978</v>
       </c>
       <c r="H197" t="n">
         <v>92448</v>
@@ -6140,7 +6140,7 @@
         <v>3.33067989349365</v>
       </c>
       <c r="G199" t="n">
-        <v>3.27419447898865</v>
+        <v>3.27419424057007</v>
       </c>
       <c r="H199" t="n">
         <v>109612</v>
@@ -6169,7 +6169,7 @@
         <v>3.35238909721375</v>
       </c>
       <c r="G200" t="n">
-        <v>3.29553532600403</v>
+        <v>3.29553556442261</v>
       </c>
       <c r="H200" t="n">
         <v>72532</v>
@@ -6343,7 +6343,7 @@
         <v>3.34308505058289</v>
       </c>
       <c r="G206" t="n">
-        <v>3.28638935089111</v>
+        <v>3.28638911247253</v>
       </c>
       <c r="H206" t="n">
         <v>211723</v>
@@ -6575,7 +6575,7 @@
         <v>3.19965505599976</v>
       </c>
       <c r="G214" t="n">
-        <v>3.1453914642334</v>
+        <v>3.14539170265198</v>
       </c>
       <c r="H214" t="n">
         <v>46695</v>
@@ -6604,7 +6604,7 @@
         <v>3.20353198051453</v>
       </c>
       <c r="G215" t="n">
-        <v>3.14920258522034</v>
+        <v>3.14920282363892</v>
       </c>
       <c r="H215" t="n">
         <v>20449</v>
@@ -6720,7 +6720,7 @@
         <v>3.04226899147034</v>
       </c>
       <c r="G219" t="n">
-        <v>2.9906747341156</v>
+        <v>2.99067449569702</v>
       </c>
       <c r="H219" t="n">
         <v>119131</v>
@@ -6778,7 +6778,7 @@
         <v>3.23299288749695</v>
       </c>
       <c r="G221" t="n">
-        <v>3.17816400527954</v>
+        <v>3.17816424369812</v>
       </c>
       <c r="H221" t="n">
         <v>190310</v>
@@ -6807,7 +6807,7 @@
         <v>3.24384689331055</v>
       </c>
       <c r="G222" t="n">
-        <v>3.18883419036865</v>
+        <v>3.18883395195007</v>
       </c>
       <c r="H222" t="n">
         <v>201688</v>
@@ -6836,7 +6836,7 @@
         <v>3.37254691123962</v>
       </c>
       <c r="G223" t="n">
-        <v>3.31535124778748</v>
+        <v>3.31535148620605</v>
       </c>
       <c r="H223" t="n">
         <v>480056</v>
@@ -7010,7 +7010,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G229" t="n">
-        <v>3.1934072971344</v>
+        <v>3.19340705871582</v>
       </c>
       <c r="H229" t="n">
         <v>91423</v>
@@ -7068,7 +7068,7 @@
         <v>3.24617290496826</v>
       </c>
       <c r="G231" t="n">
-        <v>3.19112062454224</v>
+        <v>3.19112038612366</v>
       </c>
       <c r="H231" t="n">
         <v>60078</v>
@@ -7097,7 +7097,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G232" t="n">
-        <v>3.18197441101074</v>
+        <v>3.18197464942932</v>
       </c>
       <c r="H232" t="n">
         <v>46953</v>
@@ -7213,7 +7213,7 @@
         <v>3.22601509094238</v>
       </c>
       <c r="G236" t="n">
-        <v>3.17130470275879</v>
+        <v>3.17130446434021</v>
       </c>
       <c r="H236" t="n">
         <v>92031</v>
@@ -7242,7 +7242,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G237" t="n">
-        <v>3.1934072971344</v>
+        <v>3.19340705871582</v>
       </c>
       <c r="H237" t="n">
         <v>65003</v>
@@ -7329,7 +7329,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G240" t="n">
-        <v>3.18197441101074</v>
+        <v>3.18197464942932</v>
       </c>
       <c r="H240" t="n">
         <v>117377</v>
@@ -7503,7 +7503,7 @@
         <v>3.26167893409729</v>
       </c>
       <c r="G246" t="n">
-        <v>3.20636343955994</v>
+        <v>3.20636367797852</v>
       </c>
       <c r="H246" t="n">
         <v>207240</v>
@@ -7532,7 +7532,7 @@
         <v>3.32602906227112</v>
       </c>
       <c r="G247" t="n">
-        <v>3.2696225643158</v>
+        <v>3.26962232589722</v>
       </c>
       <c r="H247" t="n">
         <v>91899</v>
@@ -7677,7 +7677,7 @@
         <v>3.5446629524231</v>
       </c>
       <c r="G252" t="n">
-        <v>3.48454833030701</v>
+        <v>3.48454856872559</v>
       </c>
       <c r="H252" t="n">
         <v>194782</v>
@@ -7851,7 +7851,7 @@
         <v>3.721431016922</v>
       </c>
       <c r="G258" t="n">
-        <v>3.65831851959229</v>
+        <v>3.65831875801086</v>
       </c>
       <c r="H258" t="n">
         <v>319621</v>
@@ -7909,7 +7909,7 @@
         <v>4.00053787231445</v>
       </c>
       <c r="G260" t="n">
-        <v>3.93269228935242</v>
+        <v>3.93269205093384</v>
       </c>
       <c r="H260" t="n">
         <v>648070</v>
@@ -8083,7 +8083,7 @@
         <v>4.05093193054199</v>
       </c>
       <c r="G266" t="n">
-        <v>3.98223161697388</v>
+        <v>3.9822313785553</v>
       </c>
       <c r="H266" t="n">
         <v>236555</v>
@@ -8257,7 +8257,7 @@
         <v>4.18661022186279</v>
       </c>
       <c r="G272" t="n">
-        <v>4.11560916900635</v>
+        <v>4.11560869216919</v>
       </c>
       <c r="H272" t="n">
         <v>1412380</v>
@@ -8286,7 +8286,7 @@
         <v>4.27964496612549</v>
       </c>
       <c r="G273" t="n">
-        <v>4.20706558227539</v>
+        <v>4.20706605911255</v>
       </c>
       <c r="H273" t="n">
         <v>1069890</v>
@@ -8315,7 +8315,7 @@
         <v>4.43858098983765</v>
       </c>
       <c r="G274" t="n">
-        <v>4.36330604553223</v>
+        <v>4.36330652236938</v>
       </c>
       <c r="H274" t="n">
         <v>723596</v>
@@ -8344,7 +8344,7 @@
         <v>4.442458152771</v>
       </c>
       <c r="G275" t="n">
-        <v>4.36711740493774</v>
+        <v>4.3671178817749</v>
       </c>
       <c r="H275" t="n">
         <v>567984</v>
@@ -8402,7 +8402,7 @@
         <v>4.3610520362854</v>
       </c>
       <c r="G277" t="n">
-        <v>4.2870922088623</v>
+        <v>4.28709268569946</v>
       </c>
       <c r="H277" t="n">
         <v>208145</v>
@@ -8431,7 +8431,7 @@
         <v>4.25251007080078</v>
       </c>
       <c r="G278" t="n">
-        <v>4.18039083480835</v>
+        <v>4.18039131164551</v>
       </c>
       <c r="H278" t="n">
         <v>280129</v>
@@ -8547,7 +8547,7 @@
         <v>4.33779287338257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.26422786712646</v>
+        <v>4.26422739028931</v>
       </c>
       <c r="H282" t="n">
         <v>221629</v>
@@ -8605,7 +8605,7 @@
         <v>4.27189207077026</v>
       </c>
       <c r="G284" t="n">
-        <v>4.19944429397583</v>
+        <v>4.19944477081299</v>
       </c>
       <c r="H284" t="n">
         <v>219679</v>
@@ -8721,7 +8721,7 @@
         <v>4.12846183776855</v>
       </c>
       <c r="G288" t="n">
-        <v>4.05844640731812</v>
+        <v>4.05844688415527</v>
       </c>
       <c r="H288" t="n">
         <v>181443</v>
@@ -8808,7 +8808,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G291" t="n">
-        <v>4.52716970443726</v>
+        <v>4.5271692276001</v>
       </c>
       <c r="H291" t="n">
         <v>1365540</v>
@@ -8866,7 +8866,7 @@
         <v>4.52386379241943</v>
       </c>
       <c r="G293" t="n">
-        <v>4.44714307785034</v>
+        <v>4.44714260101318</v>
       </c>
       <c r="H293" t="n">
         <v>403894</v>
@@ -8982,7 +8982,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G297" t="n">
-        <v>4.52716970443726</v>
+        <v>4.5271692276001</v>
       </c>
       <c r="H297" t="n">
         <v>367010</v>
@@ -9040,7 +9040,7 @@
         <v>4.64403486251831</v>
       </c>
       <c r="G299" t="n">
-        <v>4.56527614593506</v>
+        <v>4.5652756690979</v>
       </c>
       <c r="H299" t="n">
         <v>165971</v>
@@ -9098,7 +9098,7 @@
         <v>4.88437795639038</v>
       </c>
       <c r="G301" t="n">
-        <v>4.80154323577881</v>
+        <v>4.80154275894165</v>
       </c>
       <c r="H301" t="n">
         <v>885013</v>
@@ -9127,7 +9127,7 @@
         <v>5.09758520126343</v>
       </c>
       <c r="G302" t="n">
-        <v>5.01113414764404</v>
+        <v>5.0111346244812</v>
       </c>
       <c r="H302" t="n">
         <v>1328330</v>
@@ -9388,7 +9388,7 @@
         <v>5.02780818939209</v>
       </c>
       <c r="G311" t="n">
-        <v>4.94254112243652</v>
+        <v>4.94254064559937</v>
       </c>
       <c r="H311" t="n">
         <v>342293</v>
@@ -9446,7 +9446,7 @@
         <v>5.06657314300537</v>
       </c>
       <c r="G313" t="n">
-        <v>4.98064851760864</v>
+        <v>4.98064804077148</v>
       </c>
       <c r="H313" t="n">
         <v>238791</v>
@@ -9533,7 +9533,7 @@
         <v>5.11309099197388</v>
       </c>
       <c r="G316" t="n">
-        <v>5.02637720108032</v>
+        <v>5.02637767791748</v>
       </c>
       <c r="H316" t="n">
         <v>297516</v>
@@ -9562,7 +9562,7 @@
         <v>5.19449710845947</v>
       </c>
       <c r="G317" t="n">
-        <v>5.10640287399292</v>
+        <v>5.10640239715576</v>
       </c>
       <c r="H317" t="n">
         <v>464423</v>
@@ -9649,7 +9649,7 @@
         <v>5.21388006210327</v>
       </c>
       <c r="G320" t="n">
-        <v>5.12545680999756</v>
+        <v>5.12545728683472</v>
       </c>
       <c r="H320" t="n">
         <v>546852</v>
@@ -9707,7 +9707,7 @@
         <v>5.48523378372192</v>
       </c>
       <c r="G322" t="n">
-        <v>5.39220905303955</v>
+        <v>5.39220857620239</v>
       </c>
       <c r="H322" t="n">
         <v>940314</v>
@@ -9823,7 +9823,7 @@
         <v>6.08609008789062</v>
       </c>
       <c r="G326" t="n">
-        <v>5.98287534713745</v>
+        <v>5.98287487030029</v>
       </c>
       <c r="H326" t="n">
         <v>1806086</v>
@@ -9881,7 +9881,7 @@
         <v>6.11710214614868</v>
       </c>
       <c r="G328" t="n">
-        <v>6.01336145401001</v>
+        <v>6.01336097717285</v>
       </c>
       <c r="H328" t="n">
         <v>1777020</v>
@@ -10026,7 +10026,7 @@
         <v>6.20238494873047</v>
       </c>
       <c r="G333" t="n">
-        <v>6.09719753265381</v>
+        <v>6.09719800949097</v>
       </c>
       <c r="H333" t="n">
         <v>1738052</v>
@@ -10171,7 +10171,7 @@
         <v>7.13661909103394</v>
       </c>
       <c r="G338" t="n">
-        <v>7.01558780670166</v>
+        <v>7.01558828353882</v>
       </c>
       <c r="H338" t="n">
         <v>2024444</v>
@@ -10200,7 +10200,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G339" t="n">
-        <v>6.72216033935547</v>
+        <v>6.72215986251831</v>
       </c>
       <c r="H339" t="n">
         <v>1597497</v>
@@ -10316,7 +10316,7 @@
         <v>7.07847213745117</v>
       </c>
       <c r="G343" t="n">
-        <v>6.95842742919922</v>
+        <v>6.95842695236206</v>
       </c>
       <c r="H343" t="n">
         <v>1152592</v>
@@ -10345,7 +10345,7 @@
         <v>7.02420091629028</v>
       </c>
       <c r="G344" t="n">
-        <v>6.9050760269165</v>
+        <v>6.90507650375366</v>
       </c>
       <c r="H344" t="n">
         <v>757764</v>
@@ -10403,7 +10403,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G346" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H346" t="n">
         <v>1253565</v>
@@ -10432,7 +10432,7 @@
         <v>7.40797281265259</v>
       </c>
       <c r="G347" t="n">
-        <v>7.28233957290649</v>
+        <v>7.28234004974365</v>
       </c>
       <c r="H347" t="n">
         <v>953069</v>
@@ -10577,7 +10577,7 @@
         <v>6.38845586776733</v>
       </c>
       <c r="G352" t="n">
-        <v>6.28011322021484</v>
+        <v>6.28011274337769</v>
       </c>
       <c r="H352" t="n">
         <v>1189739</v>
@@ -10751,7 +10751,7 @@
         <v>7.03583002090454</v>
       </c>
       <c r="G358" t="n">
-        <v>6.91650819778442</v>
+        <v>6.91650867462158</v>
       </c>
       <c r="H358" t="n">
         <v>557993</v>
@@ -10809,7 +10809,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G360" t="n">
-        <v>6.72216033935547</v>
+        <v>6.72215986251831</v>
       </c>
       <c r="H360" t="n">
         <v>383136</v>
@@ -11070,7 +11070,7 @@
         <v>6.86526489257812</v>
       </c>
       <c r="G369" t="n">
-        <v>6.74883556365967</v>
+        <v>6.74883604049683</v>
       </c>
       <c r="H369" t="n">
         <v>381623</v>
@@ -11099,7 +11099,7 @@
         <v>6.77222919464111</v>
       </c>
       <c r="G370" t="n">
-        <v>6.65737819671631</v>
+        <v>6.65737771987915</v>
       </c>
       <c r="H370" t="n">
         <v>410334</v>
@@ -11157,7 +11157,7 @@
         <v>6.76835203170776</v>
       </c>
       <c r="G372" t="n">
-        <v>6.65356683731079</v>
+        <v>6.65356636047363</v>
       </c>
       <c r="H372" t="n">
         <v>220177</v>
@@ -11447,7 +11447,7 @@
         <v>7.37308502197266</v>
       </c>
       <c r="G382" t="n">
-        <v>7.24804401397705</v>
+        <v>7.24804353713989</v>
       </c>
       <c r="H382" t="n">
         <v>2466801</v>
@@ -11563,7 +11563,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G386" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H386" t="n">
         <v>674582</v>
@@ -11679,7 +11679,7 @@
         <v>7.72972202301025</v>
       </c>
       <c r="G390" t="n">
-        <v>7.5986328125</v>
+        <v>7.59863233566284</v>
       </c>
       <c r="H390" t="n">
         <v>446172</v>
@@ -11737,7 +11737,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G392" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H392" t="n">
         <v>528987</v>
@@ -11795,7 +11795,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G394" t="n">
-        <v>8.19310855865479</v>
+        <v>8.1931095123291</v>
       </c>
       <c r="H394" t="n">
         <v>618520</v>
@@ -11824,7 +11824,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G395" t="n">
-        <v>8.3607816696167</v>
+        <v>8.36078262329102</v>
       </c>
       <c r="H395" t="n">
         <v>589330</v>
@@ -11911,7 +11911,7 @@
         <v>8.0708532333374</v>
       </c>
       <c r="G398" t="n">
-        <v>7.93397903442383</v>
+        <v>7.93397808074951</v>
       </c>
       <c r="H398" t="n">
         <v>1105464</v>
@@ -11940,7 +11940,7 @@
         <v>8.03208827972412</v>
       </c>
       <c r="G399" t="n">
-        <v>7.89587116241455</v>
+        <v>7.89587068557739</v>
       </c>
       <c r="H399" t="n">
         <v>704166</v>
@@ -12027,7 +12027,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G402" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H402" t="n">
         <v>4317226</v>
@@ -12230,7 +12230,7 @@
         <v>7.67545080184937</v>
       </c>
       <c r="G409" t="n">
-        <v>7.54528141021729</v>
+        <v>7.54528188705444</v>
       </c>
       <c r="H409" t="n">
         <v>485472</v>
@@ -12317,7 +12317,7 @@
         <v>7.30718517303467</v>
       </c>
       <c r="G412" t="n">
-        <v>7.18326139450073</v>
+        <v>7.18326187133789</v>
       </c>
       <c r="H412" t="n">
         <v>778353</v>
@@ -12462,7 +12462,7 @@
         <v>7.07071876525879</v>
       </c>
       <c r="G417" t="n">
-        <v>6.9508056640625</v>
+        <v>6.95080518722534</v>
       </c>
       <c r="H417" t="n">
         <v>221650</v>
@@ -12520,7 +12520,7 @@
         <v>6.985435962677</v>
       </c>
       <c r="G419" t="n">
-        <v>6.86696863174438</v>
+        <v>6.86696910858154</v>
       </c>
       <c r="H419" t="n">
         <v>607996</v>
@@ -12607,7 +12607,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G422" t="n">
-        <v>7.27852964401245</v>
+        <v>7.27853012084961</v>
       </c>
       <c r="H422" t="n">
         <v>880611</v>
@@ -12723,7 +12723,7 @@
         <v>7.17925977706909</v>
       </c>
       <c r="G426" t="n">
-        <v>7.05750608444214</v>
+        <v>7.05750560760498</v>
       </c>
       <c r="H426" t="n">
         <v>1555624</v>
@@ -12752,7 +12752,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G427" t="n">
-        <v>7.30901575088501</v>
+        <v>7.30901622772217</v>
       </c>
       <c r="H427" t="n">
         <v>1335622</v>
@@ -12868,7 +12868,7 @@
         <v>8.00107669830322</v>
       </c>
       <c r="G431" t="n">
-        <v>7.86538553237915</v>
+        <v>7.86538505554199</v>
       </c>
       <c r="H431" t="n">
         <v>781944</v>
@@ -12926,7 +12926,7 @@
         <v>7.7142162322998</v>
       </c>
       <c r="G433" t="n">
-        <v>7.58338928222656</v>
+        <v>7.58338975906372</v>
       </c>
       <c r="H433" t="n">
         <v>526446</v>
@@ -12955,7 +12955,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G434" t="n">
-        <v>7.94922161102295</v>
+        <v>7.94922113418579</v>
       </c>
       <c r="H434" t="n">
         <v>1316387</v>
@@ -13071,7 +13071,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G438" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H438" t="n">
         <v>447832</v>
@@ -13129,7 +13129,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G440" t="n">
-        <v>7.94922161102295</v>
+        <v>7.94922113418579</v>
       </c>
       <c r="H440" t="n">
         <v>478643</v>
@@ -13158,7 +13158,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G441" t="n">
-        <v>7.85014200210571</v>
+        <v>7.85014247894287</v>
       </c>
       <c r="H441" t="n">
         <v>375921</v>
@@ -13303,7 +13303,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G446" t="n">
-        <v>8.3607816696167</v>
+        <v>8.36078262329102</v>
       </c>
       <c r="H446" t="n">
         <v>2904190</v>
@@ -13332,7 +13332,7 @@
         <v>8.06309986114502</v>
       </c>
       <c r="G447" t="n">
-        <v>7.92635583877563</v>
+        <v>7.92635631561279</v>
       </c>
       <c r="H447" t="n">
         <v>4805532</v>
@@ -13448,7 +13448,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G451" t="n">
-        <v>7.36617708206177</v>
+        <v>7.36617660522461</v>
       </c>
       <c r="H451" t="n">
         <v>1207097</v>
@@ -13477,7 +13477,7 @@
         <v>7.58629179000854</v>
       </c>
       <c r="G452" t="n">
-        <v>7.45763444900513</v>
+        <v>7.45763492584229</v>
       </c>
       <c r="H452" t="n">
         <v>1486373</v>
@@ -13564,7 +13564,7 @@
         <v>7.51651477813721</v>
       </c>
       <c r="G455" t="n">
-        <v>7.38904094696045</v>
+        <v>7.38904142379761</v>
       </c>
       <c r="H455" t="n">
         <v>957250</v>
@@ -13680,7 +13680,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G459" t="n">
-        <v>7.31663703918457</v>
+        <v>7.31663751602173</v>
       </c>
       <c r="H459" t="n">
         <v>430589</v>
@@ -13709,7 +13709,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G460" t="n">
-        <v>7.27852964401245</v>
+        <v>7.27853012084961</v>
       </c>
       <c r="H460" t="n">
         <v>425428</v>
@@ -13796,7 +13796,7 @@
         <v>7.50100898742676</v>
       </c>
       <c r="G463" t="n">
-        <v>7.37379837036133</v>
+        <v>7.37379789352417</v>
       </c>
       <c r="H463" t="n">
         <v>490050</v>
@@ -13825,7 +13825,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G464" t="n">
-        <v>7.31663703918457</v>
+        <v>7.31663751602173</v>
       </c>
       <c r="H464" t="n">
         <v>447048</v>
@@ -13883,7 +13883,7 @@
         <v>7.44673776626587</v>
       </c>
       <c r="G466" t="n">
-        <v>7.32044696807861</v>
+        <v>7.32044744491577</v>
       </c>
       <c r="H466" t="n">
         <v>650810</v>
@@ -13912,7 +13912,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G467" t="n">
-        <v>7.36617708206177</v>
+        <v>7.36617660522461</v>
       </c>
       <c r="H467" t="n">
         <v>504330</v>
@@ -14028,7 +14028,7 @@
         <v>8.54378509521484</v>
       </c>
       <c r="G471" t="n">
-        <v>8.39888954162598</v>
+        <v>8.39889049530029</v>
       </c>
       <c r="H471" t="n">
         <v>1645276</v>
@@ -14057,7 +14057,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G472" t="n">
-        <v>8.19310855865479</v>
+        <v>8.1931095123291</v>
       </c>
       <c r="H472" t="n">
         <v>1740272</v>
@@ -14115,7 +14115,7 @@
         <v>8.24141883850098</v>
       </c>
       <c r="G474" t="n">
-        <v>8.10165119171143</v>
+        <v>8.10165214538574</v>
       </c>
       <c r="H474" t="n">
         <v>648959</v>
@@ -14144,7 +14144,7 @@
         <v>8.21040725708008</v>
       </c>
       <c r="G475" t="n">
-        <v>8.07116603851318</v>
+        <v>8.07116508483887</v>
       </c>
       <c r="H475" t="n">
         <v>437746</v>
@@ -14231,7 +14231,7 @@
         <v>8.38872623443604</v>
       </c>
       <c r="G478" t="n">
-        <v>8.24646091461182</v>
+        <v>8.2464599609375</v>
       </c>
       <c r="H478" t="n">
         <v>2636241</v>
@@ -14289,7 +14289,7 @@
         <v>8.87716293334961</v>
       </c>
       <c r="G480" t="n">
-        <v>8.72661304473877</v>
+        <v>8.72661399841309</v>
       </c>
       <c r="H480" t="n">
         <v>2854751</v>
@@ -14405,7 +14405,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G484" t="n">
-        <v>8.88666534423828</v>
+        <v>8.8866662979126</v>
       </c>
       <c r="H484" t="n">
         <v>943241</v>
@@ -14434,7 +14434,7 @@
         <v>9.04772853851318</v>
       </c>
       <c r="G485" t="n">
-        <v>8.894287109375</v>
+        <v>8.89428615570068</v>
       </c>
       <c r="H485" t="n">
         <v>875881</v>
@@ -14521,7 +14521,7 @@
         <v>9.17177677154541</v>
       </c>
       <c r="G488" t="n">
-        <v>9.01623153686523</v>
+        <v>9.01623058319092</v>
       </c>
       <c r="H488" t="n">
         <v>886825</v>
@@ -14782,7 +14782,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G497" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H497" t="n">
         <v>1414410</v>
@@ -14898,7 +14898,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G501" t="n">
-        <v>9.96129703521729</v>
+        <v>9.96129608154297</v>
       </c>
       <c r="H501" t="n">
         <v>845538</v>
@@ -14956,7 +14956,7 @@
         <v>10.1796636581421</v>
       </c>
       <c r="G503" t="n">
-        <v>10.0070247650146</v>
+        <v>10.007025718689</v>
       </c>
       <c r="H503" t="n">
         <v>832310</v>
@@ -15043,7 +15043,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G506" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H506" t="n">
         <v>913020</v>
@@ -15072,7 +15072,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G507" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H507" t="n">
         <v>366112</v>
@@ -15159,7 +15159,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G510" t="n">
-        <v>9.79362297058105</v>
+        <v>9.79362392425537</v>
       </c>
       <c r="H510" t="n">
         <v>238182</v>
@@ -15188,7 +15188,7 @@
         <v>9.70673179626465</v>
       </c>
       <c r="G511" t="n">
-        <v>9.54211330413818</v>
+        <v>9.5421142578125</v>
       </c>
       <c r="H511" t="n">
         <v>455430</v>
@@ -15246,7 +15246,7 @@
         <v>10.1486520767212</v>
       </c>
       <c r="G513" t="n">
-        <v>9.97653961181641</v>
+        <v>9.97653865814209</v>
       </c>
       <c r="H513" t="n">
         <v>442390</v>
@@ -15304,7 +15304,7 @@
         <v>10.5285491943359</v>
       </c>
       <c r="G515" t="n">
-        <v>10.3499937057495</v>
+        <v>10.3499946594238</v>
       </c>
       <c r="H515" t="n">
         <v>969702</v>
@@ -15420,7 +15420,7 @@
         <v>11.2108106613159</v>
       </c>
       <c r="G519" t="n">
-        <v>11.0206851959229</v>
+        <v>11.0206842422485</v>
       </c>
       <c r="H519" t="n">
         <v>1860164</v>
@@ -15536,7 +15536,7 @@
         <v>11.265082359314</v>
       </c>
       <c r="G523" t="n">
-        <v>11.0740356445312</v>
+        <v>11.0740365982056</v>
       </c>
       <c r="H523" t="n">
         <v>1216725</v>
@@ -15594,7 +15594,7 @@
         <v>11.3658714294434</v>
       </c>
       <c r="G525" t="n">
-        <v>11.17311668396</v>
+        <v>11.1731157302856</v>
       </c>
       <c r="H525" t="n">
         <v>686072</v>
@@ -15623,7 +15623,7 @@
         <v>11.3426122665405</v>
       </c>
       <c r="G526" t="n">
-        <v>11.1502504348755</v>
+        <v>11.1502513885498</v>
       </c>
       <c r="H526" t="n">
         <v>701379</v>
@@ -15681,7 +15681,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G528" t="n">
-        <v>10.8225259780884</v>
+        <v>10.8225269317627</v>
       </c>
       <c r="H528" t="n">
         <v>764225</v>
@@ -15855,7 +15855,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G534" t="n">
-        <v>10.8225259780884</v>
+        <v>10.8225269317627</v>
       </c>
       <c r="H534" t="n">
         <v>1206401</v>
@@ -16029,7 +16029,7 @@
         <v>10.4200067520142</v>
       </c>
       <c r="G540" t="n">
-        <v>10.2432918548584</v>
+        <v>10.2432928085327</v>
       </c>
       <c r="H540" t="n">
         <v>1215961</v>
@@ -16058,7 +16058,7 @@
         <v>10.5052900314331</v>
       </c>
       <c r="G541" t="n">
-        <v>10.3271284103394</v>
+        <v>10.3271293640137</v>
       </c>
       <c r="H541" t="n">
         <v>891258</v>
@@ -16174,7 +16174,7 @@
         <v>10.4665250778198</v>
       </c>
       <c r="G545" t="n">
-        <v>10.2890214920044</v>
+        <v>10.2890224456787</v>
       </c>
       <c r="H545" t="n">
         <v>418757</v>
@@ -16290,7 +16290,7 @@
         <v>10.3889951705933</v>
       </c>
       <c r="G549" t="n">
-        <v>10.2128067016602</v>
+        <v>10.2128057479858</v>
       </c>
       <c r="H549" t="n">
         <v>499673</v>
@@ -16348,7 +16348,7 @@
         <v>9.9548282623291</v>
       </c>
       <c r="G551" t="n">
-        <v>9.78600215911865</v>
+        <v>9.78600311279297</v>
       </c>
       <c r="H551" t="n">
         <v>665775</v>
@@ -16464,7 +16464,7 @@
         <v>9.59043788909912</v>
       </c>
       <c r="G555" t="n">
-        <v>9.4277925491333</v>
+        <v>9.42779159545898</v>
       </c>
       <c r="H555" t="n">
         <v>595699</v>
@@ -16638,7 +16638,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G561" t="n">
-        <v>9.90032577514648</v>
+        <v>9.90032482147217</v>
       </c>
       <c r="H561" t="n">
         <v>502777</v>
@@ -16696,7 +16696,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G563" t="n">
-        <v>9.79362297058105</v>
+        <v>9.79362392425537</v>
       </c>
       <c r="H563" t="n">
         <v>395215</v>
@@ -16841,7 +16841,7 @@
         <v>10.1951704025269</v>
       </c>
       <c r="G568" t="n">
-        <v>10.0222682952881</v>
+        <v>10.0222692489624</v>
       </c>
       <c r="H568" t="n">
         <v>554786</v>
@@ -16957,7 +16957,7 @@
         <v>11.0247392654419</v>
       </c>
       <c r="G572" t="n">
-        <v>10.8377685546875</v>
+        <v>10.8377695083618</v>
       </c>
       <c r="H572" t="n">
         <v>977445</v>
@@ -17102,7 +17102,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G577" t="n">
-        <v>8.88666534423828</v>
+        <v>8.8866662979126</v>
       </c>
       <c r="H577" t="n">
         <v>1985248</v>
@@ -17189,7 +17189,7 @@
         <v>9.11750602722168</v>
       </c>
       <c r="G580" t="n">
-        <v>8.96288013458252</v>
+        <v>8.96288108825684</v>
       </c>
       <c r="H580" t="n">
         <v>887045</v>
@@ -17218,7 +17218,7 @@
         <v>9.45088386535645</v>
       </c>
       <c r="G581" t="n">
-        <v>9.29060554504395</v>
+        <v>9.29060459136963</v>
       </c>
       <c r="H581" t="n">
         <v>2141921</v>
@@ -17421,7 +17421,7 @@
         <v>9.83078002929688</v>
       </c>
       <c r="G588" t="n">
-        <v>9.66405868530273</v>
+        <v>9.66405773162842</v>
       </c>
       <c r="H588" t="n">
         <v>640698</v>
@@ -17595,7 +17595,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G594" t="n">
-        <v>9.96129703521729</v>
+        <v>9.96129608154297</v>
       </c>
       <c r="H594" t="n">
         <v>397609</v>
@@ -17711,7 +17711,7 @@
         <v>10.7068672180176</v>
       </c>
       <c r="G598" t="n">
-        <v>10.5252876281738</v>
+        <v>10.5252885818481</v>
       </c>
       <c r="H598" t="n">
         <v>677899</v>
@@ -17914,7 +17914,7 @@
         <v>10.4277601242065</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2509136199951</v>
+        <v>10.2509145736694</v>
       </c>
       <c r="H605" t="n">
         <v>654563</v>
@@ -17972,7 +17972,7 @@
         <v>10.0090990066528</v>
       </c>
       <c r="G607" t="n">
-        <v>9.83935356140137</v>
+        <v>9.83935260772705</v>
       </c>
       <c r="H607" t="n">
         <v>1087774</v>
@@ -80067,6 +80067,35 @@
         <v>1117959</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>12.0550003051758</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>12.1499996185303</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>11.8900003433228</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>12.0200004577637</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>12.0200004577637</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>1249563</v>
+      </c>
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -80099,6 +80099,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>12.0200004577637</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>12.4399995803833</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>11.9899997711182</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>12.4399995803833</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>12.4399995803833</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>1663269</v>
+      </c>
+      <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.17872190475464</v>
       </c>
       <c r="G2" t="n">
-        <v>3.12481331825256</v>
+        <v>3.12481355667114</v>
       </c>
       <c r="H2" t="n">
         <v>493230</v>
@@ -630,7 +630,7 @@
         <v>2.59337210655212</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5493905544281</v>
+        <v>2.54939079284668</v>
       </c>
       <c r="H9" t="n">
         <v>256430</v>
@@ -688,7 +688,7 @@
         <v>2.60422611236572</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56006073951721</v>
+        <v>2.56006050109863</v>
       </c>
       <c r="H11" t="n">
         <v>214063</v>
@@ -746,7 +746,7 @@
         <v>2.45769500732422</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4160144329071</v>
+        <v>2.41601467132568</v>
       </c>
       <c r="H13" t="n">
         <v>205959</v>
@@ -891,7 +891,7 @@
         <v>2.76006102561951</v>
       </c>
       <c r="G18" t="n">
-        <v>2.71325278282166</v>
+        <v>2.71325254440308</v>
       </c>
       <c r="H18" t="n">
         <v>596593</v>
@@ -1036,7 +1036,7 @@
         <v>2.71354293823242</v>
       </c>
       <c r="G23" t="n">
-        <v>2.66752338409424</v>
+        <v>2.66752362251282</v>
       </c>
       <c r="H23" t="n">
         <v>131540</v>
@@ -1065,7 +1065,7 @@
         <v>2.56468605995178</v>
       </c>
       <c r="G24" t="n">
-        <v>2.52119135856628</v>
+        <v>2.52119112014771</v>
       </c>
       <c r="H24" t="n">
         <v>163658</v>
@@ -1123,7 +1123,7 @@
         <v>2.41272711753845</v>
       </c>
       <c r="G26" t="n">
-        <v>2.37180948257446</v>
+        <v>2.37180924415588</v>
       </c>
       <c r="H26" t="n">
         <v>144800</v>
@@ -1152,7 +1152,7 @@
         <v>2.25999402999878</v>
       </c>
       <c r="G27" t="n">
-        <v>2.22166657447815</v>
+        <v>2.22166633605957</v>
       </c>
       <c r="H27" t="n">
         <v>346665</v>
@@ -1181,7 +1181,7 @@
         <v>2.10880994796753</v>
       </c>
       <c r="G28" t="n">
-        <v>2.07304620742798</v>
+        <v>2.07304644584656</v>
       </c>
       <c r="H28" t="n">
         <v>423821</v>
@@ -1239,7 +1239,7 @@
         <v>2.0933051109314</v>
       </c>
       <c r="G30" t="n">
-        <v>2.05780434608459</v>
+        <v>2.05780458450317</v>
       </c>
       <c r="H30" t="n">
         <v>144475</v>
@@ -1326,7 +1326,7 @@
         <v>2.41040110588074</v>
       </c>
       <c r="G33" t="n">
-        <v>2.3695228099823</v>
+        <v>2.36952257156372</v>
       </c>
       <c r="H33" t="n">
         <v>205506</v>
@@ -1384,7 +1384,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G35" t="n">
-        <v>2.56615734100342</v>
+        <v>2.566157579422</v>
       </c>
       <c r="H35" t="n">
         <v>251553</v>
@@ -1413,7 +1413,7 @@
         <v>2.46389698982239</v>
       </c>
       <c r="G36" t="n">
-        <v>2.42211151123047</v>
+        <v>2.42211127281189</v>
       </c>
       <c r="H36" t="n">
         <v>190917</v>
@@ -1442,7 +1442,7 @@
         <v>2.64066505432129</v>
       </c>
       <c r="G37" t="n">
-        <v>2.59588170051575</v>
+        <v>2.59588146209717</v>
       </c>
       <c r="H37" t="n">
         <v>246557</v>
@@ -1819,7 +1819,7 @@
         <v>2.45381808280945</v>
       </c>
       <c r="G50" t="n">
-        <v>2.41220331192017</v>
+        <v>2.41220355033875</v>
       </c>
       <c r="H50" t="n">
         <v>159744</v>
@@ -1935,7 +1935,7 @@
         <v>2.64841794967651</v>
       </c>
       <c r="G54" t="n">
-        <v>2.60350298881531</v>
+        <v>2.60350322723389</v>
       </c>
       <c r="H54" t="n">
         <v>485506</v>
@@ -1993,7 +1993,7 @@
         <v>2.73680210113525</v>
       </c>
       <c r="G56" t="n">
-        <v>2.69038844108582</v>
+        <v>2.69038820266724</v>
       </c>
       <c r="H56" t="n">
         <v>159844</v>
@@ -2109,7 +2109,7 @@
         <v>2.61042809486389</v>
       </c>
       <c r="G60" t="n">
-        <v>2.56615734100342</v>
+        <v>2.566157579422</v>
       </c>
       <c r="H60" t="n">
         <v>103412</v>
@@ -2341,7 +2341,7 @@
         <v>2.97326803207397</v>
       </c>
       <c r="G68" t="n">
-        <v>2.92284393310547</v>
+        <v>2.92284369468689</v>
       </c>
       <c r="H68" t="n">
         <v>318172</v>
@@ -2428,7 +2428,7 @@
         <v>2.87790608406067</v>
       </c>
       <c r="G71" t="n">
-        <v>2.82909917831421</v>
+        <v>2.82909941673279</v>
       </c>
       <c r="H71" t="n">
         <v>190823</v>
@@ -2457,7 +2457,7 @@
         <v>2.87480497360229</v>
       </c>
       <c r="G72" t="n">
-        <v>2.82605075836182</v>
+        <v>2.82605051994324</v>
       </c>
       <c r="H72" t="n">
         <v>241086</v>
@@ -2544,7 +2544,7 @@
         <v>2.81975889205933</v>
       </c>
       <c r="G75" t="n">
-        <v>2.77193808555603</v>
+        <v>2.77193832397461</v>
       </c>
       <c r="H75" t="n">
         <v>310240</v>
@@ -2573,7 +2573,7 @@
         <v>2.77634191513062</v>
       </c>
       <c r="G76" t="n">
-        <v>2.72925758361816</v>
+        <v>2.72925734519958</v>
       </c>
       <c r="H76" t="n">
         <v>301835</v>
@@ -2602,7 +2602,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G77" t="n">
-        <v>2.73306894302368</v>
+        <v>2.7330687046051</v>
       </c>
       <c r="H77" t="n">
         <v>155939</v>
@@ -2718,7 +2718,7 @@
         <v>2.79727506637573</v>
       </c>
       <c r="G81" t="n">
-        <v>2.749835729599</v>
+        <v>2.74983549118042</v>
       </c>
       <c r="H81" t="n">
         <v>168823</v>
@@ -2979,7 +2979,7 @@
         <v>2.5476291179657</v>
       </c>
       <c r="G90" t="n">
-        <v>2.50442361831665</v>
+        <v>2.50442337989807</v>
       </c>
       <c r="H90" t="n">
         <v>137592</v>
@@ -3095,7 +3095,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G94" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H94" t="n">
         <v>593089</v>
@@ -3153,7 +3153,7 @@
         <v>2.78021907806396</v>
       </c>
       <c r="G96" t="n">
-        <v>2.73306894302368</v>
+        <v>2.7330687046051</v>
       </c>
       <c r="H96" t="n">
         <v>193495</v>
@@ -3182,7 +3182,7 @@
         <v>2.94070506095886</v>
       </c>
       <c r="G97" t="n">
-        <v>2.89083337783813</v>
+        <v>2.89083313941956</v>
       </c>
       <c r="H97" t="n">
         <v>678677</v>
@@ -3298,7 +3298,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G101" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H101" t="n">
         <v>97675</v>
@@ -3385,7 +3385,7 @@
         <v>2.9693911075592</v>
       </c>
       <c r="G104" t="n">
-        <v>2.91903281211853</v>
+        <v>2.91903257369995</v>
       </c>
       <c r="H104" t="n">
         <v>94349</v>
@@ -3414,7 +3414,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G105" t="n">
-        <v>2.88244986534119</v>
+        <v>2.88244962692261</v>
       </c>
       <c r="H105" t="n">
         <v>76056</v>
@@ -3443,7 +3443,7 @@
         <v>2.8934121131897</v>
       </c>
       <c r="G106" t="n">
-        <v>2.84434247016907</v>
+        <v>2.84434223175049</v>
       </c>
       <c r="H106" t="n">
         <v>160927</v>
@@ -3472,7 +3472,7 @@
         <v>2.94458198547363</v>
       </c>
       <c r="G107" t="n">
-        <v>2.89464449882507</v>
+        <v>2.89464426040649</v>
       </c>
       <c r="H107" t="n">
         <v>122794</v>
@@ -3530,7 +3530,7 @@
         <v>2.91201901435852</v>
       </c>
       <c r="G109" t="n">
-        <v>2.86263370513916</v>
+        <v>2.86263346672058</v>
       </c>
       <c r="H109" t="n">
         <v>97079</v>
@@ -3617,7 +3617,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G112" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H112" t="n">
         <v>87752</v>
@@ -3704,7 +3704,7 @@
         <v>2.64919304847717</v>
       </c>
       <c r="G115" t="n">
-        <v>2.6042652130127</v>
+        <v>2.60426497459412</v>
       </c>
       <c r="H115" t="n">
         <v>158384</v>
@@ -3849,7 +3849,7 @@
         <v>2.90581703186035</v>
       </c>
       <c r="G120" t="n">
-        <v>2.8565366268158</v>
+        <v>2.85653686523438</v>
       </c>
       <c r="H120" t="n">
         <v>140706</v>
@@ -3907,7 +3907,7 @@
         <v>2.80502796173096</v>
       </c>
       <c r="G122" t="n">
-        <v>2.75745725631714</v>
+        <v>2.75745701789856</v>
       </c>
       <c r="H122" t="n">
         <v>103410</v>
@@ -4110,7 +4110,7 @@
         <v>2.53057289123535</v>
       </c>
       <c r="G129" t="n">
-        <v>2.48765659332275</v>
+        <v>2.48765635490417</v>
       </c>
       <c r="H129" t="n">
         <v>122546</v>
@@ -4197,7 +4197,7 @@
         <v>2.43831205368042</v>
       </c>
       <c r="G132" t="n">
-        <v>2.39696025848389</v>
+        <v>2.39696049690247</v>
       </c>
       <c r="H132" t="n">
         <v>324481</v>
@@ -4255,7 +4255,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56082248687744</v>
+        <v>2.56082224845886</v>
       </c>
       <c r="H134" t="n">
         <v>116496</v>
@@ -4284,7 +4284,7 @@
         <v>2.6050009727478</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56082248687744</v>
+        <v>2.56082224845886</v>
       </c>
       <c r="H135" t="n">
         <v>77002</v>
@@ -4371,7 +4371,7 @@
         <v>2.7057900428772</v>
       </c>
       <c r="G138" t="n">
-        <v>2.65990209579468</v>
+        <v>2.65990233421326</v>
       </c>
       <c r="H138" t="n">
         <v>227795</v>
@@ -4516,7 +4516,7 @@
         <v>2.89186191558838</v>
       </c>
       <c r="G143" t="n">
-        <v>2.84281849861145</v>
+        <v>2.84281826019287</v>
       </c>
       <c r="H143" t="n">
         <v>433122</v>
@@ -4545,7 +4545,7 @@
         <v>2.93217706680298</v>
       </c>
       <c r="G144" t="n">
-        <v>2.88244986534119</v>
+        <v>2.88244962692261</v>
       </c>
       <c r="H144" t="n">
         <v>504151</v>
@@ -4632,7 +4632,7 @@
         <v>2.95310997962952</v>
       </c>
       <c r="G147" t="n">
-        <v>2.90302777290344</v>
+        <v>2.90302753448486</v>
       </c>
       <c r="H147" t="n">
         <v>124606</v>
@@ -4661,7 +4661,7 @@
         <v>2.9918749332428</v>
       </c>
       <c r="G148" t="n">
-        <v>2.94113540649414</v>
+        <v>2.94113516807556</v>
       </c>
       <c r="H148" t="n">
         <v>115180</v>
@@ -4719,7 +4719,7 @@
         <v>2.96551489830017</v>
       </c>
       <c r="G150" t="n">
-        <v>2.91522240638733</v>
+        <v>2.91522216796875</v>
       </c>
       <c r="H150" t="n">
         <v>107908</v>
@@ -4748,7 +4748,7 @@
         <v>2.92287397384644</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87330436706543</v>
+        <v>2.87330460548401</v>
       </c>
       <c r="H151" t="n">
         <v>112608</v>
@@ -4835,7 +4835,7 @@
         <v>2.93527793884277</v>
       </c>
       <c r="G154" t="n">
-        <v>2.885498046875</v>
+        <v>2.88549828529358</v>
       </c>
       <c r="H154" t="n">
         <v>98584</v>
@@ -4922,7 +4922,7 @@
         <v>2.95388507843018</v>
       </c>
       <c r="G157" t="n">
-        <v>2.90378952026367</v>
+        <v>2.90378975868225</v>
       </c>
       <c r="H157" t="n">
         <v>130813</v>
@@ -4980,7 +4980,7 @@
         <v>3.05855107307434</v>
       </c>
       <c r="G159" t="n">
-        <v>3.00668048858643</v>
+        <v>3.006680727005</v>
       </c>
       <c r="H159" t="n">
         <v>293073</v>
@@ -5009,7 +5009,7 @@
         <v>3.0221118927002</v>
       </c>
       <c r="G160" t="n">
-        <v>2.97085928916931</v>
+        <v>2.97085952758789</v>
       </c>
       <c r="H160" t="n">
         <v>76130</v>
@@ -5067,7 +5067,7 @@
         <v>2.97404289245605</v>
       </c>
       <c r="G162" t="n">
-        <v>2.92360544204712</v>
+        <v>2.9236056804657</v>
       </c>
       <c r="H162" t="n">
         <v>29083</v>
@@ -5125,7 +5125,7 @@
         <v>3.02676391601562</v>
       </c>
       <c r="G164" t="n">
-        <v>2.97543263435364</v>
+        <v>2.97543239593506</v>
       </c>
       <c r="H164" t="n">
         <v>68786</v>
@@ -5444,7 +5444,7 @@
         <v>3.35936594009399</v>
       </c>
       <c r="G175" t="n">
-        <v>3.30239391326904</v>
+        <v>3.30239415168762</v>
       </c>
       <c r="H175" t="n">
         <v>136675</v>
@@ -5531,7 +5531,7 @@
         <v>3.38262510299683</v>
       </c>
       <c r="G178" t="n">
-        <v>3.32525849342346</v>
+        <v>3.32525873184204</v>
       </c>
       <c r="H178" t="n">
         <v>282670</v>
@@ -5560,7 +5560,7 @@
         <v>3.31750011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>3.26123833656311</v>
+        <v>3.26123809814453</v>
       </c>
       <c r="H179" t="n">
         <v>124150</v>
@@ -5647,7 +5647,7 @@
         <v>3.23764491081238</v>
       </c>
       <c r="G182" t="n">
-        <v>3.18273735046387</v>
+        <v>3.18273711204529</v>
       </c>
       <c r="H182" t="n">
         <v>146776</v>
@@ -5705,7 +5705,7 @@
         <v>3.20430707931519</v>
       </c>
       <c r="G184" t="n">
-        <v>3.14996480941772</v>
+        <v>3.14996457099915</v>
       </c>
       <c r="H184" t="n">
         <v>75785</v>
@@ -5821,7 +5821,7 @@
         <v>3.35083794593811</v>
       </c>
       <c r="G188" t="n">
-        <v>3.29401040077209</v>
+        <v>3.29401063919067</v>
       </c>
       <c r="H188" t="n">
         <v>126105</v>
@@ -5937,7 +5937,7 @@
         <v>3.35548996925354</v>
       </c>
       <c r="G192" t="n">
-        <v>3.29858374595642</v>
+        <v>3.29858350753784</v>
       </c>
       <c r="H192" t="n">
         <v>204931</v>
@@ -6082,7 +6082,7 @@
         <v>3.3570408821106</v>
       </c>
       <c r="G197" t="n">
-        <v>3.30010843276978</v>
+        <v>3.3001081943512</v>
       </c>
       <c r="H197" t="n">
         <v>92448</v>
@@ -6140,7 +6140,7 @@
         <v>3.33067989349365</v>
       </c>
       <c r="G199" t="n">
-        <v>3.27419424057007</v>
+        <v>3.27419447898865</v>
       </c>
       <c r="H199" t="n">
         <v>109612</v>
@@ -6169,7 +6169,7 @@
         <v>3.35238909721375</v>
       </c>
       <c r="G200" t="n">
-        <v>3.29553556442261</v>
+        <v>3.29553532600403</v>
       </c>
       <c r="H200" t="n">
         <v>72532</v>
@@ -6343,7 +6343,7 @@
         <v>3.34308505058289</v>
       </c>
       <c r="G206" t="n">
-        <v>3.28638911247253</v>
+        <v>3.28638935089111</v>
       </c>
       <c r="H206" t="n">
         <v>211723</v>
@@ -6575,7 +6575,7 @@
         <v>3.19965505599976</v>
       </c>
       <c r="G214" t="n">
-        <v>3.14539170265198</v>
+        <v>3.1453914642334</v>
       </c>
       <c r="H214" t="n">
         <v>46695</v>
@@ -6604,7 +6604,7 @@
         <v>3.20353198051453</v>
       </c>
       <c r="G215" t="n">
-        <v>3.14920282363892</v>
+        <v>3.14920258522034</v>
       </c>
       <c r="H215" t="n">
         <v>20449</v>
@@ -6720,7 +6720,7 @@
         <v>3.04226899147034</v>
       </c>
       <c r="G219" t="n">
-        <v>2.99067449569702</v>
+        <v>2.9906747341156</v>
       </c>
       <c r="H219" t="n">
         <v>119131</v>
@@ -6778,7 +6778,7 @@
         <v>3.23299288749695</v>
       </c>
       <c r="G221" t="n">
-        <v>3.17816424369812</v>
+        <v>3.17816400527954</v>
       </c>
       <c r="H221" t="n">
         <v>190310</v>
@@ -6807,7 +6807,7 @@
         <v>3.24384689331055</v>
       </c>
       <c r="G222" t="n">
-        <v>3.18883395195007</v>
+        <v>3.18883419036865</v>
       </c>
       <c r="H222" t="n">
         <v>201688</v>
@@ -6836,7 +6836,7 @@
         <v>3.37254691123962</v>
       </c>
       <c r="G223" t="n">
-        <v>3.31535148620605</v>
+        <v>3.31535124778748</v>
       </c>
       <c r="H223" t="n">
         <v>480056</v>
@@ -7010,7 +7010,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G229" t="n">
-        <v>3.19340705871582</v>
+        <v>3.1934072971344</v>
       </c>
       <c r="H229" t="n">
         <v>91423</v>
@@ -7068,7 +7068,7 @@
         <v>3.24617290496826</v>
       </c>
       <c r="G231" t="n">
-        <v>3.19112038612366</v>
+        <v>3.19112062454224</v>
       </c>
       <c r="H231" t="n">
         <v>60078</v>
@@ -7097,7 +7097,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G232" t="n">
-        <v>3.18197464942932</v>
+        <v>3.18197441101074</v>
       </c>
       <c r="H232" t="n">
         <v>46953</v>
@@ -7213,7 +7213,7 @@
         <v>3.22601509094238</v>
       </c>
       <c r="G236" t="n">
-        <v>3.17130446434021</v>
+        <v>3.17130470275879</v>
       </c>
       <c r="H236" t="n">
         <v>92031</v>
@@ -7242,7 +7242,7 @@
         <v>3.24849891662598</v>
       </c>
       <c r="G237" t="n">
-        <v>3.19340705871582</v>
+        <v>3.1934072971344</v>
       </c>
       <c r="H237" t="n">
         <v>65003</v>
@@ -7329,7 +7329,7 @@
         <v>3.23686909675598</v>
       </c>
       <c r="G240" t="n">
-        <v>3.18197464942932</v>
+        <v>3.18197441101074</v>
       </c>
       <c r="H240" t="n">
         <v>117377</v>
@@ -7503,7 +7503,7 @@
         <v>3.26167893409729</v>
       </c>
       <c r="G246" t="n">
-        <v>3.20636367797852</v>
+        <v>3.20636343955994</v>
       </c>
       <c r="H246" t="n">
         <v>207240</v>
@@ -7532,7 +7532,7 @@
         <v>3.32602906227112</v>
       </c>
       <c r="G247" t="n">
-        <v>3.26962232589722</v>
+        <v>3.2696225643158</v>
       </c>
       <c r="H247" t="n">
         <v>91899</v>
@@ -7677,7 +7677,7 @@
         <v>3.5446629524231</v>
       </c>
       <c r="G252" t="n">
-        <v>3.48454856872559</v>
+        <v>3.48454833030701</v>
       </c>
       <c r="H252" t="n">
         <v>194782</v>
@@ -7851,7 +7851,7 @@
         <v>3.721431016922</v>
       </c>
       <c r="G258" t="n">
-        <v>3.65831875801086</v>
+        <v>3.65831851959229</v>
       </c>
       <c r="H258" t="n">
         <v>319621</v>
@@ -7909,7 +7909,7 @@
         <v>4.00053787231445</v>
       </c>
       <c r="G260" t="n">
-        <v>3.93269205093384</v>
+        <v>3.93269228935242</v>
       </c>
       <c r="H260" t="n">
         <v>648070</v>
@@ -8083,7 +8083,7 @@
         <v>4.05093193054199</v>
       </c>
       <c r="G266" t="n">
-        <v>3.9822313785553</v>
+        <v>3.98223161697388</v>
       </c>
       <c r="H266" t="n">
         <v>236555</v>
@@ -8257,7 +8257,7 @@
         <v>4.18661022186279</v>
       </c>
       <c r="G272" t="n">
-        <v>4.11560869216919</v>
+        <v>4.11560916900635</v>
       </c>
       <c r="H272" t="n">
         <v>1412380</v>
@@ -8286,7 +8286,7 @@
         <v>4.27964496612549</v>
       </c>
       <c r="G273" t="n">
-        <v>4.20706605911255</v>
+        <v>4.20706558227539</v>
       </c>
       <c r="H273" t="n">
         <v>1069890</v>
@@ -8315,7 +8315,7 @@
         <v>4.43858098983765</v>
       </c>
       <c r="G274" t="n">
-        <v>4.36330652236938</v>
+        <v>4.36330604553223</v>
       </c>
       <c r="H274" t="n">
         <v>723596</v>
@@ -8344,7 +8344,7 @@
         <v>4.442458152771</v>
       </c>
       <c r="G275" t="n">
-        <v>4.3671178817749</v>
+        <v>4.36711740493774</v>
       </c>
       <c r="H275" t="n">
         <v>567984</v>
@@ -8402,7 +8402,7 @@
         <v>4.3610520362854</v>
       </c>
       <c r="G277" t="n">
-        <v>4.28709268569946</v>
+        <v>4.2870922088623</v>
       </c>
       <c r="H277" t="n">
         <v>208145</v>
@@ -8431,7 +8431,7 @@
         <v>4.25251007080078</v>
       </c>
       <c r="G278" t="n">
-        <v>4.18039131164551</v>
+        <v>4.18039083480835</v>
       </c>
       <c r="H278" t="n">
         <v>280129</v>
@@ -8547,7 +8547,7 @@
         <v>4.33779287338257</v>
       </c>
       <c r="G282" t="n">
-        <v>4.26422739028931</v>
+        <v>4.26422786712646</v>
       </c>
       <c r="H282" t="n">
         <v>221629</v>
@@ -8605,7 +8605,7 @@
         <v>4.27189207077026</v>
       </c>
       <c r="G284" t="n">
-        <v>4.19944477081299</v>
+        <v>4.19944429397583</v>
       </c>
       <c r="H284" t="n">
         <v>219679</v>
@@ -8721,7 +8721,7 @@
         <v>4.12846183776855</v>
       </c>
       <c r="G288" t="n">
-        <v>4.05844688415527</v>
+        <v>4.05844640731812</v>
       </c>
       <c r="H288" t="n">
         <v>181443</v>
@@ -8808,7 +8808,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G291" t="n">
-        <v>4.5271692276001</v>
+        <v>4.52716970443726</v>
       </c>
       <c r="H291" t="n">
         <v>1365540</v>
@@ -8866,7 +8866,7 @@
         <v>4.52386379241943</v>
       </c>
       <c r="G293" t="n">
-        <v>4.44714260101318</v>
+        <v>4.44714307785034</v>
       </c>
       <c r="H293" t="n">
         <v>403894</v>
@@ -8982,7 +8982,7 @@
         <v>4.60527086257935</v>
       </c>
       <c r="G297" t="n">
-        <v>4.5271692276001</v>
+        <v>4.52716970443726</v>
       </c>
       <c r="H297" t="n">
         <v>367010</v>
@@ -9040,7 +9040,7 @@
         <v>4.64403486251831</v>
       </c>
       <c r="G299" t="n">
-        <v>4.5652756690979</v>
+        <v>4.56527614593506</v>
       </c>
       <c r="H299" t="n">
         <v>165971</v>
@@ -9098,7 +9098,7 @@
         <v>4.88437795639038</v>
       </c>
       <c r="G301" t="n">
-        <v>4.80154275894165</v>
+        <v>4.80154323577881</v>
       </c>
       <c r="H301" t="n">
         <v>885013</v>
@@ -9127,7 +9127,7 @@
         <v>5.09758520126343</v>
       </c>
       <c r="G302" t="n">
-        <v>5.0111346244812</v>
+        <v>5.01113414764404</v>
       </c>
       <c r="H302" t="n">
         <v>1328330</v>
@@ -9388,7 +9388,7 @@
         <v>5.02780818939209</v>
       </c>
       <c r="G311" t="n">
-        <v>4.94254064559937</v>
+        <v>4.94254112243652</v>
       </c>
       <c r="H311" t="n">
         <v>342293</v>
@@ -9446,7 +9446,7 @@
         <v>5.06657314300537</v>
       </c>
       <c r="G313" t="n">
-        <v>4.98064804077148</v>
+        <v>4.98064851760864</v>
       </c>
       <c r="H313" t="n">
         <v>238791</v>
@@ -9533,7 +9533,7 @@
         <v>5.11309099197388</v>
       </c>
       <c r="G316" t="n">
-        <v>5.02637767791748</v>
+        <v>5.02637720108032</v>
       </c>
       <c r="H316" t="n">
         <v>297516</v>
@@ -9562,7 +9562,7 @@
         <v>5.19449710845947</v>
       </c>
       <c r="G317" t="n">
-        <v>5.10640239715576</v>
+        <v>5.10640287399292</v>
       </c>
       <c r="H317" t="n">
         <v>464423</v>
@@ -9649,7 +9649,7 @@
         <v>5.21388006210327</v>
       </c>
       <c r="G320" t="n">
-        <v>5.12545728683472</v>
+        <v>5.12545680999756</v>
       </c>
       <c r="H320" t="n">
         <v>546852</v>
@@ -9707,7 +9707,7 @@
         <v>5.48523378372192</v>
       </c>
       <c r="G322" t="n">
-        <v>5.39220857620239</v>
+        <v>5.39220905303955</v>
       </c>
       <c r="H322" t="n">
         <v>940314</v>
@@ -9823,7 +9823,7 @@
         <v>6.08609008789062</v>
       </c>
       <c r="G326" t="n">
-        <v>5.98287487030029</v>
+        <v>5.98287534713745</v>
       </c>
       <c r="H326" t="n">
         <v>1806086</v>
@@ -9881,7 +9881,7 @@
         <v>6.11710214614868</v>
       </c>
       <c r="G328" t="n">
-        <v>6.01336097717285</v>
+        <v>6.01336145401001</v>
       </c>
       <c r="H328" t="n">
         <v>1777020</v>
@@ -10026,7 +10026,7 @@
         <v>6.20238494873047</v>
       </c>
       <c r="G333" t="n">
-        <v>6.09719800949097</v>
+        <v>6.09719753265381</v>
       </c>
       <c r="H333" t="n">
         <v>1738052</v>
@@ -10171,7 +10171,7 @@
         <v>7.13661909103394</v>
       </c>
       <c r="G338" t="n">
-        <v>7.01558828353882</v>
+        <v>7.01558780670166</v>
       </c>
       <c r="H338" t="n">
         <v>2024444</v>
@@ -10200,7 +10200,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G339" t="n">
-        <v>6.72215986251831</v>
+        <v>6.72216033935547</v>
       </c>
       <c r="H339" t="n">
         <v>1597497</v>
@@ -10316,7 +10316,7 @@
         <v>7.07847213745117</v>
       </c>
       <c r="G343" t="n">
-        <v>6.95842695236206</v>
+        <v>6.95842742919922</v>
       </c>
       <c r="H343" t="n">
         <v>1152592</v>
@@ -10345,7 +10345,7 @@
         <v>7.02420091629028</v>
       </c>
       <c r="G344" t="n">
-        <v>6.90507650375366</v>
+        <v>6.9050760269165</v>
       </c>
       <c r="H344" t="n">
         <v>757764</v>
@@ -10403,7 +10403,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G346" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H346" t="n">
         <v>1253565</v>
@@ -10432,7 +10432,7 @@
         <v>7.40797281265259</v>
       </c>
       <c r="G347" t="n">
-        <v>7.28234004974365</v>
+        <v>7.28233957290649</v>
       </c>
       <c r="H347" t="n">
         <v>953069</v>
@@ -10577,7 +10577,7 @@
         <v>6.38845586776733</v>
       </c>
       <c r="G352" t="n">
-        <v>6.28011274337769</v>
+        <v>6.28011322021484</v>
       </c>
       <c r="H352" t="n">
         <v>1189739</v>
@@ -10751,7 +10751,7 @@
         <v>7.03583002090454</v>
       </c>
       <c r="G358" t="n">
-        <v>6.91650867462158</v>
+        <v>6.91650819778442</v>
       </c>
       <c r="H358" t="n">
         <v>557993</v>
@@ -10809,7 +10809,7 @@
         <v>6.8381290435791</v>
       </c>
       <c r="G360" t="n">
-        <v>6.72215986251831</v>
+        <v>6.72216033935547</v>
       </c>
       <c r="H360" t="n">
         <v>383136</v>
@@ -11070,7 +11070,7 @@
         <v>6.86526489257812</v>
       </c>
       <c r="G369" t="n">
-        <v>6.74883604049683</v>
+        <v>6.74883556365967</v>
       </c>
       <c r="H369" t="n">
         <v>381623</v>
@@ -11099,7 +11099,7 @@
         <v>6.77222919464111</v>
       </c>
       <c r="G370" t="n">
-        <v>6.65737771987915</v>
+        <v>6.65737819671631</v>
       </c>
       <c r="H370" t="n">
         <v>410334</v>
@@ -11157,7 +11157,7 @@
         <v>6.76835203170776</v>
       </c>
       <c r="G372" t="n">
-        <v>6.65356636047363</v>
+        <v>6.65356683731079</v>
       </c>
       <c r="H372" t="n">
         <v>220177</v>
@@ -11447,7 +11447,7 @@
         <v>7.37308502197266</v>
       </c>
       <c r="G382" t="n">
-        <v>7.24804353713989</v>
+        <v>7.24804401397705</v>
       </c>
       <c r="H382" t="n">
         <v>2466801</v>
@@ -11563,7 +11563,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G386" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H386" t="n">
         <v>674582</v>
@@ -11679,7 +11679,7 @@
         <v>7.72972202301025</v>
       </c>
       <c r="G390" t="n">
-        <v>7.59863233566284</v>
+        <v>7.5986328125</v>
       </c>
       <c r="H390" t="n">
         <v>446172</v>
@@ -11737,7 +11737,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G392" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H392" t="n">
         <v>528987</v>
@@ -11795,7 +11795,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G394" t="n">
-        <v>8.1931095123291</v>
+        <v>8.19310855865479</v>
       </c>
       <c r="H394" t="n">
         <v>618520</v>
@@ -11824,7 +11824,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G395" t="n">
-        <v>8.36078262329102</v>
+        <v>8.3607816696167</v>
       </c>
       <c r="H395" t="n">
         <v>589330</v>
@@ -11911,7 +11911,7 @@
         <v>8.0708532333374</v>
       </c>
       <c r="G398" t="n">
-        <v>7.93397808074951</v>
+        <v>7.93397903442383</v>
       </c>
       <c r="H398" t="n">
         <v>1105464</v>
@@ -11940,7 +11940,7 @@
         <v>8.03208827972412</v>
       </c>
       <c r="G399" t="n">
-        <v>7.89587068557739</v>
+        <v>7.89587116241455</v>
       </c>
       <c r="H399" t="n">
         <v>704166</v>
@@ -12027,7 +12027,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G402" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H402" t="n">
         <v>4317226</v>
@@ -12230,7 +12230,7 @@
         <v>7.67545080184937</v>
       </c>
       <c r="G409" t="n">
-        <v>7.54528188705444</v>
+        <v>7.54528141021729</v>
       </c>
       <c r="H409" t="n">
         <v>485472</v>
@@ -12317,7 +12317,7 @@
         <v>7.30718517303467</v>
       </c>
       <c r="G412" t="n">
-        <v>7.18326187133789</v>
+        <v>7.18326139450073</v>
       </c>
       <c r="H412" t="n">
         <v>778353</v>
@@ -12462,7 +12462,7 @@
         <v>7.07071876525879</v>
       </c>
       <c r="G417" t="n">
-        <v>6.95080518722534</v>
+        <v>6.9508056640625</v>
       </c>
       <c r="H417" t="n">
         <v>221650</v>
@@ -12520,7 +12520,7 @@
         <v>6.985435962677</v>
       </c>
       <c r="G419" t="n">
-        <v>6.86696910858154</v>
+        <v>6.86696863174438</v>
       </c>
       <c r="H419" t="n">
         <v>607996</v>
@@ -12607,7 +12607,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G422" t="n">
-        <v>7.27853012084961</v>
+        <v>7.27852964401245</v>
       </c>
       <c r="H422" t="n">
         <v>880611</v>
@@ -12723,7 +12723,7 @@
         <v>7.17925977706909</v>
       </c>
       <c r="G426" t="n">
-        <v>7.05750560760498</v>
+        <v>7.05750608444214</v>
       </c>
       <c r="H426" t="n">
         <v>1555624</v>
@@ -12752,7 +12752,7 @@
         <v>7.43510913848877</v>
       </c>
       <c r="G427" t="n">
-        <v>7.30901622772217</v>
+        <v>7.30901575088501</v>
       </c>
       <c r="H427" t="n">
         <v>1335622</v>
@@ -12868,7 +12868,7 @@
         <v>8.00107669830322</v>
       </c>
       <c r="G431" t="n">
-        <v>7.86538505554199</v>
+        <v>7.86538553237915</v>
       </c>
       <c r="H431" t="n">
         <v>781944</v>
@@ -12926,7 +12926,7 @@
         <v>7.7142162322998</v>
       </c>
       <c r="G433" t="n">
-        <v>7.58338975906372</v>
+        <v>7.58338928222656</v>
       </c>
       <c r="H433" t="n">
         <v>526446</v>
@@ -12955,7 +12955,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G434" t="n">
-        <v>7.94922113418579</v>
+        <v>7.94922161102295</v>
       </c>
       <c r="H434" t="n">
         <v>1316387</v>
@@ -13071,7 +13071,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G438" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H438" t="n">
         <v>447832</v>
@@ -13129,7 +13129,7 @@
         <v>8.08635902404785</v>
       </c>
       <c r="G440" t="n">
-        <v>7.94922113418579</v>
+        <v>7.94922161102295</v>
       </c>
       <c r="H440" t="n">
         <v>478643</v>
@@ -13158,7 +13158,7 @@
         <v>7.98557090759277</v>
       </c>
       <c r="G441" t="n">
-        <v>7.85014247894287</v>
+        <v>7.85014200210571</v>
       </c>
       <c r="H441" t="n">
         <v>375921</v>
@@ -13303,7 +13303,7 @@
         <v>8.50502014160156</v>
       </c>
       <c r="G446" t="n">
-        <v>8.36078262329102</v>
+        <v>8.3607816696167</v>
       </c>
       <c r="H446" t="n">
         <v>2904190</v>
@@ -13332,7 +13332,7 @@
         <v>8.06309986114502</v>
       </c>
       <c r="G447" t="n">
-        <v>7.92635631561279</v>
+        <v>7.92635583877563</v>
       </c>
       <c r="H447" t="n">
         <v>4805532</v>
@@ -13448,7 +13448,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G451" t="n">
-        <v>7.36617660522461</v>
+        <v>7.36617708206177</v>
       </c>
       <c r="H451" t="n">
         <v>1207097</v>
@@ -13477,7 +13477,7 @@
         <v>7.58629179000854</v>
       </c>
       <c r="G452" t="n">
-        <v>7.45763492584229</v>
+        <v>7.45763444900513</v>
       </c>
       <c r="H452" t="n">
         <v>1486373</v>
@@ -13564,7 +13564,7 @@
         <v>7.51651477813721</v>
       </c>
       <c r="G455" t="n">
-        <v>7.38904142379761</v>
+        <v>7.38904094696045</v>
       </c>
       <c r="H455" t="n">
         <v>957250</v>
@@ -13680,7 +13680,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G459" t="n">
-        <v>7.31663751602173</v>
+        <v>7.31663703918457</v>
       </c>
       <c r="H459" t="n">
         <v>430589</v>
@@ -13709,7 +13709,7 @@
         <v>7.40409708023071</v>
       </c>
       <c r="G460" t="n">
-        <v>7.27853012084961</v>
+        <v>7.27852964401245</v>
       </c>
       <c r="H460" t="n">
         <v>425428</v>
@@ -13796,7 +13796,7 @@
         <v>7.50100898742676</v>
       </c>
       <c r="G463" t="n">
-        <v>7.37379789352417</v>
+        <v>7.37379837036133</v>
       </c>
       <c r="H463" t="n">
         <v>490050</v>
@@ -13825,7 +13825,7 @@
         <v>7.44286203384399</v>
       </c>
       <c r="G464" t="n">
-        <v>7.31663751602173</v>
+        <v>7.31663703918457</v>
       </c>
       <c r="H464" t="n">
         <v>447048</v>
@@ -13883,7 +13883,7 @@
         <v>7.44673776626587</v>
       </c>
       <c r="G466" t="n">
-        <v>7.32044744491577</v>
+        <v>7.32044696807861</v>
       </c>
       <c r="H466" t="n">
         <v>650810</v>
@@ -13912,7 +13912,7 @@
         <v>7.49325609207153</v>
       </c>
       <c r="G467" t="n">
-        <v>7.36617660522461</v>
+        <v>7.36617708206177</v>
       </c>
       <c r="H467" t="n">
         <v>504330</v>
@@ -14028,7 +14028,7 @@
         <v>8.54378509521484</v>
       </c>
       <c r="G471" t="n">
-        <v>8.39889049530029</v>
+        <v>8.39888954162598</v>
       </c>
       <c r="H471" t="n">
         <v>1645276</v>
@@ -14057,7 +14057,7 @@
         <v>8.33445453643799</v>
       </c>
       <c r="G472" t="n">
-        <v>8.1931095123291</v>
+        <v>8.19310855865479</v>
       </c>
       <c r="H472" t="n">
         <v>1740272</v>
@@ -14115,7 +14115,7 @@
         <v>8.24141883850098</v>
       </c>
       <c r="G474" t="n">
-        <v>8.10165214538574</v>
+        <v>8.10165119171143</v>
       </c>
       <c r="H474" t="n">
         <v>648959</v>
@@ -14144,7 +14144,7 @@
         <v>8.21040725708008</v>
       </c>
       <c r="G475" t="n">
-        <v>8.07116508483887</v>
+        <v>8.07116603851318</v>
       </c>
       <c r="H475" t="n">
         <v>437746</v>
@@ -14231,7 +14231,7 @@
         <v>8.38872623443604</v>
       </c>
       <c r="G478" t="n">
-        <v>8.2464599609375</v>
+        <v>8.24646091461182</v>
       </c>
       <c r="H478" t="n">
         <v>2636241</v>
@@ -14289,7 +14289,7 @@
         <v>8.87716293334961</v>
       </c>
       <c r="G480" t="n">
-        <v>8.72661399841309</v>
+        <v>8.72661304473877</v>
       </c>
       <c r="H480" t="n">
         <v>2854751</v>
@@ -14405,7 +14405,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G484" t="n">
-        <v>8.8866662979126</v>
+        <v>8.88666534423828</v>
       </c>
       <c r="H484" t="n">
         <v>943241</v>
@@ -14434,7 +14434,7 @@
         <v>9.04772853851318</v>
       </c>
       <c r="G485" t="n">
-        <v>8.89428615570068</v>
+        <v>8.894287109375</v>
       </c>
       <c r="H485" t="n">
         <v>875881</v>
@@ -14521,7 +14521,7 @@
         <v>9.17177677154541</v>
       </c>
       <c r="G488" t="n">
-        <v>9.01623058319092</v>
+        <v>9.01623153686523</v>
       </c>
       <c r="H488" t="n">
         <v>886825</v>
@@ -14782,7 +14782,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G497" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H497" t="n">
         <v>1414410</v>
@@ -14898,7 +14898,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G501" t="n">
-        <v>9.96129608154297</v>
+        <v>9.96129703521729</v>
       </c>
       <c r="H501" t="n">
         <v>845538</v>
@@ -14956,7 +14956,7 @@
         <v>10.1796636581421</v>
       </c>
       <c r="G503" t="n">
-        <v>10.007025718689</v>
+        <v>10.0070247650146</v>
       </c>
       <c r="H503" t="n">
         <v>832310</v>
@@ -15043,7 +15043,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G506" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H506" t="n">
         <v>913020</v>
@@ -15072,7 +15072,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G507" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H507" t="n">
         <v>366112</v>
@@ -15159,7 +15159,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G510" t="n">
-        <v>9.79362392425537</v>
+        <v>9.79362297058105</v>
       </c>
       <c r="H510" t="n">
         <v>238182</v>
@@ -15188,7 +15188,7 @@
         <v>9.70673179626465</v>
       </c>
       <c r="G511" t="n">
-        <v>9.5421142578125</v>
+        <v>9.54211330413818</v>
       </c>
       <c r="H511" t="n">
         <v>455430</v>
@@ -15246,7 +15246,7 @@
         <v>10.1486520767212</v>
       </c>
       <c r="G513" t="n">
-        <v>9.97653865814209</v>
+        <v>9.97653961181641</v>
       </c>
       <c r="H513" t="n">
         <v>442390</v>
@@ -15304,7 +15304,7 @@
         <v>10.5285491943359</v>
       </c>
       <c r="G515" t="n">
-        <v>10.3499946594238</v>
+        <v>10.3499937057495</v>
       </c>
       <c r="H515" t="n">
         <v>969702</v>
@@ -15420,7 +15420,7 @@
         <v>11.2108106613159</v>
       </c>
       <c r="G519" t="n">
-        <v>11.0206842422485</v>
+        <v>11.0206851959229</v>
       </c>
       <c r="H519" t="n">
         <v>1860164</v>
@@ -15536,7 +15536,7 @@
         <v>11.265082359314</v>
       </c>
       <c r="G523" t="n">
-        <v>11.0740365982056</v>
+        <v>11.0740356445312</v>
       </c>
       <c r="H523" t="n">
         <v>1216725</v>
@@ -15594,7 +15594,7 @@
         <v>11.3658714294434</v>
       </c>
       <c r="G525" t="n">
-        <v>11.1731157302856</v>
+        <v>11.17311668396</v>
       </c>
       <c r="H525" t="n">
         <v>686072</v>
@@ -15623,7 +15623,7 @@
         <v>11.3426122665405</v>
       </c>
       <c r="G526" t="n">
-        <v>11.1502513885498</v>
+        <v>11.1502504348755</v>
       </c>
       <c r="H526" t="n">
         <v>701379</v>
@@ -15681,7 +15681,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G528" t="n">
-        <v>10.8225269317627</v>
+        <v>10.8225259780884</v>
       </c>
       <c r="H528" t="n">
         <v>764225</v>
@@ -15855,7 +15855,7 @@
         <v>11.0092334747314</v>
       </c>
       <c r="G534" t="n">
-        <v>10.8225269317627</v>
+        <v>10.8225259780884</v>
       </c>
       <c r="H534" t="n">
         <v>1206401</v>
@@ -16029,7 +16029,7 @@
         <v>10.4200067520142</v>
       </c>
       <c r="G540" t="n">
-        <v>10.2432928085327</v>
+        <v>10.2432918548584</v>
       </c>
       <c r="H540" t="n">
         <v>1215961</v>
@@ -16058,7 +16058,7 @@
         <v>10.5052900314331</v>
       </c>
       <c r="G541" t="n">
-        <v>10.3271293640137</v>
+        <v>10.3271284103394</v>
       </c>
       <c r="H541" t="n">
         <v>891258</v>
@@ -16174,7 +16174,7 @@
         <v>10.4665250778198</v>
       </c>
       <c r="G545" t="n">
-        <v>10.2890224456787</v>
+        <v>10.2890214920044</v>
       </c>
       <c r="H545" t="n">
         <v>418757</v>
@@ -16290,7 +16290,7 @@
         <v>10.3889951705933</v>
       </c>
       <c r="G549" t="n">
-        <v>10.2128057479858</v>
+        <v>10.2128067016602</v>
       </c>
       <c r="H549" t="n">
         <v>499673</v>
@@ -16348,7 +16348,7 @@
         <v>9.9548282623291</v>
       </c>
       <c r="G551" t="n">
-        <v>9.78600311279297</v>
+        <v>9.78600215911865</v>
       </c>
       <c r="H551" t="n">
         <v>665775</v>
@@ -16464,7 +16464,7 @@
         <v>9.59043788909912</v>
       </c>
       <c r="G555" t="n">
-        <v>9.42779159545898</v>
+        <v>9.4277925491333</v>
       </c>
       <c r="H555" t="n">
         <v>595699</v>
@@ -16638,7 +16638,7 @@
         <v>10.0711231231689</v>
       </c>
       <c r="G561" t="n">
-        <v>9.90032482147217</v>
+        <v>9.90032577514648</v>
       </c>
       <c r="H561" t="n">
         <v>502777</v>
@@ -16696,7 +16696,7 @@
         <v>9.96258068084717</v>
       </c>
       <c r="G563" t="n">
-        <v>9.79362392425537</v>
+        <v>9.79362297058105</v>
       </c>
       <c r="H563" t="n">
         <v>395215</v>
@@ -16841,7 +16841,7 @@
         <v>10.1951704025269</v>
       </c>
       <c r="G568" t="n">
-        <v>10.0222692489624</v>
+        <v>10.0222682952881</v>
       </c>
       <c r="H568" t="n">
         <v>554786</v>
@@ -16957,7 +16957,7 @@
         <v>11.0247392654419</v>
       </c>
       <c r="G572" t="n">
-        <v>10.8377695083618</v>
+        <v>10.8377685546875</v>
       </c>
       <c r="H572" t="n">
         <v>977445</v>
@@ -17102,7 +17102,7 @@
         <v>9.03997611999512</v>
       </c>
       <c r="G577" t="n">
-        <v>8.8866662979126</v>
+        <v>8.88666534423828</v>
       </c>
       <c r="H577" t="n">
         <v>1985248</v>
@@ -17189,7 +17189,7 @@
         <v>9.11750602722168</v>
       </c>
       <c r="G580" t="n">
-        <v>8.96288108825684</v>
+        <v>8.96288013458252</v>
       </c>
       <c r="H580" t="n">
         <v>887045</v>
@@ -17218,7 +17218,7 @@
         <v>9.45088386535645</v>
       </c>
       <c r="G581" t="n">
-        <v>9.29060459136963</v>
+        <v>9.29060554504395</v>
       </c>
       <c r="H581" t="n">
         <v>2141921</v>
@@ -17421,7 +17421,7 @@
         <v>9.83078002929688</v>
       </c>
       <c r="G588" t="n">
-        <v>9.66405773162842</v>
+        <v>9.66405868530273</v>
       </c>
       <c r="H588" t="n">
         <v>640698</v>
@@ -17595,7 +17595,7 @@
         <v>10.1331462860107</v>
       </c>
       <c r="G594" t="n">
-        <v>9.96129608154297</v>
+        <v>9.96129703521729</v>
       </c>
       <c r="H594" t="n">
         <v>397609</v>
@@ -17711,7 +17711,7 @@
         <v>10.7068672180176</v>
       </c>
       <c r="G598" t="n">
-        <v>10.5252885818481</v>
+        <v>10.5252876281738</v>
       </c>
       <c r="H598" t="n">
         <v>677899</v>
@@ -17914,7 +17914,7 @@
         <v>10.4277601242065</v>
       </c>
       <c r="G605" t="n">
-        <v>10.2509145736694</v>
+        <v>10.2509136199951</v>
       </c>
       <c r="H605" t="n">
         <v>654563</v>
@@ -17972,7 +17972,7 @@
         <v>10.0090990066528</v>
       </c>
       <c r="G607" t="n">
-        <v>9.83935260772705</v>
+        <v>9.83935356140137</v>
       </c>
       <c r="H607" t="n">
         <v>1087774</v>
@@ -80125,6 +80125,35 @@
         <v>1663269</v>
       </c>
       <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>12.4700002670288</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>12.6599998474121</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>12.2849998474121</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>12.6599998474121</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>12.6599998474121</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>2150790</v>
+      </c>
+      <c r="I2751" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -80157,6 +80157,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2752">
+      <c r="A2752" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2752" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2752" t="n">
+        <v>12.6300001144409</v>
+      </c>
+      <c r="D2752" t="n">
+        <v>12.7449998855591</v>
+      </c>
+      <c r="E2752" t="n">
+        <v>12.3649997711182</v>
+      </c>
+      <c r="F2752" t="n">
+        <v>12.5100002288818</v>
+      </c>
+      <c r="G2752" t="n">
+        <v>12.5100002288818</v>
+      </c>
+      <c r="H2752" t="n">
+        <v>2285627</v>
+      </c>
+      <c r="I2752" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -80186,6 +80186,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2753">
+      <c r="A2753" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2753" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2753" t="n">
+        <v>12.4650001525879</v>
+      </c>
+      <c r="D2753" t="n">
+        <v>12.875</v>
+      </c>
+      <c r="E2753" t="n">
+        <v>12.3500003814697</v>
+      </c>
+      <c r="F2753" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="G2753" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="H2753" t="n">
+        <v>2347251</v>
+      </c>
+      <c r="I2753" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FCT.MI.xlsx
+++ b/data/FCT.MI.xlsx
@@ -80215,6 +80215,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2754">
+      <c r="A2754" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2754" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2754" t="n">
+        <v>12.5950002670288</v>
+      </c>
+      <c r="D2754" t="n">
+        <v>12.6549997329712</v>
+      </c>
+      <c r="E2754" t="n">
+        <v>12.4350004196167</v>
+      </c>
+      <c r="F2754" t="n">
+        <v>12.6450004577637</v>
+      </c>
+      <c r="G2754" t="n">
+        <v>12.6450004577637</v>
+      </c>
+      <c r="H2754" t="n">
+        <v>2185745</v>
+      </c>
+      <c r="I2754" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
